--- a/data/raw/NCE_data.xlsx
+++ b/data/raw/NCE_data.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://waikatouniversitynz-my.sharepoint.com/personal/or81_students_waikato_ac_nz/Documents/Documents/PhD/Data/4.5NCE/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://waikatouniversitynz-my.sharepoint.com/personal/or81_students_waikato_ac_nz/Documents/Documents/PhD/01_thesis_chapters/05_fear_study/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C509BC5-B9CD-4355-A94E-B3E32C99D6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{1C509BC5-B9CD-4355-A94E-B3E32C99D6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CC211BF-B576-4E0F-BD09-C03127A9F36E}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="4" xr2:uid="{884ED942-72D7-478A-91F6-B92A4F060477}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{884ED942-72D7-478A-91F6-B92A4F060477}"/>
   </bookViews>
   <sheets>
     <sheet name="NCE_exp" sheetId="2" r:id="rId1"/>
-    <sheet name="GoPro" sheetId="3" r:id="rId2"/>
-    <sheet name="Feeding" sheetId="4" r:id="rId3"/>
-    <sheet name="pellet_weigth" sheetId="5" r:id="rId4"/>
-    <sheet name="Feeding2" sheetId="6" r:id="rId5"/>
+    <sheet name="Long" sheetId="7" r:id="rId2"/>
+    <sheet name="GoPro" sheetId="3" r:id="rId3"/>
+    <sheet name="Feeding" sheetId="4" r:id="rId4"/>
+    <sheet name="pellet_weigth" sheetId="5" r:id="rId5"/>
+    <sheet name="Feeding2" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">NCE_exp!$A$1:$BK$65</definedName>
@@ -151,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3993" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4023" uniqueCount="191">
   <si>
     <t>S</t>
   </si>
@@ -1211,7 +1212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B26400D-0C90-4A8A-9A9D-ADEEFBB0CA10}">
-  <dimension ref="A1:BR73"/>
+  <dimension ref="A1:BR65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.26171875" bestFit="1" customWidth="1"/>
@@ -12984,518 +12985,6 @@
       </c>
       <c r="BQ65" s="2"/>
     </row>
-    <row r="66" spans="1:69" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" t="s">
-        <v>8</v>
-      </c>
-      <c r="B66">
-        <v>65</v>
-      </c>
-      <c r="C66">
-        <v>9</v>
-      </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66" s="2">
-        <v>45946</v>
-      </c>
-      <c r="F66" t="s">
-        <v>7</v>
-      </c>
-      <c r="G66" t="s">
-        <v>12</v>
-      </c>
-      <c r="H66" t="s">
-        <v>5</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AX66" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AZ66" t="s">
-        <v>18</v>
-      </c>
-      <c r="BA66">
-        <v>97</v>
-      </c>
-      <c r="BC66">
-        <v>9</v>
-      </c>
-      <c r="BD66" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE66" t="s">
-        <v>16</v>
-      </c>
-      <c r="BF66">
-        <v>30.22</v>
-      </c>
-      <c r="BG66">
-        <v>16</v>
-      </c>
-      <c r="BH66">
-        <v>6</v>
-      </c>
-      <c r="BI66">
-        <v>1</v>
-      </c>
-      <c r="BJ66">
-        <v>2</v>
-      </c>
-      <c r="BQ66" s="2"/>
-    </row>
-    <row r="67" spans="1:69" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" t="s">
-        <v>8</v>
-      </c>
-      <c r="B67">
-        <v>66</v>
-      </c>
-      <c r="C67">
-        <v>9</v>
-      </c>
-      <c r="D67">
-        <v>2</v>
-      </c>
-      <c r="E67" s="2">
-        <v>45946</v>
-      </c>
-      <c r="F67" t="s">
-        <v>7</v>
-      </c>
-      <c r="G67" t="s">
-        <v>6</v>
-      </c>
-      <c r="H67" t="s">
-        <v>4</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AZ67" t="s">
-        <v>17</v>
-      </c>
-      <c r="BA67">
-        <v>98</v>
-      </c>
-      <c r="BC67">
-        <v>10</v>
-      </c>
-      <c r="BD67" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE67" t="s">
-        <v>16</v>
-      </c>
-      <c r="BF67">
-        <v>30.91</v>
-      </c>
-      <c r="BG67">
-        <v>21</v>
-      </c>
-      <c r="BH67">
-        <v>8</v>
-      </c>
-      <c r="BI67">
-        <v>2</v>
-      </c>
-      <c r="BJ67">
-        <v>2</v>
-      </c>
-      <c r="BQ67" s="2"/>
-    </row>
-    <row r="68" spans="1:69" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" t="s">
-        <v>8</v>
-      </c>
-      <c r="B68">
-        <v>67</v>
-      </c>
-      <c r="C68">
-        <v>9</v>
-      </c>
-      <c r="D68">
-        <v>3</v>
-      </c>
-      <c r="E68" s="2">
-        <v>45946</v>
-      </c>
-      <c r="F68" t="s">
-        <v>7</v>
-      </c>
-      <c r="G68" t="s">
-        <v>13</v>
-      </c>
-      <c r="H68" t="s">
-        <v>5</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AX68" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY68" t="s">
-        <v>3</v>
-      </c>
-      <c r="BA68">
-        <v>99</v>
-      </c>
-      <c r="BC68">
-        <v>11</v>
-      </c>
-      <c r="BD68" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE68" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF68">
-        <v>25.21</v>
-      </c>
-      <c r="BG68">
-        <v>8</v>
-      </c>
-      <c r="BH68">
-        <v>8</v>
-      </c>
-      <c r="BI68">
-        <v>2</v>
-      </c>
-      <c r="BJ68">
-        <v>2</v>
-      </c>
-      <c r="BK68" t="s">
-        <v>15</v>
-      </c>
-      <c r="BQ68" s="2">
-        <v>45944</v>
-      </c>
-    </row>
-    <row r="69" spans="1:69" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" t="s">
-        <v>8</v>
-      </c>
-      <c r="B69">
-        <v>68</v>
-      </c>
-      <c r="C69">
-        <v>9</v>
-      </c>
-      <c r="D69">
-        <v>4</v>
-      </c>
-      <c r="E69" s="2">
-        <v>45946</v>
-      </c>
-      <c r="F69" t="s">
-        <v>7</v>
-      </c>
-      <c r="G69" t="s">
-        <v>12</v>
-      </c>
-      <c r="H69" t="s">
-        <v>10</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AX69" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY69" t="s">
-        <v>3</v>
-      </c>
-      <c r="BA69">
-        <v>100</v>
-      </c>
-      <c r="BC69">
-        <v>12</v>
-      </c>
-      <c r="BD69" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE69" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF69">
-        <v>21.46</v>
-      </c>
-      <c r="BG69">
-        <v>6</v>
-      </c>
-      <c r="BH69">
-        <v>8</v>
-      </c>
-      <c r="BI69">
-        <v>2</v>
-      </c>
-      <c r="BJ69">
-        <v>2</v>
-      </c>
-      <c r="BQ69" s="2"/>
-    </row>
-    <row r="70" spans="1:69" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" t="s">
-        <v>8</v>
-      </c>
-      <c r="B70">
-        <v>69</v>
-      </c>
-      <c r="C70">
-        <v>9</v>
-      </c>
-      <c r="D70">
-        <v>5</v>
-      </c>
-      <c r="E70" s="2">
-        <v>45946</v>
-      </c>
-      <c r="F70" t="s">
-        <v>7</v>
-      </c>
-      <c r="G70" t="s">
-        <v>6</v>
-      </c>
-      <c r="H70" t="s">
-        <v>10</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AZ70" t="s">
-        <v>14</v>
-      </c>
-      <c r="BA70">
-        <v>78</v>
-      </c>
-      <c r="BC70">
-        <v>13</v>
-      </c>
-      <c r="BD70" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE70" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF70">
-        <v>18.350000000000001</v>
-      </c>
-      <c r="BG70">
-        <v>3</v>
-      </c>
-      <c r="BH70">
-        <v>8</v>
-      </c>
-      <c r="BI70">
-        <v>2</v>
-      </c>
-      <c r="BJ70">
-        <v>2</v>
-      </c>
-      <c r="BQ70" s="2"/>
-    </row>
-    <row r="71" spans="1:69" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" t="s">
-        <v>8</v>
-      </c>
-      <c r="B71">
-        <v>70</v>
-      </c>
-      <c r="C71">
-        <v>9</v>
-      </c>
-      <c r="D71">
-        <v>6</v>
-      </c>
-      <c r="E71" s="2">
-        <v>45946</v>
-      </c>
-      <c r="F71" t="s">
-        <v>7</v>
-      </c>
-      <c r="G71" t="s">
-        <v>13</v>
-      </c>
-      <c r="H71" t="s">
-        <v>10</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AX71" t="s">
-        <v>4</v>
-      </c>
-      <c r="AY71" t="s">
-        <v>3</v>
-      </c>
-      <c r="BA71">
-        <v>102</v>
-      </c>
-      <c r="BB71">
-        <v>58</v>
-      </c>
-      <c r="BC71">
-        <v>14</v>
-      </c>
-      <c r="BD71" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE71" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF71">
-        <v>26.87</v>
-      </c>
-      <c r="BG71">
-        <v>11</v>
-      </c>
-      <c r="BH71">
-        <v>7</v>
-      </c>
-      <c r="BI71">
-        <v>2</v>
-      </c>
-      <c r="BJ71">
-        <v>2</v>
-      </c>
-      <c r="BQ71" s="2"/>
-    </row>
-    <row r="72" spans="1:69" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" t="s">
-        <v>8</v>
-      </c>
-      <c r="B72">
-        <v>71</v>
-      </c>
-      <c r="C72">
-        <v>9</v>
-      </c>
-      <c r="D72">
-        <v>7</v>
-      </c>
-      <c r="E72" s="2">
-        <v>45946</v>
-      </c>
-      <c r="F72" t="s">
-        <v>7</v>
-      </c>
-      <c r="G72" t="s">
-        <v>12</v>
-      </c>
-      <c r="H72" t="s">
-        <v>10</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AX72" t="s">
-        <v>10</v>
-      </c>
-      <c r="AY72" t="s">
-        <v>9</v>
-      </c>
-      <c r="BA72">
-        <v>84</v>
-      </c>
-      <c r="BC72">
-        <v>15</v>
-      </c>
-      <c r="BD72" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE72" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF72">
-        <v>25.2</v>
-      </c>
-      <c r="BG72">
-        <v>11</v>
-      </c>
-      <c r="BH72">
-        <v>8</v>
-      </c>
-      <c r="BI72">
-        <v>2</v>
-      </c>
-      <c r="BJ72">
-        <v>2</v>
-      </c>
-      <c r="BQ72" s="2"/>
-    </row>
-    <row r="73" spans="1:69" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" t="s">
-        <v>8</v>
-      </c>
-      <c r="B73">
-        <v>72</v>
-      </c>
-      <c r="C73">
-        <v>9</v>
-      </c>
-      <c r="D73">
-        <v>8</v>
-      </c>
-      <c r="E73" s="2">
-        <v>45946</v>
-      </c>
-      <c r="F73" t="s">
-        <v>7</v>
-      </c>
-      <c r="G73" t="s">
-        <v>6</v>
-      </c>
-      <c r="H73" t="s">
-        <v>5</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AX73" t="s">
-        <v>4</v>
-      </c>
-      <c r="AY73" t="s">
-        <v>3</v>
-      </c>
-      <c r="AZ73" t="s">
-        <v>2</v>
-      </c>
-      <c r="BA73">
-        <v>87</v>
-      </c>
-      <c r="BC73">
-        <v>16</v>
-      </c>
-      <c r="BD73" t="s">
-        <v>1</v>
-      </c>
-      <c r="BE73" t="s">
-        <v>0</v>
-      </c>
-      <c r="BF73">
-        <v>21.26</v>
-      </c>
-      <c r="BG73">
-        <v>7</v>
-      </c>
-      <c r="BH73">
-        <v>6</v>
-      </c>
-      <c r="BI73">
-        <v>2</v>
-      </c>
-      <c r="BJ73">
-        <v>2</v>
-      </c>
-      <c r="BQ73" s="2"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:BK65" xr:uid="{4A698BA5-38D0-4CDC-AB59-F3ED83474DEE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13503,6 +12992,626 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{755ECFD5-44B2-41A9-9B91-2DC8174B9BDF}">
+  <dimension ref="A1:AD9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="8" max="8" width="9.89453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.3125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.89453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.3671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" s="6" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>65</v>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45946</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2">
+        <v>97</v>
+      </c>
+      <c r="O2">
+        <v>9</v>
+      </c>
+      <c r="P2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2">
+        <v>30.22</v>
+      </c>
+      <c r="S2">
+        <v>16</v>
+      </c>
+      <c r="T2">
+        <v>6</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>2</v>
+      </c>
+      <c r="AC2" s="2"/>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>66</v>
+      </c>
+      <c r="C3">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45946</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3">
+        <v>98</v>
+      </c>
+      <c r="O3">
+        <v>10</v>
+      </c>
+      <c r="P3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3">
+        <v>30.91</v>
+      </c>
+      <c r="S3">
+        <v>21</v>
+      </c>
+      <c r="T3">
+        <v>8</v>
+      </c>
+      <c r="U3">
+        <v>2</v>
+      </c>
+      <c r="V3">
+        <v>2</v>
+      </c>
+      <c r="AC3" s="2"/>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>67</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45946</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>99</v>
+      </c>
+      <c r="O4">
+        <v>11</v>
+      </c>
+      <c r="P4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>25.21</v>
+      </c>
+      <c r="S4">
+        <v>8</v>
+      </c>
+      <c r="T4">
+        <v>8</v>
+      </c>
+      <c r="U4">
+        <v>2</v>
+      </c>
+      <c r="V4">
+        <v>2</v>
+      </c>
+      <c r="W4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>45944</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>68</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45946</v>
+      </c>
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>100</v>
+      </c>
+      <c r="O5">
+        <v>12</v>
+      </c>
+      <c r="P5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>21.46</v>
+      </c>
+      <c r="S5">
+        <v>6</v>
+      </c>
+      <c r="T5">
+        <v>8</v>
+      </c>
+      <c r="U5">
+        <v>2</v>
+      </c>
+      <c r="V5">
+        <v>2</v>
+      </c>
+      <c r="AC5" s="2"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>69</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45946</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6">
+        <v>78</v>
+      </c>
+      <c r="O6">
+        <v>13</v>
+      </c>
+      <c r="P6" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>18.350000000000001</v>
+      </c>
+      <c r="S6">
+        <v>3</v>
+      </c>
+      <c r="T6">
+        <v>8</v>
+      </c>
+      <c r="U6">
+        <v>2</v>
+      </c>
+      <c r="V6">
+        <v>2</v>
+      </c>
+      <c r="AC6" s="2"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>70</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45946</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7">
+        <v>102</v>
+      </c>
+      <c r="N7">
+        <v>58</v>
+      </c>
+      <c r="O7">
+        <v>14</v>
+      </c>
+      <c r="P7" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>26.87</v>
+      </c>
+      <c r="S7">
+        <v>11</v>
+      </c>
+      <c r="T7">
+        <v>7</v>
+      </c>
+      <c r="U7">
+        <v>2</v>
+      </c>
+      <c r="V7">
+        <v>2</v>
+      </c>
+      <c r="AC7" s="2"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>71</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45946</v>
+      </c>
+      <c r="F8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M8">
+        <v>84</v>
+      </c>
+      <c r="O8">
+        <v>15</v>
+      </c>
+      <c r="P8" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>25.2</v>
+      </c>
+      <c r="S8">
+        <v>11</v>
+      </c>
+      <c r="T8">
+        <v>8</v>
+      </c>
+      <c r="U8">
+        <v>2</v>
+      </c>
+      <c r="V8">
+        <v>2</v>
+      </c>
+      <c r="AC8" s="2"/>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>72</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45946</v>
+      </c>
+      <c r="F9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" t="s">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>87</v>
+      </c>
+      <c r="O9">
+        <v>16</v>
+      </c>
+      <c r="P9" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>21.26</v>
+      </c>
+      <c r="S9">
+        <v>7</v>
+      </c>
+      <c r="T9">
+        <v>6</v>
+      </c>
+      <c r="U9">
+        <v>2</v>
+      </c>
+      <c r="V9">
+        <v>2</v>
+      </c>
+      <c r="AC9" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E0D278E-32E1-454A-B1A3-B767039FD5C6}">
   <dimension ref="A1:N58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -13574,19 +13683,19 @@
         <v>13681</v>
       </c>
       <c r="H2">
-        <f>G2-F2+1</f>
+        <f t="shared" ref="H2:H19" si="0">G2-F2+1</f>
         <v>3674</v>
       </c>
       <c r="I2">
         <v>5</v>
       </c>
       <c r="J2" s="9">
-        <f>IF(OR(H2="",I2=""),"", ((H2-1)*I2)/86400)</f>
+        <f t="shared" ref="J2:J19" si="1">IF(OR(H2="",I2=""),"", ((H2-1)*I2)/86400)</f>
         <v>0.21255787037037038</v>
       </c>
       <c r="K2" s="9"/>
       <c r="L2" s="9">
-        <f>K2+J2</f>
+        <f t="shared" ref="L2:L19" si="2">K2+J2</f>
         <v>0.21255787037037038</v>
       </c>
       <c r="M2" t="s">
@@ -13616,19 +13725,19 @@
         <v>16183</v>
       </c>
       <c r="H3">
-        <f>G3-F3+1</f>
+        <f t="shared" si="0"/>
         <v>3675</v>
       </c>
       <c r="I3">
         <v>5</v>
       </c>
       <c r="J3" s="9">
-        <f>IF(OR(H3="",I3=""),"", ((H3-1)*I3)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.21261574074074074</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="9">
-        <f>K3+J3</f>
+        <f t="shared" si="2"/>
         <v>0.21261574074074074</v>
       </c>
       <c r="M3" t="s">
@@ -13658,19 +13767,19 @@
         <v>17320</v>
       </c>
       <c r="H4">
-        <f>G4-F4+1</f>
+        <f t="shared" si="0"/>
         <v>3639</v>
       </c>
       <c r="I4">
         <v>5</v>
       </c>
       <c r="J4" s="9">
-        <f>IF(OR(H4="",I4=""),"", ((H4-1)*I4)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.21053240740740742</v>
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="9">
-        <f>K4+J4</f>
+        <f t="shared" si="2"/>
         <v>0.21053240740740742</v>
       </c>
       <c r="M4" t="s">
@@ -13700,19 +13809,19 @@
         <v>16146</v>
       </c>
       <c r="H5">
-        <f>G5-F5+1</f>
+        <f t="shared" si="0"/>
         <v>3643</v>
       </c>
       <c r="I5">
         <v>5</v>
       </c>
       <c r="J5" s="9">
-        <f>IF(OR(H5="",I5=""),"", ((H5-1)*I5)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.21076388888888889</v>
       </c>
       <c r="K5" s="9"/>
       <c r="L5" s="9">
-        <f>K5+J5</f>
+        <f t="shared" si="2"/>
         <v>0.21076388888888889</v>
       </c>
       <c r="M5" t="s">
@@ -13742,19 +13851,19 @@
         <v>20955</v>
       </c>
       <c r="H6">
-        <f>G6-F6+1</f>
+        <f t="shared" si="0"/>
         <v>3635</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
       <c r="J6" s="9">
-        <f>IF(OR(H6="",I6=""),"", ((H6-1)*I6)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.21030092592592592</v>
       </c>
       <c r="K6" s="9"/>
       <c r="L6" s="9">
-        <f>K6+J6</f>
+        <f t="shared" si="2"/>
         <v>0.21030092592592592</v>
       </c>
       <c r="M6" t="s">
@@ -13784,19 +13893,19 @@
         <v>19780</v>
       </c>
       <c r="H7">
-        <f>G7-F7+1</f>
+        <f t="shared" si="0"/>
         <v>3634</v>
       </c>
       <c r="I7">
         <v>5</v>
       </c>
       <c r="J7" s="9">
-        <f>IF(OR(H7="",I7=""),"", ((H7-1)*I7)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.21024305555555556</v>
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="9">
-        <f>K7+J7</f>
+        <f t="shared" si="2"/>
         <v>0.21024305555555556</v>
       </c>
       <c r="M7" t="s">
@@ -13826,19 +13935,19 @@
         <v>19968</v>
       </c>
       <c r="H8">
-        <f>G8-F8+1</f>
+        <f t="shared" si="0"/>
         <v>188</v>
       </c>
       <c r="I8">
         <v>5</v>
       </c>
       <c r="J8" s="9">
-        <f>IF(OR(H8="",I8=""),"", ((H8-1)*I8)/86400)</f>
+        <f t="shared" si="1"/>
         <v>1.0821759259259258E-2</v>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9">
-        <f>K8+J8</f>
+        <f t="shared" si="2"/>
         <v>1.0821759259259258E-2</v>
       </c>
       <c r="M8" t="s">
@@ -13868,19 +13977,19 @@
         <v>19813</v>
       </c>
       <c r="H9">
-        <f>G9-F9+1</f>
+        <f t="shared" si="0"/>
         <v>3630</v>
       </c>
       <c r="I9">
         <v>5</v>
       </c>
       <c r="J9" s="9">
-        <f>IF(OR(H9="",I9=""),"", ((H9-1)*I9)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.21001157407407409</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9">
-        <f>K9+J9</f>
+        <f t="shared" si="2"/>
         <v>0.21001157407407409</v>
       </c>
       <c r="M9" t="s">
@@ -13910,19 +14019,19 @@
         <v>33456</v>
       </c>
       <c r="H10">
-        <f>G10-F10+1</f>
+        <f t="shared" si="0"/>
         <v>3643</v>
       </c>
       <c r="I10">
         <v>5</v>
       </c>
       <c r="J10" s="9">
-        <f>IF(OR(H10="",I10=""),"", ((H10-1)*I10)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.21076388888888889</v>
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="9">
-        <f>K10+J10</f>
+        <f t="shared" si="2"/>
         <v>0.21076388888888889</v>
       </c>
       <c r="M10" t="s">
@@ -13952,19 +14061,19 @@
         <v>13415</v>
       </c>
       <c r="H11">
-        <f>G11-F11+1</f>
+        <f t="shared" si="0"/>
         <v>2460</v>
       </c>
       <c r="I11">
         <v>5</v>
       </c>
       <c r="J11" s="9">
-        <f>IF(OR(H11="",I11=""),"", ((H11-1)*I11)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.14230324074074074</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9">
-        <f>K11+J11</f>
+        <f t="shared" si="2"/>
         <v>0.14230324074074074</v>
       </c>
       <c r="M11" t="s">
@@ -13997,19 +14106,19 @@
         <v>17074</v>
       </c>
       <c r="H12">
-        <f>G12-F12+1</f>
+        <f t="shared" si="0"/>
         <v>3618</v>
       </c>
       <c r="I12">
         <v>5</v>
       </c>
       <c r="J12" s="9">
-        <f>IF(OR(H12="",I12=""),"", ((H12-1)*I12)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.20931712962962962</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9">
-        <f>K12+J12</f>
+        <f t="shared" si="2"/>
         <v>0.20931712962962962</v>
       </c>
       <c r="M12" t="s">
@@ -14039,19 +14148,19 @@
         <v>17036</v>
       </c>
       <c r="H13">
-        <f>G13-F13+1</f>
+        <f t="shared" si="0"/>
         <v>3621</v>
       </c>
       <c r="I13">
         <v>5</v>
       </c>
       <c r="J13" s="9">
-        <f>IF(OR(H13="",I13=""),"", ((H13-1)*I13)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.20949074074074073</v>
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9">
-        <f>K13+J13</f>
+        <f t="shared" si="2"/>
         <v>0.20949074074074073</v>
       </c>
       <c r="M13" t="s">
@@ -14081,19 +14190,19 @@
         <v>30697</v>
       </c>
       <c r="H14">
-        <f>G14-F14+1</f>
+        <f t="shared" si="0"/>
         <v>3621</v>
       </c>
       <c r="I14">
         <v>5</v>
       </c>
       <c r="J14" s="9">
-        <f>IF(OR(H14="",I14=""),"", ((H14-1)*I14)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.20949074074074073</v>
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9">
-        <f>K14+J14</f>
+        <f t="shared" si="2"/>
         <v>0.20949074074074073</v>
       </c>
       <c r="M14" t="s">
@@ -14123,19 +14232,19 @@
         <v>20659</v>
       </c>
       <c r="H15">
-        <f>G15-F15+1</f>
+        <f t="shared" si="0"/>
         <v>3623</v>
       </c>
       <c r="I15">
         <v>5</v>
       </c>
       <c r="J15" s="9">
-        <f>IF(OR(H15="",I15=""),"", ((H15-1)*I15)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.20960648148148148</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9">
-        <f>K15+J15</f>
+        <f t="shared" si="2"/>
         <v>0.20960648148148148</v>
       </c>
       <c r="M15" t="s">
@@ -14165,19 +14274,19 @@
         <v>14310</v>
       </c>
       <c r="H16">
-        <f>G16-F16+1</f>
+        <f t="shared" si="0"/>
         <v>3613</v>
       </c>
       <c r="I16">
         <v>5</v>
       </c>
       <c r="J16" s="9">
-        <f>IF(OR(H16="",I16=""),"", ((H16-1)*I16)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.20902777777777778</v>
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="9">
-        <f>K16+J16</f>
+        <f t="shared" si="2"/>
         <v>0.20902777777777778</v>
       </c>
       <c r="M16" t="s">
@@ -14207,19 +14316,19 @@
         <v>14273</v>
       </c>
       <c r="H17">
-        <f>G17-F17+1</f>
+        <f t="shared" si="0"/>
         <v>3614</v>
       </c>
       <c r="I17">
         <v>5</v>
       </c>
       <c r="J17" s="9">
-        <f>IF(OR(H17="",I17=""),"", ((H17-1)*I17)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.20908564814814815</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9">
-        <f>K17+J17</f>
+        <f t="shared" si="2"/>
         <v>0.20908564814814815</v>
       </c>
       <c r="M17" t="s">
@@ -14249,19 +14358,19 @@
         <v>27762</v>
       </c>
       <c r="H18">
-        <f>G18-F18+1</f>
+        <f t="shared" si="0"/>
         <v>13452</v>
       </c>
       <c r="I18">
         <v>5</v>
       </c>
       <c r="J18" s="9">
-        <f>IF(OR(H18="",I18=""),"", ((H18-1)*I18)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.77841435185185182</v>
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9">
-        <f>K18+J18</f>
+        <f t="shared" si="2"/>
         <v>0.77841435185185182</v>
       </c>
       <c r="M18" t="s">
@@ -14291,19 +14400,19 @@
         <v>27708</v>
       </c>
       <c r="H19">
-        <f>G19-F19+1</f>
+        <f t="shared" si="0"/>
         <v>13435</v>
       </c>
       <c r="I19">
         <v>5</v>
       </c>
       <c r="J19" s="9">
-        <f>IF(OR(H19="",I19=""),"", ((H19-1)*I19)/86400)</f>
+        <f t="shared" si="1"/>
         <v>0.77743055555555551</v>
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9">
-        <f>K19+J19</f>
+        <f t="shared" si="2"/>
         <v>0.77743055555555551</v>
       </c>
       <c r="M19" t="s">
@@ -14510,7 +14619,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{853DF2F7-7B07-467C-B845-65DDCE944602}">
   <dimension ref="A1:AO65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -14679,14 +14788,14 @@
         <v>5</v>
       </c>
       <c r="M2" s="3">
-        <f>I2+L2</f>
+        <f t="shared" ref="M2:M33" si="0">I2+L2</f>
         <v>10</v>
       </c>
       <c r="N2" s="3">
         <v>7</v>
       </c>
       <c r="O2" s="3">
-        <f>N2/M2</f>
+        <f t="shared" ref="O2:O33" si="1">N2/M2</f>
         <v>0.7</v>
       </c>
       <c r="P2" s="3">
@@ -14696,11 +14805,11 @@
         <v>2</v>
       </c>
       <c r="R2" s="3">
-        <f>I2+L2+P2</f>
+        <f t="shared" ref="R2:R33" si="2">I2+L2+P2</f>
         <v>10</v>
       </c>
       <c r="S2" s="3">
-        <f>R2-Q2</f>
+        <f t="shared" ref="S2:S17" si="3">R2-Q2</f>
         <v>8</v>
       </c>
       <c r="T2" s="12">
@@ -14714,11 +14823,11 @@
         <v>5.3324999999999996</v>
       </c>
       <c r="W2" s="3">
-        <f>V2-U2</f>
+        <f t="shared" ref="W2:W17" si="4">V2-U2</f>
         <v>1.9899999999999807E-2</v>
       </c>
       <c r="X2" s="12">
-        <f>T2-W2</f>
+        <f t="shared" ref="X2:X17" si="5">T2-W2</f>
         <v>0.52146666666666663</v>
       </c>
       <c r="Y2" s="3" t="s">
@@ -14795,14 +14904,14 @@
         <v>0</v>
       </c>
       <c r="M3" s="3">
-        <f>I3+L3</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N3" s="3">
         <v>5</v>
       </c>
       <c r="O3" s="3">
-        <f>N3/M3</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="P3" s="3">
@@ -14812,11 +14921,11 @@
         <v>4.5</v>
       </c>
       <c r="R3" s="3">
-        <f>I3+L3+P3</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="S3" s="3">
-        <f>R3-Q3</f>
+        <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
       <c r="T3" s="12">
@@ -14830,11 +14939,11 @@
         <v>5.3487999999999998</v>
       </c>
       <c r="W3" s="3">
-        <f>V3-U3</f>
+        <f t="shared" si="4"/>
         <v>4.3499999999999872E-2</v>
       </c>
       <c r="X3" s="12">
-        <f>T3-W3</f>
+        <f t="shared" si="5"/>
         <v>0.22718333333333335</v>
       </c>
       <c r="Y3" s="3" t="s">
@@ -14911,14 +15020,14 @@
         <v>5</v>
       </c>
       <c r="M4" s="3">
-        <f>I4+L4</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N4" s="3">
         <v>1</v>
       </c>
       <c r="O4" s="3">
-        <f>N4/M4</f>
+        <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
       <c r="P4" s="3">
@@ -14928,11 +15037,11 @@
         <v>4.5</v>
       </c>
       <c r="R4" s="3">
-        <f>I4+L4+P4</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="S4" s="3">
-        <f>R4-Q4</f>
+        <f t="shared" si="3"/>
         <v>10.5</v>
       </c>
       <c r="T4" s="12">
@@ -14946,11 +15055,11 @@
         <v>5.4924999999999997</v>
       </c>
       <c r="W4" s="3">
-        <f>V4-U4</f>
+        <f t="shared" si="4"/>
         <v>0.19029999999999969</v>
       </c>
       <c r="X4" s="12">
-        <f>T4-W4</f>
+        <f t="shared" si="5"/>
         <v>0.62175000000000002</v>
       </c>
       <c r="Y4" s="3" t="s">
@@ -15027,14 +15136,14 @@
         <v>0</v>
       </c>
       <c r="M5" s="3">
-        <f>I5+L5</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N5" s="3">
         <v>4</v>
       </c>
       <c r="O5" s="3">
-        <f>N5/M5</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
       <c r="P5" s="3">
@@ -15044,11 +15153,11 @@
         <v>0</v>
       </c>
       <c r="R5" s="3">
-        <f>I5+L5+P5</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="S5" s="3">
-        <f>R5-Q5</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="T5" s="12">
@@ -15062,11 +15171,11 @@
         <v>5.3719000000000001</v>
       </c>
       <c r="W5" s="3">
-        <f>V5-U5</f>
+        <f t="shared" si="4"/>
         <v>4.750000000000032E-2</v>
       </c>
       <c r="X5" s="12">
-        <f>T5-W5</f>
+        <f t="shared" si="5"/>
         <v>0.2231833333333329</v>
       </c>
       <c r="Y5" s="3" t="s">
@@ -15143,14 +15252,14 @@
         <v>0</v>
       </c>
       <c r="M6" s="3">
-        <f>I6+L6</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N6" s="3">
         <v>4.5</v>
       </c>
       <c r="O6" s="3">
-        <f>N6/M6</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="P6" s="3">
@@ -15160,11 +15269,11 @@
         <v>0.5</v>
       </c>
       <c r="R6" s="3">
-        <f>I6+L6+P6</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="S6" s="3">
-        <f>R6-Q6</f>
+        <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
       <c r="T6" s="12">
@@ -15178,11 +15287,11 @@
         <v>5.3333000000000004</v>
       </c>
       <c r="W6" s="3">
-        <f>V6-U6</f>
+        <f t="shared" si="4"/>
         <v>2.8700000000000614E-2</v>
       </c>
       <c r="X6" s="12">
-        <f>T6-W6</f>
+        <f t="shared" si="5"/>
         <v>0.24198333333333261</v>
       </c>
       <c r="Y6" s="3" t="s">
@@ -15257,14 +15366,14 @@
         <v>5</v>
       </c>
       <c r="M7" s="3">
-        <f>I7+L7</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N7" s="3">
         <v>5</v>
       </c>
       <c r="O7" s="3">
-        <f>N7/M7</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="P7" s="3">
@@ -15274,11 +15383,11 @@
         <v>5</v>
       </c>
       <c r="R7" s="3">
-        <f>I7+L7+P7</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S7" s="3">
-        <f>R7-Q7</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="T7" s="12">
@@ -15292,11 +15401,11 @@
         <v>5.4973000000000001</v>
       </c>
       <c r="W7" s="3">
-        <f>V7-U7</f>
+        <f t="shared" si="4"/>
         <v>0.14839999999999964</v>
       </c>
       <c r="X7" s="12">
-        <f>T7-W7</f>
+        <f t="shared" si="5"/>
         <v>0.3929666666666668</v>
       </c>
       <c r="Y7" s="3" t="s">
@@ -15371,14 +15480,14 @@
         <v>5</v>
       </c>
       <c r="M8" s="3">
-        <f>I8+L8</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N8" s="3">
         <v>2.5</v>
       </c>
       <c r="O8" s="3">
-        <f>N8/M8</f>
+        <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
       <c r="P8" s="3">
@@ -15388,11 +15497,11 @@
         <v>5</v>
       </c>
       <c r="R8" s="3">
-        <f>I8+L8+P8</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="S8" s="3">
-        <f>R8-Q8</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="T8" s="12">
@@ -15406,11 +15515,11 @@
         <v>5.5107999999999997</v>
       </c>
       <c r="W8" s="3">
-        <f>V8-U8</f>
+        <f t="shared" si="4"/>
         <v>0.1888999999999994</v>
       </c>
       <c r="X8" s="12">
-        <f>T8-W8</f>
+        <f t="shared" si="5"/>
         <v>0.62315000000000031</v>
       </c>
       <c r="Y8" s="3" t="s">
@@ -15487,14 +15596,14 @@
         <v>5</v>
       </c>
       <c r="M9" s="3">
-        <f>I9+L9</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N9" s="3">
         <v>7</v>
       </c>
       <c r="O9" s="3">
-        <f>N9/M9</f>
+        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
       <c r="P9" s="3">
@@ -15504,11 +15613,11 @@
         <v>6</v>
       </c>
       <c r="R9" s="3">
-        <f>I9+L9+P9</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S9" s="3">
-        <f>R9-Q9</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="T9" s="12">
@@ -15522,11 +15631,11 @@
         <v>5.4987000000000004</v>
       </c>
       <c r="W9" s="3">
-        <f>V9-U9</f>
+        <f t="shared" si="4"/>
         <v>0.15700000000000003</v>
       </c>
       <c r="X9" s="12">
-        <f>T9-W9</f>
+        <f t="shared" si="5"/>
         <v>0.38436666666666641</v>
       </c>
       <c r="Y9" s="3" t="s">
@@ -15601,14 +15710,14 @@
         <v>0</v>
       </c>
       <c r="M10" s="3">
-        <f>I10+L10</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N10" s="3">
         <v>0</v>
       </c>
       <c r="O10" s="3">
-        <f>N10/M10</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P10" s="3">
@@ -15618,11 +15727,11 @@
         <v>0</v>
       </c>
       <c r="R10" s="3">
-        <f>I10+L10+P10</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S10" s="3">
-        <f>R10-Q10</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="T10" s="12">
@@ -15636,11 +15745,11 @@
         <v>5.3574000000000002</v>
       </c>
       <c r="W10" s="3">
-        <f>V10-U10</f>
+        <f t="shared" si="4"/>
         <v>2.3200000000000109E-2</v>
       </c>
       <c r="X10" s="12">
-        <f>T10-W10</f>
+        <f t="shared" si="5"/>
         <v>0.51816666666666633</v>
       </c>
       <c r="Y10" s="3" t="s">
@@ -15717,14 +15826,14 @@
         <v>5</v>
       </c>
       <c r="M11" s="3">
-        <f>I11+L11</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N11" s="3">
         <v>5</v>
       </c>
       <c r="O11" s="3">
-        <f>N11/M11</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="P11" s="3">
@@ -15734,11 +15843,11 @@
         <v>2</v>
       </c>
       <c r="R11" s="3">
-        <f>I11+L11+P11</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S11" s="3">
-        <f>R11-Q11</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="T11" s="12">
@@ -15752,11 +15861,11 @@
         <v>5.3703000000000003</v>
       </c>
       <c r="W11" s="3">
-        <f>V11-U11</f>
+        <f t="shared" si="4"/>
         <v>8.8000000000000078E-2</v>
       </c>
       <c r="X11" s="12">
-        <f>T11-W11</f>
+        <f t="shared" si="5"/>
         <v>0.45336666666666636</v>
       </c>
       <c r="Y11" s="3" t="s">
@@ -15833,14 +15942,14 @@
         <v>0</v>
       </c>
       <c r="M12" s="3">
-        <f>I12+L12</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N12" s="3">
         <v>5</v>
       </c>
       <c r="O12" s="3">
-        <f>N12/M12</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="P12" s="3">
@@ -15850,11 +15959,11 @@
         <v>2.5</v>
       </c>
       <c r="R12" s="3">
-        <f>I12+L12+P12</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="S12" s="3">
-        <f>R12-Q12</f>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="T12" s="12">
@@ -15868,11 +15977,11 @@
         <v>5.4090999999999996</v>
       </c>
       <c r="W12" s="3">
-        <f>V12-U12</f>
+        <f t="shared" si="4"/>
         <v>3.2199999999999562E-2</v>
       </c>
       <c r="X12" s="12">
-        <f>T12-W12</f>
+        <f t="shared" si="5"/>
         <v>0.23848333333333366</v>
       </c>
       <c r="Y12" s="3" t="s">
@@ -15949,14 +16058,14 @@
         <v>5</v>
       </c>
       <c r="M13" s="3">
-        <f>I13+L13</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N13" s="3">
         <v>7</v>
       </c>
       <c r="O13" s="3">
-        <f>N13/M13</f>
+        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
       <c r="P13" s="3">
@@ -15966,11 +16075,11 @@
         <v>1</v>
       </c>
       <c r="R13" s="3">
-        <f>I13+L13+P13</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S13" s="3">
-        <f>R13-Q13</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="T13" s="12">
@@ -15984,11 +16093,11 @@
         <v>5.3334999999999999</v>
       </c>
       <c r="W13" s="3">
-        <f>V13-U13</f>
+        <f t="shared" si="4"/>
         <v>6.8399999999999572E-2</v>
       </c>
       <c r="X13" s="12">
-        <f>T13-W13</f>
+        <f t="shared" si="5"/>
         <v>0.47296666666666687</v>
       </c>
       <c r="Y13" s="3" t="s">
@@ -16065,14 +16174,14 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
-        <f>I14+L14</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>5</v>
       </c>
       <c r="O14" s="3">
-        <f>N14/M14</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="P14" s="3">
@@ -16082,11 +16191,11 @@
         <v>0.5</v>
       </c>
       <c r="R14" s="3">
-        <f>I14+L14+P14</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="S14" s="3">
-        <f>R14-Q14</f>
+        <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
       <c r="T14" s="12">
@@ -16100,11 +16209,11 @@
         <v>5.3845999999999998</v>
       </c>
       <c r="W14" s="3">
-        <f>V14-U14</f>
+        <f t="shared" si="4"/>
         <v>4.3800000000000061E-2</v>
       </c>
       <c r="X14" s="12">
-        <f>T14-W14</f>
+        <f t="shared" si="5"/>
         <v>0.22688333333333316</v>
       </c>
       <c r="Y14" s="3" t="s">
@@ -16181,14 +16290,14 @@
         <v>0</v>
       </c>
       <c r="M15" s="3">
-        <f>I15+L15</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N15" s="3">
         <v>5</v>
       </c>
       <c r="O15" s="3">
-        <f>N15/M15</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="P15" s="3">
@@ -16198,11 +16307,11 @@
         <v>0.5</v>
       </c>
       <c r="R15" s="3">
-        <f>I15+L15+P15</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="S15" s="3">
-        <f>R15-Q15</f>
+        <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
       <c r="T15" s="12">
@@ -16216,11 +16325,11 @@
         <v>5.3742999999999999</v>
       </c>
       <c r="W15" s="3">
-        <f>V15-U15</f>
+        <f t="shared" si="4"/>
         <v>3.9299999999999891E-2</v>
       </c>
       <c r="X15" s="12">
-        <f>T15-W15</f>
+        <f t="shared" si="5"/>
         <v>0.23138333333333333</v>
       </c>
       <c r="Y15" s="3" t="s">
@@ -16311,14 +16420,14 @@
         <v>5</v>
       </c>
       <c r="M16" s="3">
-        <f>I16+L16</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N16" s="3">
         <v>7</v>
       </c>
       <c r="O16" s="3">
-        <f>N16/M16</f>
+        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
       <c r="P16" s="3">
@@ -16328,11 +16437,11 @@
         <v>1</v>
       </c>
       <c r="R16" s="3">
-        <f>I16+L16+P16</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S16" s="3">
-        <f>R16-Q16</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="T16" s="12">
@@ -16346,11 +16455,11 @@
         <v>5.5160999999999998</v>
       </c>
       <c r="W16" s="3">
-        <f>V16-U16</f>
+        <f t="shared" si="4"/>
         <v>0.12549999999999972</v>
       </c>
       <c r="X16" s="12">
-        <f>T16-W16</f>
+        <f t="shared" si="5"/>
         <v>0.41586666666666672</v>
       </c>
       <c r="Y16" s="3" t="s">
@@ -16425,14 +16534,14 @@
         <v>5</v>
       </c>
       <c r="M17" s="3">
-        <f>I17+L17</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N17" s="3">
         <v>6</v>
       </c>
       <c r="O17" s="3">
-        <f>N17/M17</f>
+        <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
       <c r="P17" s="3">
@@ -16442,11 +16551,11 @@
         <v>0</v>
       </c>
       <c r="R17" s="3">
-        <f>I17+L17+P17</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S17" s="3">
-        <f>R17-Q17</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="T17" s="12">
@@ -16460,11 +16569,11 @@
         <v>5.4272999999999998</v>
       </c>
       <c r="W17" s="3">
-        <f>V17-U17</f>
+        <f t="shared" si="4"/>
         <v>7.0699999999999541E-2</v>
       </c>
       <c r="X17" s="12">
-        <f>T17-W17</f>
+        <f t="shared" si="5"/>
         <v>0.4706666666666669</v>
       </c>
       <c r="Y17" s="3" t="s">
@@ -16537,22 +16646,22 @@
         <v>0.47839999999999999</v>
       </c>
       <c r="M18">
-        <f>I18+L18</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N18">
         <v>9.5</v>
       </c>
       <c r="O18">
-        <f>N18/M18</f>
+        <f t="shared" si="1"/>
         <v>0.95</v>
       </c>
       <c r="R18">
-        <f>I18+L18+P18</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S18">
-        <f>R18-N18</f>
+        <f t="shared" ref="S18:S65" si="6">R18-N18</f>
         <v>0.5</v>
       </c>
       <c r="Z18">
@@ -16615,22 +16724,22 @@
         <v>0.4506</v>
       </c>
       <c r="M19">
-        <f>I19+L19</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N19">
         <v>10</v>
       </c>
       <c r="O19">
-        <f>N19/M19</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R19">
-        <f>I19+L19+P19</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S19">
-        <f>R19-N19</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z19">
@@ -16693,22 +16802,22 @@
         <v>0.47849999999999998</v>
       </c>
       <c r="M20">
-        <f>I20+L20</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N20">
         <v>9</v>
       </c>
       <c r="O20">
-        <f>N20/M20</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="R20">
-        <f>I20+L20+P20</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S20">
-        <f>R20-N20</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z20">
@@ -16771,22 +16880,22 @@
         <v>0.4909</v>
       </c>
       <c r="M21">
-        <f>I21+L21</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N21">
         <v>10</v>
       </c>
       <c r="O21">
-        <f>N21/M21</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R21">
-        <f>I21+L21+P21</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S21">
-        <f>R21-N21</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z21">
@@ -16849,22 +16958,22 @@
         <v>0.47770000000000001</v>
       </c>
       <c r="M22">
-        <f>I22+L22</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N22">
         <v>8</v>
       </c>
       <c r="O22">
-        <f>N22/M22</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
       <c r="R22">
-        <f>I22+L22+P22</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S22">
-        <f>R22-N22</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Z22">
@@ -16924,22 +17033,22 @@
         <v>0.47989999999999999</v>
       </c>
       <c r="M23">
-        <f>I23+L23</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N23">
         <v>10</v>
       </c>
       <c r="O23">
-        <f>N23/M23</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R23">
-        <f>I23+L23+P23</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S23">
-        <f>R23-N23</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z23">
@@ -17002,22 +17111,22 @@
         <v>0.46079999999999999</v>
       </c>
       <c r="M24">
-        <f>I24+L24</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N24">
         <v>10</v>
       </c>
       <c r="O24">
-        <f>N24/M24</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R24">
-        <f>I24+L24+P24</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S24">
-        <f>R24-N24</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z24">
@@ -17077,22 +17186,22 @@
         <v>0.46360000000000001</v>
       </c>
       <c r="M25">
-        <f>I25+L25</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N25">
         <v>9.5</v>
       </c>
       <c r="O25">
-        <f>N25/M25</f>
+        <f t="shared" si="1"/>
         <v>0.95</v>
       </c>
       <c r="R25">
-        <f>I25+L25+P25</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S25">
-        <f>R25-N25</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="Z25">
@@ -17155,22 +17264,22 @@
         <v>0.50549999999999995</v>
       </c>
       <c r="M26">
-        <f>I26+L26</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N26">
         <v>10</v>
       </c>
       <c r="O26">
-        <f>N26/M26</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R26">
-        <f>I26+L26+P26</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S26">
-        <f>R26-N26</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z26">
@@ -17233,22 +17342,22 @@
         <v>0.51680000000000004</v>
       </c>
       <c r="M27">
-        <f>I27+L27</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N27">
         <v>10</v>
       </c>
       <c r="O27">
-        <f>N27/M27</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R27">
-        <f>I27+L27+P27</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S27">
-        <f>R27-N27</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z27">
@@ -17308,22 +17417,22 @@
         <v>0.47489999999999999</v>
       </c>
       <c r="M28">
-        <f>I28+L28</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N28">
         <v>10</v>
       </c>
       <c r="O28">
-        <f>N28/M28</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R28">
-        <f>I28+L28+P28</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S28">
-        <f>R28-N28</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z28">
@@ -17386,22 +17495,22 @@
         <v>0.50090000000000001</v>
       </c>
       <c r="M29">
-        <f>I29+L29</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N29">
         <v>10</v>
       </c>
       <c r="O29">
-        <f>N29/M29</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R29">
-        <f>I29+L29+P29</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S29">
-        <f>R29-N29</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z29">
@@ -17464,22 +17573,22 @@
         <v>0.52549999999999997</v>
       </c>
       <c r="M30">
-        <f>I30+L30</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N30">
         <v>10</v>
       </c>
       <c r="O30">
-        <f>N30/M30</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R30">
-        <f>I30+L30+P30</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S30">
-        <f>R30-N30</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z30">
@@ -17539,22 +17648,22 @@
         <v>0.49430000000000002</v>
       </c>
       <c r="M31">
-        <f>I31+L31</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N31">
         <v>10</v>
       </c>
       <c r="O31">
-        <f>N31/M31</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R31">
-        <f>I31+L31+P31</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S31">
-        <f>R31-N31</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z31">
@@ -17614,22 +17723,22 @@
         <v>0.52490000000000003</v>
       </c>
       <c r="M32">
-        <f>I32+L32</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N32">
         <v>10</v>
       </c>
       <c r="O32">
-        <f>N32/M32</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R32">
-        <f>I32+L32+P32</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S32">
-        <f>R32-N32</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z32">
@@ -17689,22 +17798,22 @@
         <v>0.52170000000000005</v>
       </c>
       <c r="M33">
-        <f>I33+L33</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N33">
         <v>9</v>
       </c>
       <c r="O33">
-        <f>N33/M33</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="R33">
-        <f>I33+L33+P33</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S33">
-        <f>R33-N33</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z33">
@@ -17761,22 +17870,22 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <f>I34+L34</f>
+        <f t="shared" ref="M34:M65" si="7">I34+L34</f>
         <v>10</v>
       </c>
       <c r="N34">
         <v>10</v>
       </c>
       <c r="O34">
-        <f>N34/M34</f>
+        <f t="shared" ref="O34:O65" si="8">N34/M34</f>
         <v>1</v>
       </c>
       <c r="R34">
-        <f>I34+L34+P34</f>
+        <f t="shared" ref="R34:R65" si="9">I34+L34+P34</f>
         <v>10</v>
       </c>
       <c r="S34">
-        <f>R34-N34</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z34">
@@ -17836,22 +17945,22 @@
         <v>10</v>
       </c>
       <c r="M35">
-        <f>I35+L35</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N35">
         <v>3.5</v>
       </c>
       <c r="O35">
-        <f>N35/M35</f>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="R35">
-        <f>I35+L35+P35</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S35">
-        <f>R35-N35</f>
+        <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
       <c r="Z35">
@@ -17908,22 +18017,22 @@
         <v>10</v>
       </c>
       <c r="M36">
-        <f>I36+L36</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N36">
         <v>4.5</v>
       </c>
       <c r="O36">
-        <f>N36/M36</f>
+        <f t="shared" si="8"/>
         <v>0.45</v>
       </c>
       <c r="R36">
-        <f>I36+L36+P36</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S36">
-        <f>R36-N36</f>
+        <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
       <c r="Z36">
@@ -17983,22 +18092,22 @@
         <v>10</v>
       </c>
       <c r="M37">
-        <f>I37+L37</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N37">
         <v>7</v>
       </c>
       <c r="O37">
-        <f>N37/M37</f>
+        <f t="shared" si="8"/>
         <v>0.7</v>
       </c>
       <c r="R37">
-        <f>I37+L37+P37</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S37">
-        <f>R37-N37</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="Z37">
@@ -18058,22 +18167,22 @@
         <v>10</v>
       </c>
       <c r="M38">
-        <f>I38+L38</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N38">
         <v>5</v>
       </c>
       <c r="O38">
-        <f>N38/M38</f>
+        <f t="shared" si="8"/>
         <v>0.5</v>
       </c>
       <c r="R38">
-        <f>I38+L38+P38</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S38">
-        <f>R38-N38</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="Z38">
@@ -18130,22 +18239,22 @@
         <v>10</v>
       </c>
       <c r="M39">
-        <f>I39+L39</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N39">
         <v>8</v>
       </c>
       <c r="O39">
-        <f>N39/M39</f>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="R39">
-        <f>I39+L39+P39</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S39">
-        <f>R39-N39</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Z39">
@@ -18202,22 +18311,22 @@
         <v>10</v>
       </c>
       <c r="M40">
-        <f>I40+L40</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N40">
         <v>8</v>
       </c>
       <c r="O40">
-        <f>N40/M40</f>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="R40">
-        <f>I40+L40+P40</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S40">
-        <f>R40-N40</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Z40">
@@ -18274,22 +18383,22 @@
         <v>10</v>
       </c>
       <c r="M41">
-        <f>I41+L41</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N41">
         <v>7</v>
       </c>
       <c r="O41">
-        <f>N41/M41</f>
+        <f t="shared" si="8"/>
         <v>0.7</v>
       </c>
       <c r="R41">
-        <f>I41+L41+P41</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S41">
-        <f>R41-N41</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="Z41">
@@ -18346,22 +18455,22 @@
         <v>10</v>
       </c>
       <c r="M42">
-        <f>I42+L42</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N42">
         <v>9</v>
       </c>
       <c r="O42">
-        <f>N42/M42</f>
+        <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
       <c r="R42">
-        <f>I42+L42+P42</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S42">
-        <f>R42-N42</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z42">
@@ -18421,22 +18530,22 @@
         <v>10</v>
       </c>
       <c r="M43">
-        <f>I43+L43</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N43">
         <v>9</v>
       </c>
       <c r="O43">
-        <f>N43/M43</f>
+        <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
       <c r="R43">
-        <f>I43+L43+P43</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S43">
-        <f>R43-N43</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z43">
@@ -18493,22 +18602,22 @@
         <v>10</v>
       </c>
       <c r="M44">
-        <f>I44+L44</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N44">
         <v>10</v>
       </c>
       <c r="O44">
-        <f>N44/M44</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="R44">
-        <f>I44+L44+P44</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S44">
-        <f>R44-N44</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z44">
@@ -18565,22 +18674,22 @@
         <v>10</v>
       </c>
       <c r="M45">
-        <f>I45+L45</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N45">
         <v>5</v>
       </c>
       <c r="O45">
-        <f>N45/M45</f>
+        <f t="shared" si="8"/>
         <v>0.5</v>
       </c>
       <c r="R45">
-        <f>I45+L45+P45</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S45">
-        <f>R45-N45</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="Z45">
@@ -18637,22 +18746,22 @@
         <v>10</v>
       </c>
       <c r="M46">
-        <f>I46+L46</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N46">
         <v>7</v>
       </c>
       <c r="O46">
-        <f>N46/M46</f>
+        <f t="shared" si="8"/>
         <v>0.7</v>
       </c>
       <c r="R46">
-        <f>I46+L46+P46</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S46">
-        <f>R46-N46</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="Z46">
@@ -18712,22 +18821,22 @@
         <v>10</v>
       </c>
       <c r="M47">
-        <f>I47+L47</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N47">
         <v>9</v>
       </c>
       <c r="O47">
-        <f>N47/M47</f>
+        <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
       <c r="R47">
-        <f>I47+L47+P47</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S47">
-        <f>R47-N47</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z47">
@@ -18787,22 +18896,22 @@
         <v>10</v>
       </c>
       <c r="M48">
-        <f>I48+L48</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N48">
         <v>5</v>
       </c>
       <c r="O48">
-        <f>N48/M48</f>
+        <f t="shared" si="8"/>
         <v>0.5</v>
       </c>
       <c r="R48">
-        <f>I48+L48+P48</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S48">
-        <f>R48-N48</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="Z48">
@@ -18859,22 +18968,22 @@
         <v>10</v>
       </c>
       <c r="M49">
-        <f>I49+L49</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N49">
         <v>10</v>
       </c>
       <c r="O49">
-        <f>N49/M49</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="R49">
-        <f>I49+L49+P49</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S49">
-        <f>R49-N49</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z49">
@@ -18940,22 +19049,22 @@
         <v>10</v>
       </c>
       <c r="M50">
-        <f>I50+L50</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N50">
         <v>9.5</v>
       </c>
       <c r="O50">
-        <f>N50/M50</f>
+        <f t="shared" si="8"/>
         <v>0.95</v>
       </c>
       <c r="R50">
-        <f>I50+L50+P50</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S50">
-        <f>R50-N50</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="Z50">
@@ -19015,22 +19124,22 @@
         <v>10</v>
       </c>
       <c r="M51">
-        <f>I51+L51</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N51">
         <v>6.5</v>
       </c>
       <c r="O51">
-        <f>N51/M51</f>
+        <f t="shared" si="8"/>
         <v>0.65</v>
       </c>
       <c r="R51">
-        <f>I51+L51+P51</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S51">
-        <f>R51-N51</f>
+        <f t="shared" si="6"/>
         <v>3.5</v>
       </c>
       <c r="Z51">
@@ -19090,22 +19199,22 @@
         <v>10</v>
       </c>
       <c r="M52">
-        <f>I52+L52</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N52">
         <v>8.5</v>
       </c>
       <c r="O52">
-        <f>N52/M52</f>
+        <f t="shared" si="8"/>
         <v>0.85</v>
       </c>
       <c r="R52">
-        <f>I52+L52+P52</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S52">
-        <f>R52-N52</f>
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
       <c r="Z52">
@@ -19165,22 +19274,22 @@
         <v>10</v>
       </c>
       <c r="M53">
-        <f>I53+L53</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N53">
         <v>8.5</v>
       </c>
       <c r="O53">
-        <f>N53/M53</f>
+        <f t="shared" si="8"/>
         <v>0.85</v>
       </c>
       <c r="R53">
-        <f>I53+L53+P53</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S53">
-        <f>R53-N53</f>
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
       <c r="Z53">
@@ -19240,22 +19349,22 @@
         <v>10</v>
       </c>
       <c r="M54">
-        <f>I54+L54</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N54">
         <v>9</v>
       </c>
       <c r="O54">
-        <f>N54/M54</f>
+        <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
       <c r="R54">
-        <f>I54+L54+P54</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S54">
-        <f>R54-N54</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z54">
@@ -19312,22 +19421,22 @@
         <v>10</v>
       </c>
       <c r="M55">
-        <f>I55+L55</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N55">
         <v>9</v>
       </c>
       <c r="O55">
-        <f>N55/M55</f>
+        <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
       <c r="R55">
-        <f>I55+L55+P55</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S55">
-        <f>R55-N55</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z55">
@@ -19387,22 +19496,22 @@
         <v>10</v>
       </c>
       <c r="M56">
-        <f>I56+L56</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N56">
         <v>10</v>
       </c>
       <c r="O56">
-        <f>N56/M56</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="R56">
-        <f>I56+L56+P56</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S56">
-        <f>R56-N56</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z56">
@@ -19462,22 +19571,22 @@
         <v>10</v>
       </c>
       <c r="M57">
-        <f>I57+L57</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N57">
         <v>8.5</v>
       </c>
       <c r="O57">
-        <f>N57/M57</f>
+        <f t="shared" si="8"/>
         <v>0.85</v>
       </c>
       <c r="R57">
-        <f>I57+L57+P57</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S57">
-        <f>R57-N57</f>
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
       <c r="Z57">
@@ -19534,22 +19643,22 @@
         <v>10</v>
       </c>
       <c r="M58">
-        <f>I58+L58</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N58">
         <v>10</v>
       </c>
       <c r="O58">
-        <f>N58/M58</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="R58">
-        <f>I58+L58+P58</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S58">
-        <f>R58-N58</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z58">
@@ -19609,22 +19718,22 @@
         <v>10</v>
       </c>
       <c r="M59">
-        <f>I59+L59</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N59">
         <v>1</v>
       </c>
       <c r="O59">
-        <f>N59/M59</f>
+        <f t="shared" si="8"/>
         <v>0.1</v>
       </c>
       <c r="R59">
-        <f>I59+L59+P59</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S59">
-        <f>R59-N59</f>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="Z59">
@@ -19684,22 +19793,22 @@
         <v>10</v>
       </c>
       <c r="M60">
-        <f>I60+L60</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N60">
         <v>9.5</v>
       </c>
       <c r="O60">
-        <f>N60/M60</f>
+        <f t="shared" si="8"/>
         <v>0.95</v>
       </c>
       <c r="R60">
-        <f>I60+L60+P60</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S60">
-        <f>R60-N60</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="Z60">
@@ -19756,22 +19865,22 @@
         <v>10</v>
       </c>
       <c r="M61">
-        <f>I61+L61</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N61">
         <v>9</v>
       </c>
       <c r="O61">
-        <f>N61/M61</f>
+        <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
       <c r="R61">
-        <f>I61+L61+P61</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S61">
-        <f>R61-N61</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z61">
@@ -19831,22 +19940,22 @@
         <v>10</v>
       </c>
       <c r="M62">
-        <f>I62+L62</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N62">
         <v>8</v>
       </c>
       <c r="O62">
-        <f>N62/M62</f>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="R62">
-        <f>I62+L62+P62</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S62">
-        <f>R62-N62</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Z62">
@@ -19903,22 +20012,22 @@
         <v>10</v>
       </c>
       <c r="M63">
-        <f>I63+L63</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N63">
         <v>9.5</v>
       </c>
       <c r="O63">
-        <f>N63/M63</f>
+        <f t="shared" si="8"/>
         <v>0.95</v>
       </c>
       <c r="R63">
-        <f>I63+L63+P63</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S63">
-        <f>R63-N63</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="Z63">
@@ -19978,22 +20087,22 @@
         <v>10</v>
       </c>
       <c r="M64">
-        <f>I64+L64</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N64">
         <v>10</v>
       </c>
       <c r="O64">
-        <f>N64/M64</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="R64">
-        <f>I64+L64+P64</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S64">
-        <f>R64-N64</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z64">
@@ -20053,22 +20162,22 @@
         <v>10</v>
       </c>
       <c r="M65">
-        <f>I65+L65</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N65">
         <v>8</v>
       </c>
       <c r="O65">
-        <f>N65/M65</f>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="R65">
-        <f>I65+L65+P65</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S65">
-        <f>R65-N65</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Z65">
@@ -20102,7 +20211,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BBCDD3C-BFC6-4E05-889C-A3C43CAF9042}">
   <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -20489,7 +20598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B60B41AF-8105-4C18-8106-47C7D54E511E}">
   <dimension ref="A1:AO66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -20665,14 +20774,14 @@
         <v>5</v>
       </c>
       <c r="M2" s="3">
-        <f>I2+L2</f>
+        <f t="shared" ref="M2:M33" si="0">I2+L2</f>
         <v>10</v>
       </c>
       <c r="N2" s="3">
         <v>7</v>
       </c>
       <c r="O2" s="3">
-        <f>N2/M2</f>
+        <f t="shared" ref="O2:O33" si="1">N2/M2</f>
         <v>0.7</v>
       </c>
       <c r="P2" s="3">
@@ -20682,11 +20791,11 @@
         <v>2</v>
       </c>
       <c r="R2" s="3">
-        <f>I2+L2+P2</f>
+        <f t="shared" ref="R2:R33" si="2">I2+L2+P2</f>
         <v>10</v>
       </c>
       <c r="S2" s="3">
-        <f>R2-Q2</f>
+        <f t="shared" ref="S2:S17" si="3">R2-Q2</f>
         <v>8</v>
       </c>
       <c r="T2" s="12">
@@ -20700,11 +20809,11 @@
         <v>5.3324999999999996</v>
       </c>
       <c r="W2" s="3">
-        <f>V2-U2</f>
+        <f t="shared" ref="W2:W17" si="4">V2-U2</f>
         <v>1.9899999999999807E-2</v>
       </c>
       <c r="X2" s="12">
-        <f>T2-W2</f>
+        <f t="shared" ref="X2:X17" si="5">T2-W2</f>
         <v>0.52146666666666663</v>
       </c>
       <c r="Y2" s="3" t="s">
@@ -20773,14 +20882,14 @@
         <v>0</v>
       </c>
       <c r="M3" s="3">
-        <f>I3+L3</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N3" s="3">
         <v>5</v>
       </c>
       <c r="O3" s="3">
-        <f>N3/M3</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="P3" s="3">
@@ -20790,11 +20899,11 @@
         <v>4.5</v>
       </c>
       <c r="R3" s="3">
-        <f>I3+L3+P3</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="S3" s="3">
-        <f>R3-Q3</f>
+        <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
       <c r="T3" s="12">
@@ -20808,11 +20917,11 @@
         <v>5.3487999999999998</v>
       </c>
       <c r="W3" s="3">
-        <f>V3-U3</f>
+        <f t="shared" si="4"/>
         <v>4.3499999999999872E-2</v>
       </c>
       <c r="X3" s="12">
-        <f>T3-W3</f>
+        <f t="shared" si="5"/>
         <v>0.22718333333333335</v>
       </c>
       <c r="Y3" s="3" t="s">
@@ -20881,14 +20990,14 @@
         <v>5</v>
       </c>
       <c r="M4" s="3">
-        <f>I4+L4</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N4" s="3">
         <v>1</v>
       </c>
       <c r="O4" s="3">
-        <f>N4/M4</f>
+        <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
       <c r="P4" s="3">
@@ -20898,11 +21007,11 @@
         <v>4.5</v>
       </c>
       <c r="R4" s="3">
-        <f>I4+L4+P4</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="S4" s="3">
-        <f>R4-Q4</f>
+        <f t="shared" si="3"/>
         <v>10.5</v>
       </c>
       <c r="T4" s="12">
@@ -20916,11 +21025,11 @@
         <v>5.4924999999999997</v>
       </c>
       <c r="W4" s="3">
-        <f>V4-U4</f>
+        <f t="shared" si="4"/>
         <v>0.19029999999999969</v>
       </c>
       <c r="X4" s="12">
-        <f>T4-W4</f>
+        <f t="shared" si="5"/>
         <v>0.62175000000000002</v>
       </c>
       <c r="Y4" s="3" t="s">
@@ -20989,14 +21098,14 @@
         <v>0</v>
       </c>
       <c r="M5" s="3">
-        <f>I5+L5</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N5" s="3">
         <v>4</v>
       </c>
       <c r="O5" s="3">
-        <f>N5/M5</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
       <c r="P5" s="3">
@@ -21006,11 +21115,11 @@
         <v>0</v>
       </c>
       <c r="R5" s="3">
-        <f>I5+L5+P5</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="S5" s="3">
-        <f>R5-Q5</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="T5" s="12">
@@ -21024,11 +21133,11 @@
         <v>5.3719000000000001</v>
       </c>
       <c r="W5" s="3">
-        <f>V5-U5</f>
+        <f t="shared" si="4"/>
         <v>4.750000000000032E-2</v>
       </c>
       <c r="X5" s="12">
-        <f>T5-W5</f>
+        <f t="shared" si="5"/>
         <v>0.2231833333333329</v>
       </c>
       <c r="Y5" s="3" t="s">
@@ -21097,14 +21206,14 @@
         <v>0</v>
       </c>
       <c r="M6" s="3">
-        <f>I6+L6</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N6" s="3">
         <v>4.5</v>
       </c>
       <c r="O6" s="3">
-        <f>N6/M6</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="P6" s="3">
@@ -21114,11 +21223,11 @@
         <v>0.5</v>
       </c>
       <c r="R6" s="3">
-        <f>I6+L6+P6</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="S6" s="3">
-        <f>R6-Q6</f>
+        <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
       <c r="T6" s="12">
@@ -21132,11 +21241,11 @@
         <v>5.3333000000000004</v>
       </c>
       <c r="W6" s="3">
-        <f>V6-U6</f>
+        <f t="shared" si="4"/>
         <v>2.8700000000000614E-2</v>
       </c>
       <c r="X6" s="12">
-        <f>T6-W6</f>
+        <f t="shared" si="5"/>
         <v>0.24198333333333261</v>
       </c>
       <c r="Y6" s="3" t="s">
@@ -21202,14 +21311,14 @@
         <v>5</v>
       </c>
       <c r="M7" s="3">
-        <f>I7+L7</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N7" s="3">
         <v>5</v>
       </c>
       <c r="O7" s="3">
-        <f>N7/M7</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="P7" s="3">
@@ -21219,11 +21328,11 @@
         <v>5</v>
       </c>
       <c r="R7" s="3">
-        <f>I7+L7+P7</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S7" s="3">
-        <f>R7-Q7</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="T7" s="12">
@@ -21237,11 +21346,11 @@
         <v>5.4973000000000001</v>
       </c>
       <c r="W7" s="3">
-        <f>V7-U7</f>
+        <f t="shared" si="4"/>
         <v>0.14839999999999964</v>
       </c>
       <c r="X7" s="12">
-        <f>T7-W7</f>
+        <f t="shared" si="5"/>
         <v>0.3929666666666668</v>
       </c>
       <c r="Y7" s="3" t="s">
@@ -21307,14 +21416,14 @@
         <v>5</v>
       </c>
       <c r="M8" s="3">
-        <f>I8+L8</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N8" s="3">
         <v>2.5</v>
       </c>
       <c r="O8" s="3">
-        <f>N8/M8</f>
+        <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
       <c r="P8" s="3">
@@ -21324,11 +21433,11 @@
         <v>5</v>
       </c>
       <c r="R8" s="3">
-        <f>I8+L8+P8</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="S8" s="3">
-        <f>R8-Q8</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="T8" s="12">
@@ -21342,11 +21451,11 @@
         <v>5.5107999999999997</v>
       </c>
       <c r="W8" s="3">
-        <f>V8-U8</f>
+        <f t="shared" si="4"/>
         <v>0.1888999999999994</v>
       </c>
       <c r="X8" s="12">
-        <f>T8-W8</f>
+        <f t="shared" si="5"/>
         <v>0.62315000000000031</v>
       </c>
       <c r="Y8" s="3" t="s">
@@ -21415,14 +21524,14 @@
         <v>5</v>
       </c>
       <c r="M9" s="3">
-        <f>I9+L9</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N9" s="3">
         <v>7</v>
       </c>
       <c r="O9" s="3">
-        <f>N9/M9</f>
+        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
       <c r="P9" s="3">
@@ -21432,11 +21541,11 @@
         <v>6</v>
       </c>
       <c r="R9" s="3">
-        <f>I9+L9+P9</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S9" s="3">
-        <f>R9-Q9</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="T9" s="12">
@@ -21450,11 +21559,11 @@
         <v>5.4987000000000004</v>
       </c>
       <c r="W9" s="3">
-        <f>V9-U9</f>
+        <f t="shared" si="4"/>
         <v>0.15700000000000003</v>
       </c>
       <c r="X9" s="12">
-        <f>T9-W9</f>
+        <f t="shared" si="5"/>
         <v>0.38436666666666641</v>
       </c>
       <c r="Y9" s="3" t="s">
@@ -21520,14 +21629,14 @@
         <v>0</v>
       </c>
       <c r="M10" s="3">
-        <f>I10+L10</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N10" s="3">
         <v>0</v>
       </c>
       <c r="O10" s="3">
-        <f>N10/M10</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P10" s="3">
@@ -21537,11 +21646,11 @@
         <v>0</v>
       </c>
       <c r="R10" s="3">
-        <f>I10+L10+P10</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S10" s="3">
-        <f>R10-Q10</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="T10" s="12">
@@ -21555,11 +21664,11 @@
         <v>5.3574000000000002</v>
       </c>
       <c r="W10" s="3">
-        <f>V10-U10</f>
+        <f t="shared" si="4"/>
         <v>2.3200000000000109E-2</v>
       </c>
       <c r="X10" s="12">
-        <f>T10-W10</f>
+        <f t="shared" si="5"/>
         <v>0.51816666666666633</v>
       </c>
       <c r="Y10" s="3" t="s">
@@ -21628,14 +21737,14 @@
         <v>5</v>
       </c>
       <c r="M11" s="3">
-        <f>I11+L11</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N11" s="3">
         <v>5</v>
       </c>
       <c r="O11" s="3">
-        <f>N11/M11</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="P11" s="3">
@@ -21645,11 +21754,11 @@
         <v>2</v>
       </c>
       <c r="R11" s="3">
-        <f>I11+L11+P11</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S11" s="3">
-        <f>R11-Q11</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="T11" s="12">
@@ -21663,11 +21772,11 @@
         <v>5.3703000000000003</v>
       </c>
       <c r="W11" s="3">
-        <f>V11-U11</f>
+        <f t="shared" si="4"/>
         <v>8.8000000000000078E-2</v>
       </c>
       <c r="X11" s="12">
-        <f>T11-W11</f>
+        <f t="shared" si="5"/>
         <v>0.45336666666666636</v>
       </c>
       <c r="Y11" s="3" t="s">
@@ -21736,14 +21845,14 @@
         <v>0</v>
       </c>
       <c r="M12" s="3">
-        <f>I12+L12</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N12" s="3">
         <v>5</v>
       </c>
       <c r="O12" s="3">
-        <f>N12/M12</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="P12" s="3">
@@ -21753,11 +21862,11 @@
         <v>2.5</v>
       </c>
       <c r="R12" s="3">
-        <f>I12+L12+P12</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="S12" s="3">
-        <f>R12-Q12</f>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="T12" s="12">
@@ -21771,11 +21880,11 @@
         <v>5.4090999999999996</v>
       </c>
       <c r="W12" s="3">
-        <f>V12-U12</f>
+        <f t="shared" si="4"/>
         <v>3.2199999999999562E-2</v>
       </c>
       <c r="X12" s="12">
-        <f>T12-W12</f>
+        <f t="shared" si="5"/>
         <v>0.23848333333333366</v>
       </c>
       <c r="Y12" s="3" t="s">
@@ -21844,14 +21953,14 @@
         <v>5</v>
       </c>
       <c r="M13" s="3">
-        <f>I13+L13</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N13" s="3">
         <v>7</v>
       </c>
       <c r="O13" s="3">
-        <f>N13/M13</f>
+        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
       <c r="P13" s="3">
@@ -21861,11 +21970,11 @@
         <v>1</v>
       </c>
       <c r="R13" s="3">
-        <f>I13+L13+P13</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S13" s="3">
-        <f>R13-Q13</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="T13" s="12">
@@ -21879,11 +21988,11 @@
         <v>5.3334999999999999</v>
       </c>
       <c r="W13" s="3">
-        <f>V13-U13</f>
+        <f t="shared" si="4"/>
         <v>6.8399999999999572E-2</v>
       </c>
       <c r="X13" s="12">
-        <f>T13-W13</f>
+        <f t="shared" si="5"/>
         <v>0.47296666666666687</v>
       </c>
       <c r="Y13" s="3" t="s">
@@ -21952,14 +22061,14 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
-        <f>I14+L14</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>5</v>
       </c>
       <c r="O14" s="3">
-        <f>N14/M14</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="P14" s="3">
@@ -21969,11 +22078,11 @@
         <v>0.5</v>
       </c>
       <c r="R14" s="3">
-        <f>I14+L14+P14</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="S14" s="3">
-        <f>R14-Q14</f>
+        <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
       <c r="T14" s="12">
@@ -21987,11 +22096,11 @@
         <v>5.3845999999999998</v>
       </c>
       <c r="W14" s="3">
-        <f>V14-U14</f>
+        <f t="shared" si="4"/>
         <v>4.3800000000000061E-2</v>
       </c>
       <c r="X14" s="12">
-        <f>T14-W14</f>
+        <f t="shared" si="5"/>
         <v>0.22688333333333316</v>
       </c>
       <c r="Y14" s="3" t="s">
@@ -22060,14 +22169,14 @@
         <v>0</v>
       </c>
       <c r="M15" s="3">
-        <f>I15+L15</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="N15" s="3">
         <v>5</v>
       </c>
       <c r="O15" s="3">
-        <f>N15/M15</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="P15" s="3">
@@ -22077,11 +22186,11 @@
         <v>0.5</v>
       </c>
       <c r="R15" s="3">
-        <f>I15+L15+P15</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="S15" s="3">
-        <f>R15-Q15</f>
+        <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
       <c r="T15" s="12">
@@ -22095,11 +22204,11 @@
         <v>5.3742999999999999</v>
       </c>
       <c r="W15" s="3">
-        <f>V15-U15</f>
+        <f t="shared" si="4"/>
         <v>3.9299999999999891E-2</v>
       </c>
       <c r="X15" s="12">
-        <f>T15-W15</f>
+        <f t="shared" si="5"/>
         <v>0.23138333333333333</v>
       </c>
       <c r="Y15" s="3" t="s">
@@ -22189,14 +22298,14 @@
         <v>5</v>
       </c>
       <c r="M16" s="3">
-        <f>I16+L16</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N16" s="3">
         <v>7</v>
       </c>
       <c r="O16" s="3">
-        <f>N16/M16</f>
+        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
       <c r="P16" s="3">
@@ -22206,11 +22315,11 @@
         <v>1</v>
       </c>
       <c r="R16" s="3">
-        <f>I16+L16+P16</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S16" s="3">
-        <f>R16-Q16</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="T16" s="12">
@@ -22224,11 +22333,11 @@
         <v>5.5160999999999998</v>
       </c>
       <c r="W16" s="3">
-        <f>V16-U16</f>
+        <f t="shared" si="4"/>
         <v>0.12549999999999972</v>
       </c>
       <c r="X16" s="12">
-        <f>T16-W16</f>
+        <f t="shared" si="5"/>
         <v>0.41586666666666672</v>
       </c>
       <c r="Y16" s="3" t="s">
@@ -22294,14 +22403,14 @@
         <v>5</v>
       </c>
       <c r="M17" s="3">
-        <f>I17+L17</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N17" s="3">
         <v>6</v>
       </c>
       <c r="O17" s="3">
-        <f>N17/M17</f>
+        <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
       <c r="P17" s="3">
@@ -22311,11 +22420,11 @@
         <v>0</v>
       </c>
       <c r="R17" s="3">
-        <f>I17+L17+P17</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S17" s="3">
-        <f>R17-Q17</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="T17" s="12">
@@ -22329,11 +22438,11 @@
         <v>5.4272999999999998</v>
       </c>
       <c r="W17" s="3">
-        <f>V17-U17</f>
+        <f t="shared" si="4"/>
         <v>7.0699999999999541E-2</v>
       </c>
       <c r="X17" s="12">
-        <f>T17-W17</f>
+        <f t="shared" si="5"/>
         <v>0.4706666666666669</v>
       </c>
       <c r="Y17" s="3" t="s">
@@ -22400,22 +22509,22 @@
         <v>0.47839999999999999</v>
       </c>
       <c r="M18">
-        <f>I18+L18</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N18">
         <v>9.5</v>
       </c>
       <c r="O18">
-        <f>N18/M18</f>
+        <f t="shared" si="1"/>
         <v>0.95</v>
       </c>
       <c r="R18">
-        <f>I18+L18+P18</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S18">
-        <f>R18-N18</f>
+        <f t="shared" ref="S18:S65" si="6">R18-N18</f>
         <v>0.5</v>
       </c>
       <c r="Z18">
@@ -22478,22 +22587,22 @@
         <v>0.4506</v>
       </c>
       <c r="M19">
-        <f>I19+L19</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N19">
         <v>10</v>
       </c>
       <c r="O19">
-        <f>N19/M19</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R19">
-        <f>I19+L19+P19</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S19">
-        <f>R19-N19</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z19">
@@ -22556,22 +22665,22 @@
         <v>0.47849999999999998</v>
       </c>
       <c r="M20">
-        <f>I20+L20</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N20">
         <v>9</v>
       </c>
       <c r="O20">
-        <f>N20/M20</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="R20">
-        <f>I20+L20+P20</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S20">
-        <f>R20-N20</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z20">
@@ -22634,22 +22743,22 @@
         <v>0.4909</v>
       </c>
       <c r="M21">
-        <f>I21+L21</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N21">
         <v>10</v>
       </c>
       <c r="O21">
-        <f>N21/M21</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R21">
-        <f>I21+L21+P21</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S21">
-        <f>R21-N21</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z21">
@@ -22712,22 +22821,22 @@
         <v>0.47770000000000001</v>
       </c>
       <c r="M22">
-        <f>I22+L22</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N22">
         <v>8</v>
       </c>
       <c r="O22">
-        <f>N22/M22</f>
+        <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
       <c r="R22">
-        <f>I22+L22+P22</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S22">
-        <f>R22-N22</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Z22">
@@ -22787,22 +22896,22 @@
         <v>0.47989999999999999</v>
       </c>
       <c r="M23">
-        <f>I23+L23</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N23">
         <v>10</v>
       </c>
       <c r="O23">
-        <f>N23/M23</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R23">
-        <f>I23+L23+P23</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S23">
-        <f>R23-N23</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z23">
@@ -22865,22 +22974,22 @@
         <v>0.46079999999999999</v>
       </c>
       <c r="M24">
-        <f>I24+L24</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N24">
         <v>10</v>
       </c>
       <c r="O24">
-        <f>N24/M24</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R24">
-        <f>I24+L24+P24</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S24">
-        <f>R24-N24</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z24">
@@ -22940,22 +23049,22 @@
         <v>0.46360000000000001</v>
       </c>
       <c r="M25">
-        <f>I25+L25</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N25">
         <v>9.5</v>
       </c>
       <c r="O25">
-        <f>N25/M25</f>
+        <f t="shared" si="1"/>
         <v>0.95</v>
       </c>
       <c r="R25">
-        <f>I25+L25+P25</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S25">
-        <f>R25-N25</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="Z25">
@@ -23018,22 +23127,22 @@
         <v>0.50549999999999995</v>
       </c>
       <c r="M26">
-        <f>I26+L26</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N26">
         <v>10</v>
       </c>
       <c r="O26">
-        <f>N26/M26</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R26">
-        <f>I26+L26+P26</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S26">
-        <f>R26-N26</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z26">
@@ -23096,22 +23205,22 @@
         <v>0.51680000000000004</v>
       </c>
       <c r="M27">
-        <f>I27+L27</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N27">
         <v>10</v>
       </c>
       <c r="O27">
-        <f>N27/M27</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R27">
-        <f>I27+L27+P27</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S27">
-        <f>R27-N27</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z27">
@@ -23171,22 +23280,22 @@
         <v>0.47489999999999999</v>
       </c>
       <c r="M28">
-        <f>I28+L28</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N28">
         <v>10</v>
       </c>
       <c r="O28">
-        <f>N28/M28</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R28">
-        <f>I28+L28+P28</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S28">
-        <f>R28-N28</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z28">
@@ -23249,22 +23358,22 @@
         <v>0.50090000000000001</v>
       </c>
       <c r="M29">
-        <f>I29+L29</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N29">
         <v>10</v>
       </c>
       <c r="O29">
-        <f>N29/M29</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R29">
-        <f>I29+L29+P29</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S29">
-        <f>R29-N29</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z29">
@@ -23327,22 +23436,22 @@
         <v>0.52549999999999997</v>
       </c>
       <c r="M30">
-        <f>I30+L30</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N30">
         <v>10</v>
       </c>
       <c r="O30">
-        <f>N30/M30</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R30">
-        <f>I30+L30+P30</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S30">
-        <f>R30-N30</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z30">
@@ -23402,22 +23511,22 @@
         <v>0.49430000000000002</v>
       </c>
       <c r="M31">
-        <f>I31+L31</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N31">
         <v>10</v>
       </c>
       <c r="O31">
-        <f>N31/M31</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R31">
-        <f>I31+L31+P31</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S31">
-        <f>R31-N31</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z31">
@@ -23477,22 +23586,22 @@
         <v>0.52490000000000003</v>
       </c>
       <c r="M32">
-        <f>I32+L32</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N32">
         <v>10</v>
       </c>
       <c r="O32">
-        <f>N32/M32</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R32">
-        <f>I32+L32+P32</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S32">
-        <f>R32-N32</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z32">
@@ -23552,22 +23661,22 @@
         <v>0.52170000000000005</v>
       </c>
       <c r="M33">
-        <f>I33+L33</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="N33">
         <v>9</v>
       </c>
       <c r="O33">
-        <f>N33/M33</f>
+        <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
       <c r="R33">
-        <f>I33+L33+P33</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="S33">
-        <f>R33-N33</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z33">
@@ -23618,22 +23727,22 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <f>I34+L34</f>
+        <f t="shared" ref="M34:M65" si="7">I34+L34</f>
         <v>10</v>
       </c>
       <c r="N34">
         <v>10</v>
       </c>
       <c r="O34">
-        <f>N34/M34</f>
+        <f t="shared" ref="O34:O65" si="8">N34/M34</f>
         <v>1</v>
       </c>
       <c r="R34">
-        <f>I34+L34+P34</f>
+        <f t="shared" ref="R34:R65" si="9">I34+L34+P34</f>
         <v>10</v>
       </c>
       <c r="S34">
-        <f>R34-N34</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z34">
@@ -23687,22 +23796,22 @@
         <v>10</v>
       </c>
       <c r="M35">
-        <f>I35+L35</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N35">
         <v>3.5</v>
       </c>
       <c r="O35">
-        <f>N35/M35</f>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="R35">
-        <f>I35+L35+P35</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S35">
-        <f>R35-N35</f>
+        <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
       <c r="Z35">
@@ -23753,22 +23862,22 @@
         <v>10</v>
       </c>
       <c r="M36">
-        <f>I36+L36</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N36">
         <v>4.5</v>
       </c>
       <c r="O36">
-        <f>N36/M36</f>
+        <f t="shared" si="8"/>
         <v>0.45</v>
       </c>
       <c r="R36">
-        <f>I36+L36+P36</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S36">
-        <f>R36-N36</f>
+        <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
       <c r="Z36">
@@ -23822,22 +23931,22 @@
         <v>10</v>
       </c>
       <c r="M37">
-        <f>I37+L37</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N37">
         <v>7</v>
       </c>
       <c r="O37">
-        <f>N37/M37</f>
+        <f t="shared" si="8"/>
         <v>0.7</v>
       </c>
       <c r="R37">
-        <f>I37+L37+P37</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S37">
-        <f>R37-N37</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="Z37">
@@ -23891,22 +24000,22 @@
         <v>10</v>
       </c>
       <c r="M38">
-        <f>I38+L38</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N38">
         <v>5</v>
       </c>
       <c r="O38">
-        <f>N38/M38</f>
+        <f t="shared" si="8"/>
         <v>0.5</v>
       </c>
       <c r="R38">
-        <f>I38+L38+P38</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S38">
-        <f>R38-N38</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="Z38">
@@ -23957,22 +24066,22 @@
         <v>10</v>
       </c>
       <c r="M39">
-        <f>I39+L39</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N39">
         <v>8</v>
       </c>
       <c r="O39">
-        <f>N39/M39</f>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="R39">
-        <f>I39+L39+P39</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S39">
-        <f>R39-N39</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Z39">
@@ -24023,22 +24132,22 @@
         <v>10</v>
       </c>
       <c r="M40">
-        <f>I40+L40</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N40">
         <v>8</v>
       </c>
       <c r="O40">
-        <f>N40/M40</f>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="R40">
-        <f>I40+L40+P40</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S40">
-        <f>R40-N40</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Z40">
@@ -24089,22 +24198,22 @@
         <v>10</v>
       </c>
       <c r="M41">
-        <f>I41+L41</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N41">
         <v>7</v>
       </c>
       <c r="O41">
-        <f>N41/M41</f>
+        <f t="shared" si="8"/>
         <v>0.7</v>
       </c>
       <c r="R41">
-        <f>I41+L41+P41</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S41">
-        <f>R41-N41</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="Z41">
@@ -24155,22 +24264,22 @@
         <v>10</v>
       </c>
       <c r="M42">
-        <f>I42+L42</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N42">
         <v>9</v>
       </c>
       <c r="O42">
-        <f>N42/M42</f>
+        <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
       <c r="R42">
-        <f>I42+L42+P42</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S42">
-        <f>R42-N42</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z42">
@@ -24224,22 +24333,22 @@
         <v>10</v>
       </c>
       <c r="M43">
-        <f>I43+L43</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N43">
         <v>9</v>
       </c>
       <c r="O43">
-        <f>N43/M43</f>
+        <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
       <c r="R43">
-        <f>I43+L43+P43</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S43">
-        <f>R43-N43</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z43">
@@ -24290,22 +24399,22 @@
         <v>10</v>
       </c>
       <c r="M44">
-        <f>I44+L44</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N44">
         <v>10</v>
       </c>
       <c r="O44">
-        <f>N44/M44</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="R44">
-        <f>I44+L44+P44</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S44">
-        <f>R44-N44</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z44">
@@ -24356,22 +24465,22 @@
         <v>10</v>
       </c>
       <c r="M45">
-        <f>I45+L45</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N45">
         <v>5</v>
       </c>
       <c r="O45">
-        <f>N45/M45</f>
+        <f t="shared" si="8"/>
         <v>0.5</v>
       </c>
       <c r="R45">
-        <f>I45+L45+P45</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S45">
-        <f>R45-N45</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="Z45">
@@ -24422,22 +24531,22 @@
         <v>10</v>
       </c>
       <c r="M46">
-        <f>I46+L46</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N46">
         <v>7</v>
       </c>
       <c r="O46">
-        <f>N46/M46</f>
+        <f t="shared" si="8"/>
         <v>0.7</v>
       </c>
       <c r="R46">
-        <f>I46+L46+P46</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S46">
-        <f>R46-N46</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="Z46">
@@ -24491,22 +24600,22 @@
         <v>10</v>
       </c>
       <c r="M47">
-        <f>I47+L47</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N47">
         <v>9</v>
       </c>
       <c r="O47">
-        <f>N47/M47</f>
+        <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
       <c r="R47">
-        <f>I47+L47+P47</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S47">
-        <f>R47-N47</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z47">
@@ -24560,22 +24669,22 @@
         <v>10</v>
       </c>
       <c r="M48">
-        <f>I48+L48</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N48">
         <v>5</v>
       </c>
       <c r="O48">
-        <f>N48/M48</f>
+        <f t="shared" si="8"/>
         <v>0.5</v>
       </c>
       <c r="R48">
-        <f>I48+L48+P48</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S48">
-        <f>R48-N48</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="Z48">
@@ -24626,22 +24735,22 @@
         <v>10</v>
       </c>
       <c r="M49">
-        <f>I49+L49</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N49">
         <v>10</v>
       </c>
       <c r="O49">
-        <f>N49/M49</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="R49">
-        <f>I49+L49+P49</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S49">
-        <f>R49-N49</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z49">
@@ -24701,22 +24810,22 @@
         <v>10</v>
       </c>
       <c r="M50">
-        <f>I50+L50</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N50">
         <v>9.5</v>
       </c>
       <c r="O50">
-        <f>N50/M50</f>
+        <f t="shared" si="8"/>
         <v>0.95</v>
       </c>
       <c r="R50">
-        <f>I50+L50+P50</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S50">
-        <f>R50-N50</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="Z50">
@@ -24770,22 +24879,22 @@
         <v>10</v>
       </c>
       <c r="M51">
-        <f>I51+L51</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N51">
         <v>6.5</v>
       </c>
       <c r="O51">
-        <f>N51/M51</f>
+        <f t="shared" si="8"/>
         <v>0.65</v>
       </c>
       <c r="R51">
-        <f>I51+L51+P51</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S51">
-        <f>R51-N51</f>
+        <f t="shared" si="6"/>
         <v>3.5</v>
       </c>
       <c r="Z51">
@@ -24839,22 +24948,22 @@
         <v>10</v>
       </c>
       <c r="M52">
-        <f>I52+L52</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N52">
         <v>8.5</v>
       </c>
       <c r="O52">
-        <f>N52/M52</f>
+        <f t="shared" si="8"/>
         <v>0.85</v>
       </c>
       <c r="R52">
-        <f>I52+L52+P52</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S52">
-        <f>R52-N52</f>
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
       <c r="Z52">
@@ -24908,22 +25017,22 @@
         <v>10</v>
       </c>
       <c r="M53">
-        <f>I53+L53</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N53">
         <v>8.5</v>
       </c>
       <c r="O53">
-        <f>N53/M53</f>
+        <f t="shared" si="8"/>
         <v>0.85</v>
       </c>
       <c r="R53">
-        <f>I53+L53+P53</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S53">
-        <f>R53-N53</f>
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
       <c r="Z53">
@@ -24977,22 +25086,22 @@
         <v>10</v>
       </c>
       <c r="M54">
-        <f>I54+L54</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N54">
         <v>9</v>
       </c>
       <c r="O54">
-        <f>N54/M54</f>
+        <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
       <c r="R54">
-        <f>I54+L54+P54</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S54">
-        <f>R54-N54</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z54">
@@ -25043,22 +25152,22 @@
         <v>10</v>
       </c>
       <c r="M55">
-        <f>I55+L55</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N55">
         <v>9</v>
       </c>
       <c r="O55">
-        <f>N55/M55</f>
+        <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
       <c r="R55">
-        <f>I55+L55+P55</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S55">
-        <f>R55-N55</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z55">
@@ -25112,22 +25221,22 @@
         <v>10</v>
       </c>
       <c r="M56">
-        <f>I56+L56</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N56">
         <v>10</v>
       </c>
       <c r="O56">
-        <f>N56/M56</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="R56">
-        <f>I56+L56+P56</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S56">
-        <f>R56-N56</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z56">
@@ -25181,22 +25290,22 @@
         <v>10</v>
       </c>
       <c r="M57">
-        <f>I57+L57</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N57">
         <v>8.5</v>
       </c>
       <c r="O57">
-        <f>N57/M57</f>
+        <f t="shared" si="8"/>
         <v>0.85</v>
       </c>
       <c r="R57">
-        <f>I57+L57+P57</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S57">
-        <f>R57-N57</f>
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
       <c r="Z57">
@@ -25247,22 +25356,22 @@
         <v>10</v>
       </c>
       <c r="M58">
-        <f>I58+L58</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N58">
         <v>10</v>
       </c>
       <c r="O58">
-        <f>N58/M58</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="R58">
-        <f>I58+L58+P58</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S58">
-        <f>R58-N58</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z58">
@@ -25316,22 +25425,22 @@
         <v>10</v>
       </c>
       <c r="M59">
-        <f>I59+L59</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N59">
         <v>1</v>
       </c>
       <c r="O59">
-        <f>N59/M59</f>
+        <f t="shared" si="8"/>
         <v>0.1</v>
       </c>
       <c r="R59">
-        <f>I59+L59+P59</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S59">
-        <f>R59-N59</f>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="Z59">
@@ -25385,22 +25494,22 @@
         <v>10</v>
       </c>
       <c r="M60">
-        <f>I60+L60</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N60">
         <v>9.5</v>
       </c>
       <c r="O60">
-        <f>N60/M60</f>
+        <f t="shared" si="8"/>
         <v>0.95</v>
       </c>
       <c r="R60">
-        <f>I60+L60+P60</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S60">
-        <f>R60-N60</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="Z60">
@@ -25451,22 +25560,22 @@
         <v>10</v>
       </c>
       <c r="M61">
-        <f>I61+L61</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N61">
         <v>9</v>
       </c>
       <c r="O61">
-        <f>N61/M61</f>
+        <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
       <c r="R61">
-        <f>I61+L61+P61</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S61">
-        <f>R61-N61</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Z61">
@@ -25520,22 +25629,22 @@
         <v>10</v>
       </c>
       <c r="M62">
-        <f>I62+L62</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N62">
         <v>8</v>
       </c>
       <c r="O62">
-        <f>N62/M62</f>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="R62">
-        <f>I62+L62+P62</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S62">
-        <f>R62-N62</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Z62">
@@ -25586,22 +25695,22 @@
         <v>10</v>
       </c>
       <c r="M63">
-        <f>I63+L63</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N63">
         <v>9.5</v>
       </c>
       <c r="O63">
-        <f>N63/M63</f>
+        <f t="shared" si="8"/>
         <v>0.95</v>
       </c>
       <c r="R63">
-        <f>I63+L63+P63</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S63">
-        <f>R63-N63</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="Z63">
@@ -25655,22 +25764,22 @@
         <v>10</v>
       </c>
       <c r="M64">
-        <f>I64+L64</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N64">
         <v>10</v>
       </c>
       <c r="O64">
-        <f>N64/M64</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="R64">
-        <f>I64+L64+P64</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S64">
-        <f>R64-N64</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z64">
@@ -25724,22 +25833,22 @@
         <v>10</v>
       </c>
       <c r="M65">
-        <f>I65+L65</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N65">
         <v>8</v>
       </c>
       <c r="O65">
-        <f>N65/M65</f>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="R65">
-        <f>I65+L65+P65</f>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="S65">
-        <f>R65-N65</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Z65">

--- a/data/raw/NCE_data.xlsx
+++ b/data/raw/NCE_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://waikatouniversitynz-my.sharepoint.com/personal/or81_students_waikato_ac_nz/Documents/Documents/PhD/01_thesis_chapters/05_fear_study/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{1C509BC5-B9CD-4355-A94E-B3E32C99D6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CC211BF-B576-4E0F-BD09-C03127A9F36E}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{1C509BC5-B9CD-4355-A94E-B3E32C99D6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46560DEC-76A5-493E-A4D2-746278E237B5}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{884ED942-72D7-478A-91F6-B92A4F060477}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="3" xr2:uid="{884ED942-72D7-478A-91F6-B92A4F060477}"/>
   </bookViews>
   <sheets>
     <sheet name="NCE_exp" sheetId="2" r:id="rId1"/>
@@ -53,7 +53,7 @@
     <author>tc={DA4195C2-418A-4F3F-9226-CF4AB1AFECEF}</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{3461571A-8435-47F5-932C-87907A560006}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{3461571A-8435-47F5-932C-87907A560006}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -61,7 +61,7 @@
     Treatment is applied by adding to the 7 Liter in the tank an extra Liter of water coming from the catfish or eel holding tanks or a Liter of dechlorinaded tab water.</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="1" shapeId="0" xr:uid="{725FDFAA-9574-4676-B0CD-96F47B5BAC4E}">
+    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{725FDFAA-9574-4676-B0CD-96F47B5BAC4E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -69,7 +69,7 @@
     Pellets left after this time</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="2" shapeId="0" xr:uid="{2F95F192-4B86-4AC9-8D2D-24C01B901B1E}">
+    <comment ref="M1" authorId="2" shapeId="0" xr:uid="{2F95F192-4B86-4AC9-8D2D-24C01B901B1E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -77,7 +77,7 @@
     Extra food given when less than 3 pellets left. Than 5 new given</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="3" shapeId="0" xr:uid="{8FD33AC5-01BC-4A61-82BE-07CE2703C754}">
+    <comment ref="O1" authorId="3" shapeId="0" xr:uid="{8FD33AC5-01BC-4A61-82BE-07CE2703C754}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -85,7 +85,7 @@
     Light might not have gone out for round 1 due to error with the lighting from now fixed and day is 7:00-20:00</t>
       </text>
     </comment>
-    <comment ref="P1" authorId="4" shapeId="0" xr:uid="{DA4195C2-418A-4F3F-9226-CF4AB1AFECEF}">
+    <comment ref="Q1" authorId="4" shapeId="0" xr:uid="{DA4195C2-418A-4F3F-9226-CF4AB1AFECEF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4023" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4024" uniqueCount="191">
   <si>
     <t>S</t>
   </si>
@@ -814,7 +814,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -832,6 +832,7 @@
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1172,19 +1173,19 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D1" dT="2025-10-07T22:37:37.41" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{3461571A-8435-47F5-932C-87907A560006}">
+  <threadedComment ref="E1" dT="2025-10-07T22:37:37.41" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{3461571A-8435-47F5-932C-87907A560006}">
     <text>Treatment is applied by adding to the 7 Liter in the tank an extra Liter of water coming from the catfish or eel holding tanks or a Liter of dechlorinaded tab water.</text>
   </threadedComment>
-  <threadedComment ref="K1" dT="2025-10-07T22:21:57.50" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{725FDFAA-9574-4676-B0CD-96F47B5BAC4E}">
+  <threadedComment ref="L1" dT="2025-10-07T22:21:57.50" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{725FDFAA-9574-4676-B0CD-96F47B5BAC4E}">
     <text>Pellets left after this time</text>
   </threadedComment>
-  <threadedComment ref="L1" dT="2025-10-07T22:32:08.27" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{2F95F192-4B86-4AC9-8D2D-24C01B901B1E}">
+  <threadedComment ref="M1" dT="2025-10-07T22:32:08.27" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{2F95F192-4B86-4AC9-8D2D-24C01B901B1E}">
     <text>Extra food given when less than 3 pellets left. Than 5 new given</text>
   </threadedComment>
-  <threadedComment ref="N1" dT="2025-10-07T22:28:09.61" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{8FD33AC5-01BC-4A61-82BE-07CE2703C754}">
+  <threadedComment ref="O1" dT="2025-10-07T22:28:09.61" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{8FD33AC5-01BC-4A61-82BE-07CE2703C754}">
     <text>Light might not have gone out for round 1 due to error with the lighting from now fixed and day is 7:00-20:00</text>
   </threadedComment>
-  <threadedComment ref="P1" dT="2025-10-07T22:32:08.27" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{DA4195C2-418A-4F3F-9226-CF4AB1AFECEF}">
+  <threadedComment ref="Q1" dT="2025-10-07T22:32:08.27" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{DA4195C2-418A-4F3F-9226-CF4AB1AFECEF}">
     <text>Extra food given when less than 3 pellets left. Than 5 new given</text>
   </threadedComment>
 </ThreadedComments>
@@ -14621,2078 +14622,2132 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{853DF2F7-7B07-467C-B845-65DDCE944602}">
-  <dimension ref="A1:AO65"/>
+  <dimension ref="A1:AP65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="6" max="6" width="9.83984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
         <v>135</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="B2" s="3">
+        <v>0</v>
       </c>
       <c r="C2" s="3">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="17">
         <v>45937</v>
       </c>
-      <c r="G2" s="13">
+      <c r="H2" s="13">
         <v>0.5</v>
       </c>
-      <c r="H2" s="3">
-        <v>2</v>
-      </c>
       <c r="I2" s="3">
-        <v>5</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J2" s="3">
+        <v>5</v>
+      </c>
+      <c r="K2" s="3"/>
       <c r="L2" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2" s="3">
-        <f t="shared" ref="M2:M33" si="0">I2+L2</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N2" s="3">
+        <f t="shared" ref="N2:N33" si="0">J2+M2</f>
+        <v>10</v>
+      </c>
+      <c r="O2" s="3">
         <v>7</v>
       </c>
-      <c r="O2" s="3">
-        <f t="shared" ref="O2:O33" si="1">N2/M2</f>
+      <c r="P2" s="3">
+        <f t="shared" ref="P2:P33" si="1">O2/N2</f>
         <v>0.7</v>
       </c>
-      <c r="P2" s="3">
+      <c r="Q2" s="3">
         <v>0</v>
       </c>
-      <c r="Q2" s="3">
-        <v>2</v>
-      </c>
       <c r="R2" s="3">
-        <f t="shared" ref="R2:R33" si="2">I2+L2+P2</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="S2" s="3">
-        <f t="shared" ref="S2:S17" si="3">R2-Q2</f>
+        <f t="shared" ref="S2:S33" si="2">J2+M2+Q2</f>
+        <v>10</v>
+      </c>
+      <c r="T2" s="3">
+        <f t="shared" ref="T2:T17" si="3">S2-R2</f>
         <v>8</v>
       </c>
-      <c r="T2" s="12">
-        <f>R2*pellet_weigth!$B$3</f>
+      <c r="U2" s="12">
+        <f>S2*pellet_weigth!$B$3</f>
         <v>0.54136666666666644</v>
       </c>
-      <c r="U2" s="3">
+      <c r="V2" s="3">
         <v>5.3125999999999998</v>
       </c>
-      <c r="V2" s="3">
+      <c r="W2" s="3">
         <v>5.3324999999999996</v>
       </c>
-      <c r="W2" s="3">
-        <f t="shared" ref="W2:W17" si="4">V2-U2</f>
+      <c r="X2" s="3">
+        <f t="shared" ref="X2:X17" si="4">W2-V2</f>
         <v>1.9899999999999807E-2</v>
       </c>
-      <c r="X2" s="12">
-        <f t="shared" ref="X2:X17" si="5">T2-W2</f>
+      <c r="Y2" s="12">
+        <f t="shared" ref="Y2:Y17" si="5">U2-X2</f>
         <v>0.52146666666666663</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Z2" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z2" s="3">
-        <v>1</v>
-      </c>
       <c r="AA2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="3">
         <v>27</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AC2" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="3">
+      <c r="AD2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="3">
         <v>28.66</v>
       </c>
-      <c r="AE2" s="3">
+      <c r="AF2" s="3">
         <v>16</v>
       </c>
-      <c r="AF2" s="3">
+      <c r="AG2" s="3">
         <v>8</v>
       </c>
-      <c r="AG2" s="3">
-        <v>2</v>
-      </c>
       <c r="AH2" s="3">
         <v>2</v>
       </c>
-      <c r="AI2" s="3"/>
+      <c r="AI2" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ2" s="3"/>
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
       <c r="AO2" s="3"/>
-    </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
+      <c r="AP2" s="3"/>
+    </row>
+    <row r="3" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B3">
-        <v>1</v>
+      <c r="B3" s="3">
+        <v>0</v>
       </c>
       <c r="C3" s="3">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="17">
         <v>45937</v>
       </c>
-      <c r="G3" s="13">
+      <c r="H3" s="13">
         <v>0.5</v>
       </c>
-      <c r="H3" s="3">
-        <v>2</v>
-      </c>
       <c r="I3" s="3">
-        <v>5</v>
-      </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J3" s="3">
+        <v>5</v>
+      </c>
+      <c r="K3" s="3"/>
       <c r="L3" s="3">
+        <v>5</v>
+      </c>
+      <c r="M3" s="3">
         <v>0</v>
       </c>
-      <c r="M3" s="3">
+      <c r="N3" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N3" s="3">
-        <v>5</v>
-      </c>
       <c r="O3" s="3">
+        <v>5</v>
+      </c>
+      <c r="P3" s="3">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P3" s="3">
+      <c r="Q3" s="3">
         <v>0</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="R3" s="3">
         <v>4.5</v>
       </c>
-      <c r="R3" s="3">
+      <c r="S3" s="3">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="S3" s="3">
+      <c r="T3" s="3">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="T3" s="12">
-        <f>R3*pellet_weigth!$B$3</f>
+      <c r="U3" s="12">
+        <f>S3*pellet_weigth!$B$3</f>
         <v>0.27068333333333322</v>
       </c>
-      <c r="U3" s="3">
+      <c r="V3" s="3">
         <v>5.3052999999999999</v>
       </c>
-      <c r="V3" s="3">
+      <c r="W3" s="3">
         <v>5.3487999999999998</v>
       </c>
-      <c r="W3" s="3">
+      <c r="X3" s="3">
         <f t="shared" si="4"/>
         <v>4.3499999999999872E-2</v>
       </c>
-      <c r="X3" s="12">
+      <c r="Y3" s="12">
         <f t="shared" si="5"/>
         <v>0.22718333333333335</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Z3" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z3" s="3">
-        <v>2</v>
-      </c>
       <c r="AA3" s="3">
+        <v>2</v>
+      </c>
+      <c r="AB3" s="3">
         <v>30</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AC3" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD3" s="3">
+      <c r="AD3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="3">
         <v>27.29</v>
       </c>
-      <c r="AE3" s="3">
+      <c r="AF3" s="3">
         <v>12</v>
       </c>
-      <c r="AF3" s="3">
+      <c r="AG3" s="3">
         <v>8</v>
       </c>
-      <c r="AG3" s="3">
-        <v>2</v>
-      </c>
       <c r="AH3" s="3">
         <v>2</v>
       </c>
-      <c r="AI3" s="3"/>
+      <c r="AI3" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
       <c r="AM3" s="3"/>
       <c r="AN3" s="3"/>
       <c r="AO3" s="3"/>
-    </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
+      <c r="AP3" s="3"/>
+    </row>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="B4" s="3">
+        <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="17">
         <v>45937</v>
       </c>
-      <c r="G4" s="13">
+      <c r="H4" s="13">
         <v>0.5</v>
       </c>
-      <c r="H4" s="3">
-        <v>2</v>
-      </c>
       <c r="I4" s="3">
-        <v>5</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3">
+        <v>2</v>
+      </c>
+      <c r="J4" s="3">
+        <v>5</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3">
         <v>0</v>
       </c>
-      <c r="L4" s="3">
-        <v>5</v>
-      </c>
       <c r="M4" s="3">
+        <v>5</v>
+      </c>
+      <c r="N4" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N4" s="3">
-        <v>1</v>
-      </c>
       <c r="O4" s="3">
+        <v>1</v>
+      </c>
+      <c r="P4" s="3">
         <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
-      <c r="P4" s="3">
-        <v>5</v>
-      </c>
       <c r="Q4" s="3">
+        <v>5</v>
+      </c>
+      <c r="R4" s="3">
         <v>4.5</v>
       </c>
-      <c r="R4" s="3">
+      <c r="S4" s="3">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="S4" s="3">
+      <c r="T4" s="3">
         <f t="shared" si="3"/>
         <v>10.5</v>
       </c>
-      <c r="T4" s="12">
-        <f>R4*pellet_weigth!$B$3</f>
+      <c r="U4" s="12">
+        <f>S4*pellet_weigth!$B$3</f>
         <v>0.81204999999999972</v>
       </c>
-      <c r="U4" s="3">
+      <c r="V4" s="3">
         <v>5.3022</v>
       </c>
-      <c r="V4" s="3">
+      <c r="W4" s="3">
         <v>5.4924999999999997</v>
       </c>
-      <c r="W4" s="3">
+      <c r="X4" s="3">
         <f t="shared" si="4"/>
         <v>0.19029999999999969</v>
       </c>
-      <c r="X4" s="12">
+      <c r="Y4" s="12">
         <f t="shared" si="5"/>
         <v>0.62175000000000002</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="Z4" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z4" s="3">
-        <v>3</v>
-      </c>
       <c r="AA4" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB4" s="3">
         <v>18</v>
       </c>
-      <c r="AB4" s="3" t="s">
+      <c r="AC4" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="3">
+      <c r="AD4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="3">
         <v>28.54</v>
       </c>
-      <c r="AE4" s="3">
+      <c r="AF4" s="3">
         <v>16</v>
       </c>
-      <c r="AF4" s="3">
+      <c r="AG4" s="3">
         <v>8</v>
       </c>
-      <c r="AG4" s="3">
-        <v>2</v>
-      </c>
       <c r="AH4" s="3">
         <v>2</v>
       </c>
-      <c r="AI4" s="3"/>
+      <c r="AI4" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
       <c r="AM4" s="3"/>
       <c r="AN4" s="3"/>
       <c r="AO4" s="3"/>
-    </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
+      <c r="AP4" s="3"/>
+    </row>
+    <row r="5" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="B5" s="3">
+        <v>0</v>
       </c>
       <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="17">
         <v>45937</v>
       </c>
-      <c r="G5" s="13">
+      <c r="H5" s="13">
         <v>0.5</v>
       </c>
-      <c r="H5" s="3">
-        <v>2</v>
-      </c>
       <c r="I5" s="3">
-        <v>5</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3">
+        <v>2</v>
+      </c>
+      <c r="J5" s="3">
+        <v>5</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3">
         <v>4</v>
       </c>
-      <c r="L5" s="3">
+      <c r="M5" s="3">
         <v>0</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N5" s="3">
+      <c r="O5" s="3">
         <v>4</v>
       </c>
-      <c r="O5" s="3">
+      <c r="P5" s="3">
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="P5" s="3">
-        <v>0</v>
-      </c>
       <c r="Q5" s="3">
         <v>0</v>
       </c>
       <c r="R5" s="3">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="S5" s="3">
+      <c r="T5" s="3">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="T5" s="12">
-        <f>R5*pellet_weigth!$B$3</f>
+      <c r="U5" s="12">
+        <f>S5*pellet_weigth!$B$3</f>
         <v>0.27068333333333322</v>
       </c>
-      <c r="U5" s="3">
+      <c r="V5" s="3">
         <v>5.3243999999999998</v>
       </c>
-      <c r="V5" s="3">
+      <c r="W5" s="3">
         <v>5.3719000000000001</v>
       </c>
-      <c r="W5" s="3">
+      <c r="X5" s="3">
         <f t="shared" si="4"/>
         <v>4.750000000000032E-2</v>
       </c>
-      <c r="X5" s="12">
+      <c r="Y5" s="12">
         <f t="shared" si="5"/>
         <v>0.2231833333333329</v>
       </c>
-      <c r="Y5" s="3" t="s">
+      <c r="Z5" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z5" s="3">
+      <c r="AA5" s="3">
         <v>4</v>
       </c>
-      <c r="AA5" s="3">
+      <c r="AB5" s="3">
         <v>7</v>
       </c>
-      <c r="AB5" s="3" t="s">
+      <c r="AC5" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC5" s="3" t="s">
+      <c r="AD5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AD5" s="3">
+      <c r="AE5" s="3">
         <v>30.81</v>
       </c>
-      <c r="AE5" s="3">
+      <c r="AF5" s="3">
         <v>20</v>
       </c>
-      <c r="AF5" s="3">
+      <c r="AG5" s="3">
         <v>8</v>
       </c>
-      <c r="AG5" s="3">
-        <v>2</v>
-      </c>
       <c r="AH5" s="3">
         <v>2</v>
       </c>
-      <c r="AI5" s="3"/>
+      <c r="AI5" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
       <c r="AN5" s="3"/>
       <c r="AO5" s="3"/>
-    </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
+      <c r="AP5" s="3"/>
+    </row>
+    <row r="6" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B6">
-        <v>1</v>
+      <c r="B6" s="3">
+        <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>5</v>
-      </c>
-      <c r="D6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="17">
         <v>45937</v>
       </c>
-      <c r="G6" s="13">
+      <c r="H6" s="13">
         <v>0.5</v>
       </c>
-      <c r="H6" s="3">
-        <v>2</v>
-      </c>
       <c r="I6" s="3">
-        <v>5</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J6" s="3">
+        <v>5</v>
+      </c>
+      <c r="K6" s="3"/>
       <c r="L6" s="3">
+        <v>5</v>
+      </c>
+      <c r="M6" s="3">
         <v>0</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="3">
         <v>4.5</v>
       </c>
-      <c r="O6" s="3">
+      <c r="P6" s="3">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
-      <c r="P6" s="3">
+      <c r="Q6" s="3">
         <v>0</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="R6" s="3">
         <v>0.5</v>
       </c>
-      <c r="R6" s="3">
+      <c r="S6" s="3">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="S6" s="3">
+      <c r="T6" s="3">
         <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
-      <c r="T6" s="12">
-        <f>R6*pellet_weigth!$B$3</f>
+      <c r="U6" s="12">
+        <f>S6*pellet_weigth!$B$3</f>
         <v>0.27068333333333322</v>
       </c>
-      <c r="U6" s="3">
+      <c r="V6" s="3">
         <v>5.3045999999999998</v>
       </c>
-      <c r="V6" s="3">
+      <c r="W6" s="3">
         <v>5.3333000000000004</v>
       </c>
-      <c r="W6" s="3">
+      <c r="X6" s="3">
         <f t="shared" si="4"/>
         <v>2.8700000000000614E-2</v>
       </c>
-      <c r="X6" s="12">
+      <c r="Y6" s="12">
         <f t="shared" si="5"/>
         <v>0.24198333333333261</v>
       </c>
-      <c r="Y6" s="3" t="s">
+      <c r="Z6" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3" t="s">
+      <c r="AA6" s="3">
+        <v>5</v>
+      </c>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC6" s="3" t="s">
+      <c r="AD6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="AD6" s="3">
+      <c r="AE6" s="3">
         <v>20.21</v>
       </c>
-      <c r="AE6" s="3">
-        <v>5</v>
-      </c>
       <c r="AF6" s="3">
+        <v>5</v>
+      </c>
+      <c r="AG6" s="3">
         <v>8</v>
       </c>
-      <c r="AG6" s="3">
-        <v>2</v>
-      </c>
       <c r="AH6" s="3">
         <v>2</v>
       </c>
-      <c r="AI6" s="3"/>
+      <c r="AI6" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
       <c r="AN6" s="3"/>
       <c r="AO6" s="3"/>
-    </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
+      <c r="AP6" s="3"/>
+    </row>
+    <row r="7" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B7">
-        <v>1</v>
+      <c r="B7" s="3">
+        <v>0</v>
       </c>
       <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
         <v>6</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="17">
         <v>45937</v>
       </c>
-      <c r="G7" s="13">
+      <c r="H7" s="13">
         <v>0.5</v>
       </c>
-      <c r="H7" s="3">
-        <v>2</v>
-      </c>
       <c r="I7" s="3">
-        <v>5</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J7" s="3">
+        <v>5</v>
+      </c>
+      <c r="K7" s="3"/>
       <c r="L7" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M7" s="3">
+        <v>5</v>
+      </c>
+      <c r="N7" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N7" s="3">
-        <v>5</v>
-      </c>
       <c r="O7" s="3">
+        <v>5</v>
+      </c>
+      <c r="P7" s="3">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="P7" s="3">
+      <c r="Q7" s="3">
         <v>0</v>
       </c>
-      <c r="Q7" s="3">
-        <v>5</v>
-      </c>
       <c r="R7" s="3">
+        <v>5</v>
+      </c>
+      <c r="S7" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S7" s="3">
+      <c r="T7" s="3">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="T7" s="12">
-        <f>R7*pellet_weigth!$B$3</f>
+      <c r="U7" s="12">
+        <f>S7*pellet_weigth!$B$3</f>
         <v>0.54136666666666644</v>
       </c>
-      <c r="U7" s="3">
+      <c r="V7" s="3">
         <v>5.3489000000000004</v>
       </c>
-      <c r="V7" s="3">
+      <c r="W7" s="3">
         <v>5.4973000000000001</v>
       </c>
-      <c r="W7" s="3">
+      <c r="X7" s="3">
         <f t="shared" si="4"/>
         <v>0.14839999999999964</v>
       </c>
-      <c r="X7" s="12">
+      <c r="Y7" s="12">
         <f t="shared" si="5"/>
         <v>0.3929666666666668</v>
       </c>
-      <c r="Y7" s="3" t="s">
+      <c r="Z7" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z7" s="3">
+      <c r="AA7" s="3">
         <v>6</v>
       </c>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="3" t="s">
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="3">
+      <c r="AD7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="3">
         <v>23.21</v>
       </c>
-      <c r="AE7" s="3">
+      <c r="AF7" s="3">
         <v>8</v>
       </c>
-      <c r="AF7" s="3">
+      <c r="AG7" s="3">
         <v>6</v>
       </c>
-      <c r="AG7" s="3">
-        <v>1</v>
-      </c>
       <c r="AH7" s="3">
-        <v>2</v>
-      </c>
-      <c r="AI7" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="AI7" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ7" s="3"/>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
       <c r="AO7" s="3"/>
-    </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
+      <c r="AP7" s="3"/>
+    </row>
+    <row r="8" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B8">
-        <v>1</v>
+      <c r="B8" s="3">
+        <v>0</v>
       </c>
       <c r="C8" s="3">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
         <v>7</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="17">
         <v>45937</v>
       </c>
-      <c r="G8" s="13">
+      <c r="H8" s="13">
         <v>0.5</v>
       </c>
-      <c r="H8" s="3">
-        <v>2</v>
-      </c>
       <c r="I8" s="3">
-        <v>5</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3">
+        <v>2</v>
+      </c>
+      <c r="J8" s="3">
+        <v>5</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3">
         <v>0</v>
       </c>
-      <c r="L8" s="3">
-        <v>5</v>
-      </c>
       <c r="M8" s="3">
+        <v>5</v>
+      </c>
+      <c r="N8" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2.5</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
-      <c r="P8" s="3">
-        <v>5</v>
-      </c>
       <c r="Q8" s="3">
         <v>5</v>
       </c>
       <c r="R8" s="3">
+        <v>5</v>
+      </c>
+      <c r="S8" s="3">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="T8" s="12">
-        <f>R8*pellet_weigth!$B$3</f>
+      <c r="U8" s="12">
+        <f>S8*pellet_weigth!$B$3</f>
         <v>0.81204999999999972</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5.3219000000000003</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5.5107999999999997</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <f t="shared" si="4"/>
         <v>0.1888999999999994</v>
       </c>
-      <c r="X8" s="12">
+      <c r="Y8" s="12">
         <f t="shared" si="5"/>
         <v>0.62315000000000031</v>
       </c>
-      <c r="Y8" s="3" t="s">
+      <c r="Z8" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>35</v>
       </c>
-      <c r="AB8" s="3" t="s">
+      <c r="AC8" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD8" s="3">
+      <c r="AD8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="3">
         <v>25.55</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>7</v>
       </c>
-      <c r="AG8" s="3">
-        <v>2</v>
-      </c>
       <c r="AH8" s="3">
-        <v>1</v>
-      </c>
-      <c r="AI8" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>1</v>
+      </c>
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
       <c r="AN8" s="3"/>
       <c r="AO8" s="3"/>
-    </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
+      <c r="AP8" s="3"/>
+    </row>
+    <row r="9" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B9">
-        <v>1</v>
+      <c r="B9" s="3">
+        <v>0</v>
       </c>
       <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
         <v>8</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="17">
         <v>45937</v>
       </c>
-      <c r="G9" s="13">
+      <c r="H9" s="13">
         <v>0.5</v>
       </c>
-      <c r="H9" s="3">
-        <v>2</v>
-      </c>
       <c r="I9" s="3">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J9" s="3">
+        <v>5</v>
+      </c>
+      <c r="K9" s="3"/>
       <c r="L9" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M9" s="3">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>0</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="T9" s="12">
-        <f>R9*pellet_weigth!$B$3</f>
+      <c r="U9" s="12">
+        <f>S9*pellet_weigth!$B$3</f>
         <v>0.54136666666666644</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5.3417000000000003</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5.4987000000000004</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <f t="shared" si="4"/>
         <v>0.15700000000000003</v>
       </c>
-      <c r="X9" s="12">
+      <c r="Y9" s="12">
         <f t="shared" si="5"/>
         <v>0.38436666666666641</v>
       </c>
-      <c r="Y9" s="3" t="s">
+      <c r="Z9" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8</v>
       </c>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3" t="s">
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC9" s="3" t="s">
+      <c r="AD9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>21.62</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8</v>
       </c>
-      <c r="AG9" s="3">
-        <v>2</v>
-      </c>
       <c r="AH9" s="3">
         <v>2</v>
       </c>
-      <c r="AI9" s="3"/>
+      <c r="AI9" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
       <c r="AN9" s="3"/>
       <c r="AO9" s="3"/>
-    </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
+      <c r="AP9" s="3"/>
+    </row>
+    <row r="10" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B10">
-        <v>1</v>
+      <c r="B10" s="3">
+        <v>0</v>
       </c>
       <c r="C10" s="3">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G10" s="17">
         <v>45937</v>
       </c>
-      <c r="G10" s="13">
+      <c r="H10" s="13">
         <v>0.5</v>
       </c>
-      <c r="H10" s="3">
-        <v>2</v>
-      </c>
       <c r="I10" s="3">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3"/>
       <c r="L10" s="3">
+        <v>5</v>
+      </c>
+      <c r="M10" s="3">
         <v>0</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>0</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P10" s="3">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>0</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="T10" s="12">
-        <f>R10*pellet_weigth!$B$3</f>
+      <c r="U10" s="12">
+        <f>S10*pellet_weigth!$B$3</f>
         <v>0.54136666666666644</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5.3342000000000001</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5.3574000000000002</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <f t="shared" si="4"/>
         <v>2.3200000000000109E-2</v>
       </c>
-      <c r="X10" s="12">
+      <c r="Y10" s="12">
         <f t="shared" si="5"/>
         <v>0.51816666666666633</v>
       </c>
-      <c r="Y10" s="3" t="s">
+      <c r="Z10" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z10" s="3">
-        <v>9</v>
-      </c>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="3" t="s">
+      <c r="AA10" s="3">
+        <v>9</v>
+      </c>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="3">
+      <c r="AD10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="3">
         <v>29.91</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>16</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8</v>
       </c>
-      <c r="AG10" s="3">
-        <v>2</v>
-      </c>
       <c r="AH10" s="3">
         <v>2</v>
       </c>
-      <c r="AI10" s="3"/>
+      <c r="AI10" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ10" s="3"/>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
       <c r="AN10" s="3"/>
-      <c r="AO10" s="3" t="s">
+      <c r="AO10" s="3"/>
+      <c r="AP10" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B11">
-        <v>1</v>
+      <c r="B11" s="3">
+        <v>0</v>
       </c>
       <c r="C11" s="3">
-        <v>10</v>
-      </c>
-      <c r="D11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>10</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F11" s="2">
+      <c r="G11" s="17">
         <v>45937</v>
       </c>
-      <c r="G11" s="13">
+      <c r="H11" s="13">
         <v>0.5</v>
       </c>
-      <c r="H11" s="3">
-        <v>2</v>
-      </c>
       <c r="I11" s="3">
-        <v>5</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J11" s="3">
+        <v>5</v>
+      </c>
+      <c r="K11" s="3"/>
       <c r="L11" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M11" s="3">
+        <v>5</v>
+      </c>
+      <c r="N11" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N11" s="3">
-        <v>5</v>
-      </c>
       <c r="O11" s="3">
+        <v>5</v>
+      </c>
+      <c r="P11" s="3">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="P11" s="3">
+      <c r="Q11" s="3">
         <v>0</v>
       </c>
-      <c r="Q11" s="3">
-        <v>2</v>
-      </c>
       <c r="R11" s="3">
+        <v>2</v>
+      </c>
+      <c r="S11" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S11" s="3">
+      <c r="T11" s="3">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="T11" s="12">
-        <f>R11*pellet_weigth!$B$3</f>
+      <c r="U11" s="12">
+        <f>S11*pellet_weigth!$B$3</f>
         <v>0.54136666666666644</v>
       </c>
-      <c r="U11" s="3">
+      <c r="V11" s="3">
         <v>5.2823000000000002</v>
       </c>
-      <c r="V11" s="3">
+      <c r="W11" s="3">
         <v>5.3703000000000003</v>
       </c>
-      <c r="W11" s="3">
+      <c r="X11" s="3">
         <f t="shared" si="4"/>
         <v>8.8000000000000078E-2</v>
       </c>
-      <c r="X11" s="12">
+      <c r="Y11" s="12">
         <f t="shared" si="5"/>
         <v>0.45336666666666636</v>
       </c>
-      <c r="Y11" s="3" t="s">
+      <c r="Z11" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z11" s="3">
-        <v>10</v>
-      </c>
       <c r="AA11" s="3">
         <v>10</v>
       </c>
-      <c r="AB11" s="3" t="s">
+      <c r="AB11" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC11" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD11" s="3">
+      <c r="AD11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="3">
         <v>26.41</v>
       </c>
-      <c r="AE11" s="3">
+      <c r="AF11" s="3">
         <v>12</v>
       </c>
-      <c r="AF11" s="3">
+      <c r="AG11" s="3">
         <v>6</v>
       </c>
-      <c r="AG11" s="3">
-        <v>2</v>
-      </c>
       <c r="AH11" s="3">
         <v>2</v>
       </c>
-      <c r="AI11" s="3"/>
+      <c r="AI11" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
-    </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" t="s">
+      <c r="AP11" s="3"/>
+    </row>
+    <row r="12" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B12">
-        <v>1</v>
+      <c r="B12" s="3">
+        <v>0</v>
       </c>
       <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
         <v>11</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F12" s="2">
+      <c r="G12" s="17">
         <v>45937</v>
       </c>
-      <c r="G12" s="13">
+      <c r="H12" s="13">
         <v>0.5</v>
       </c>
-      <c r="H12" s="3">
-        <v>2</v>
-      </c>
       <c r="I12" s="3">
-        <v>5</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J12" s="3">
+        <v>5</v>
+      </c>
+      <c r="K12" s="3"/>
       <c r="L12" s="3">
+        <v>5</v>
+      </c>
+      <c r="M12" s="3">
         <v>0</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N12" s="3">
-        <v>5</v>
-      </c>
       <c r="O12" s="3">
+        <v>5</v>
+      </c>
+      <c r="P12" s="3">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>0</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2.5</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
-      <c r="T12" s="12">
-        <f>R12*pellet_weigth!$B$3</f>
+      <c r="U12" s="12">
+        <f>S12*pellet_weigth!$B$3</f>
         <v>0.27068333333333322</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5.3769</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5.4090999999999996</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <f t="shared" si="4"/>
         <v>3.2199999999999562E-2</v>
       </c>
-      <c r="X12" s="12">
+      <c r="Y12" s="12">
         <f t="shared" si="5"/>
         <v>0.23848333333333366</v>
       </c>
-      <c r="Y12" s="3" t="s">
+      <c r="Z12" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>11</v>
       </c>
-      <c r="AA12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="3" t="s">
+      <c r="AB12" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD12" s="3">
+      <c r="AD12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="3">
         <v>25.6</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>11</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>8</v>
       </c>
-      <c r="AG12" s="3">
-        <v>2</v>
-      </c>
       <c r="AH12" s="3">
         <v>2</v>
       </c>
-      <c r="AI12" s="3"/>
+      <c r="AI12" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ12" s="3"/>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
       <c r="AN12" s="3"/>
       <c r="AO12" s="3"/>
-    </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" t="s">
+      <c r="AP12" s="3"/>
+    </row>
+    <row r="13" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B13">
-        <v>1</v>
+      <c r="B13" s="3">
+        <v>0</v>
       </c>
       <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
         <v>12</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G13" s="17">
         <v>45937</v>
       </c>
-      <c r="G13" s="13">
+      <c r="H13" s="13">
         <v>0.5</v>
       </c>
-      <c r="H13" s="3">
-        <v>2</v>
-      </c>
       <c r="I13" s="3">
-        <v>5</v>
-      </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J13" s="3">
+        <v>5</v>
+      </c>
+      <c r="K13" s="3"/>
       <c r="L13" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M13" s="3">
+        <v>5</v>
+      </c>
+      <c r="N13" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N13" s="3">
+      <c r="O13" s="3">
         <v>7</v>
       </c>
-      <c r="O13" s="3">
+      <c r="P13" s="3">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="P13" s="3">
+      <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3">
-        <v>1</v>
-      </c>
       <c r="R13" s="3">
+        <v>1</v>
+      </c>
+      <c r="S13" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S13" s="3">
+      <c r="T13" s="3">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="T13" s="12">
-        <f>R13*pellet_weigth!$B$3</f>
+      <c r="U13" s="12">
+        <f>S13*pellet_weigth!$B$3</f>
         <v>0.54136666666666644</v>
       </c>
-      <c r="U13" s="3">
+      <c r="V13" s="3">
         <v>5.2651000000000003</v>
       </c>
-      <c r="V13" s="3">
+      <c r="W13" s="3">
         <v>5.3334999999999999</v>
       </c>
-      <c r="W13" s="3">
+      <c r="X13" s="3">
         <f t="shared" si="4"/>
         <v>6.8399999999999572E-2</v>
       </c>
-      <c r="X13" s="12">
+      <c r="Y13" s="12">
         <f t="shared" si="5"/>
         <v>0.47296666666666687</v>
       </c>
-      <c r="Y13" s="3" t="s">
+      <c r="Z13" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z13" s="3">
+      <c r="AA13" s="3">
         <v>12</v>
       </c>
-      <c r="AA13" s="3">
+      <c r="AB13" s="3">
         <v>20</v>
       </c>
-      <c r="AB13" s="3" t="s">
+      <c r="AC13" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD13" s="3">
+      <c r="AD13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="3">
         <v>24.06</v>
       </c>
-      <c r="AE13" s="3">
-        <v>10</v>
-      </c>
       <c r="AF13" s="3">
+        <v>10</v>
+      </c>
+      <c r="AG13" s="3">
         <v>8</v>
       </c>
-      <c r="AG13" s="3">
-        <v>2</v>
-      </c>
       <c r="AH13" s="3">
         <v>2</v>
       </c>
-      <c r="AI13" s="3"/>
+      <c r="AI13" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ13" s="3"/>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
       <c r="AO13" s="3"/>
-    </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" t="s">
+      <c r="AP13" s="3"/>
+    </row>
+    <row r="14" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B14">
-        <v>1</v>
+      <c r="B14" s="3">
+        <v>0</v>
       </c>
       <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
         <v>13</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G14" s="17">
         <v>45937</v>
       </c>
-      <c r="G14" s="13">
+      <c r="H14" s="13">
         <v>0.5</v>
       </c>
-      <c r="H14" s="3">
-        <v>2</v>
-      </c>
       <c r="I14" s="3">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J14" s="3">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3"/>
       <c r="L14" s="3">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N14" s="3">
-        <v>5</v>
-      </c>
       <c r="O14" s="3">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>0.5</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
-      <c r="T14" s="12">
-        <f>R14*pellet_weigth!$B$3</f>
+      <c r="U14" s="12">
+        <f>S14*pellet_weigth!$B$3</f>
         <v>0.27068333333333322</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>5.3407999999999998</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>5.3845999999999998</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <f t="shared" si="4"/>
         <v>4.3800000000000061E-2</v>
       </c>
-      <c r="X14" s="12">
+      <c r="Y14" s="12">
         <f t="shared" si="5"/>
         <v>0.22688333333333316</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>13</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>8</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="3">
         <v>29.75</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>17</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
-        <v>2</v>
-      </c>
       <c r="AH14" s="3">
         <v>2</v>
       </c>
-      <c r="AI14" s="3"/>
+      <c r="AI14" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ14" s="3"/>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
-    </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" t="s">
+      <c r="AP14" s="3"/>
+    </row>
+    <row r="15" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B15">
-        <v>1</v>
+      <c r="B15" s="3">
+        <v>0</v>
       </c>
       <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3">
         <v>14</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F15" s="2">
+      <c r="G15" s="17">
         <v>45937</v>
       </c>
-      <c r="G15" s="13">
+      <c r="H15" s="13">
         <v>0.5</v>
       </c>
-      <c r="H15" s="3">
-        <v>2</v>
-      </c>
       <c r="I15" s="3">
-        <v>5</v>
-      </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J15" s="3">
+        <v>5</v>
+      </c>
+      <c r="K15" s="3"/>
       <c r="L15" s="3">
+        <v>5</v>
+      </c>
+      <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="N15" s="3">
-        <v>5</v>
-      </c>
       <c r="O15" s="3">
+        <v>5</v>
+      </c>
+      <c r="P15" s="3">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>0.5</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
-      <c r="T15" s="12">
-        <f>R15*pellet_weigth!$B$3</f>
+      <c r="U15" s="12">
+        <f>S15*pellet_weigth!$B$3</f>
         <v>0.27068333333333322</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>5.335</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>5.3742999999999999</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <f t="shared" si="4"/>
         <v>3.9299999999999891E-2</v>
       </c>
-      <c r="X15" s="12">
+      <c r="Y15" s="12">
         <f t="shared" si="5"/>
         <v>0.23138333333333333</v>
       </c>
-      <c r="Y15" s="3" t="s">
+      <c r="Z15" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>14</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>38</v>
       </c>
-      <c r="AB15" s="3" t="s">
+      <c r="AC15" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC15" s="3" t="s">
+      <c r="AD15" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>19.899999999999999</v>
       </c>
-      <c r="AE15" s="3">
-        <v>5</v>
-      </c>
       <c r="AF15" s="3">
         <v>5</v>
       </c>
       <c r="AG15" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH15" s="3">
         <v>0</v>
       </c>
       <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>21.24</v>
       </c>
-      <c r="AJ15" s="3">
-        <v>5</v>
-      </c>
       <c r="AK15" s="3">
         <v>5</v>
       </c>
       <c r="AL15" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM15" s="3">
         <v>0</v>
       </c>
-      <c r="AN15" s="14">
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="14">
         <v>45939</v>
       </c>
-      <c r="AO15" s="3" t="s">
+      <c r="AP15" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B16">
-        <v>1</v>
+      <c r="B16" s="3">
+        <v>0</v>
       </c>
       <c r="C16" s="3">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3">
         <v>15</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F16" s="2">
+      <c r="G16" s="17">
         <v>45937</v>
       </c>
-      <c r="G16" s="13">
+      <c r="H16" s="13">
         <v>0.5</v>
       </c>
-      <c r="H16" s="3">
-        <v>2</v>
-      </c>
       <c r="I16" s="3">
-        <v>5</v>
-      </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J16" s="3">
+        <v>5</v>
+      </c>
+      <c r="K16" s="3"/>
       <c r="L16" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M16" s="3">
+        <v>5</v>
+      </c>
+      <c r="N16" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N16" s="3">
+      <c r="O16" s="3">
         <v>7</v>
       </c>
-      <c r="O16" s="3">
+      <c r="P16" s="3">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="P16" s="3">
+      <c r="Q16" s="3">
         <v>0</v>
       </c>
-      <c r="Q16" s="3">
-        <v>1</v>
-      </c>
       <c r="R16" s="3">
+        <v>1</v>
+      </c>
+      <c r="S16" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S16" s="3">
+      <c r="T16" s="3">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="T16" s="12">
-        <f>R16*pellet_weigth!$B$3</f>
+      <c r="U16" s="12">
+        <f>S16*pellet_weigth!$B$3</f>
         <v>0.54136666666666644</v>
       </c>
-      <c r="U16" s="3">
+      <c r="V16" s="3">
         <v>5.3906000000000001</v>
       </c>
-      <c r="V16" s="3">
+      <c r="W16" s="3">
         <v>5.5160999999999998</v>
       </c>
-      <c r="W16" s="3">
+      <c r="X16" s="3">
         <f t="shared" si="4"/>
         <v>0.12549999999999972</v>
       </c>
-      <c r="X16" s="12">
+      <c r="Y16" s="12">
         <f t="shared" si="5"/>
         <v>0.41586666666666672</v>
       </c>
-      <c r="Y16" s="3" t="s">
+      <c r="Z16" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z16" s="3">
+      <c r="AA16" s="3">
         <v>15</v>
       </c>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="3" t="s">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC16" s="3" t="s">
+      <c r="AD16" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="AD16" s="3">
+      <c r="AE16" s="3">
         <v>20.73</v>
       </c>
-      <c r="AE16" s="3">
-        <v>5</v>
-      </c>
       <c r="AF16" s="3">
+        <v>5</v>
+      </c>
+      <c r="AG16" s="3">
         <v>8</v>
       </c>
-      <c r="AG16" s="3">
-        <v>2</v>
-      </c>
       <c r="AH16" s="3">
         <v>2</v>
       </c>
-      <c r="AI16" s="3"/>
+      <c r="AI16" s="3">
+        <v>2</v>
+      </c>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
-    </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" t="s">
+      <c r="AP16" s="3"/>
+    </row>
+    <row r="17" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B17">
-        <v>1</v>
+      <c r="B17" s="3">
+        <v>0</v>
       </c>
       <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
         <v>16</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F17" s="2">
+      <c r="G17" s="17">
         <v>45937</v>
       </c>
-      <c r="G17" s="13">
+      <c r="H17" s="13">
         <v>0.5</v>
       </c>
-      <c r="H17" s="3">
-        <v>2</v>
-      </c>
       <c r="I17" s="3">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J17" s="3">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3"/>
       <c r="L17" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M17" s="3">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
       <c r="Q17" s="3">
         <v>0</v>
       </c>
       <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="T17" s="12">
-        <f>R17*pellet_weigth!$B$3</f>
+      <c r="U17" s="12">
+        <f>S17*pellet_weigth!$B$3</f>
         <v>0.54136666666666644</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5.3566000000000003</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5.4272999999999998</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <f t="shared" si="4"/>
         <v>7.0699999999999541E-2</v>
       </c>
-      <c r="X17" s="12">
+      <c r="Y17" s="12">
         <f t="shared" si="5"/>
         <v>0.4706666666666669</v>
       </c>
-      <c r="Y17" s="3" t="s">
+      <c r="Z17" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>16</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4</v>
       </c>
-      <c r="AB17" s="3" t="s">
+      <c r="AC17" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD17" s="3">
+      <c r="AD17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="3">
         <v>26.88</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>14</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8</v>
       </c>
-      <c r="AG17" s="3">
-        <v>2</v>
-      </c>
       <c r="AH17" s="3">
         <v>2</v>
       </c>
-      <c r="AI17" s="11"/>
-      <c r="AJ17" s="3"/>
+      <c r="AI17" s="3">
+        <v>2</v>
+      </c>
+      <c r="AJ17" s="11"/>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
       <c r="AM17" s="3"/>
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
-    </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AP17" s="3"/>
+    </row>
+    <row r="18" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>156</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
         <v>12</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>155</v>
       </c>
-      <c r="F18" s="2">
+      <c r="G18" s="2">
         <v>45953</v>
       </c>
-      <c r="G18" s="10">
+      <c r="H18" s="10">
         <v>0.45833333333333331</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>0</v>
       </c>
-      <c r="I18">
-        <v>10</v>
-      </c>
       <c r="J18">
+        <v>10</v>
+      </c>
+      <c r="K18">
         <v>0.47839999999999999</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>9.5</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <f t="shared" si="1"/>
         <v>0.95</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S18">
-        <f t="shared" ref="S18:S65" si="6">R18-N18</f>
+      <c r="T18">
+        <f t="shared" ref="T18:T65" si="6">S18-O18</f>
         <v>0.5</v>
       </c>
-      <c r="Z18">
+      <c r="AA18">
         <v>17</v>
       </c>
-      <c r="AA18">
+      <c r="AB18">
         <v>23</v>
       </c>
-      <c r="AB18" t="s">
-        <v>1</v>
-      </c>
       <c r="AC18" t="s">
         <v>1</v>
       </c>
-      <c r="AD18">
+      <c r="AD18" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE18">
         <v>24.15</v>
       </c>
-      <c r="AE18">
+      <c r="AF18">
         <v>8</v>
       </c>
-      <c r="AF18">
+      <c r="AG18">
         <v>4</v>
       </c>
-      <c r="AG18">
-        <v>2</v>
-      </c>
       <c r="AH18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>156</v>
       </c>
@@ -16702,3506 +16757,3647 @@
       <c r="C19">
         <v>2</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19" t="s">
         <v>6</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>155</v>
       </c>
-      <c r="F19" s="2">
+      <c r="G19" s="2">
         <v>45953</v>
       </c>
-      <c r="G19" s="10">
+      <c r="H19" s="10">
         <v>0.45833333333333331</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>0</v>
       </c>
-      <c r="I19">
-        <v>10</v>
-      </c>
       <c r="J19">
+        <v>10</v>
+      </c>
+      <c r="K19">
         <v>0.4506</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N19">
-        <v>10</v>
-      </c>
       <c r="O19">
+        <v>10</v>
+      </c>
+      <c r="P19">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S19">
+      <c r="T19">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z19">
+      <c r="AA19">
         <v>19</v>
       </c>
-      <c r="AA19">
+      <c r="AB19">
         <v>17</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="AC19" t="s">
         <v>162</v>
       </c>
-      <c r="AC19" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD19">
+      <c r="AD19" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE19">
         <v>25.35</v>
       </c>
-      <c r="AE19">
+      <c r="AF19">
         <v>12</v>
       </c>
-      <c r="AF19">
+      <c r="AG19">
         <v>7</v>
       </c>
-      <c r="AG19">
-        <v>2</v>
-      </c>
       <c r="AH19">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>156</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>3</v>
-      </c>
-      <c r="D20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20" t="s">
         <v>13</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>155</v>
       </c>
-      <c r="F20" s="2">
+      <c r="G20" s="2">
         <v>45953</v>
       </c>
-      <c r="G20" s="10">
+      <c r="H20" s="10">
         <v>0.45833333333333298</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>0</v>
       </c>
-      <c r="I20">
-        <v>10</v>
-      </c>
       <c r="J20">
+        <v>10</v>
+      </c>
+      <c r="K20">
         <v>0.47849999999999998</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N20">
-        <v>9</v>
-      </c>
       <c r="O20">
+        <v>9</v>
+      </c>
+      <c r="P20">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="Z20">
+      <c r="AA20">
         <v>20</v>
       </c>
-      <c r="AA20">
+      <c r="AB20">
         <v>14</v>
       </c>
-      <c r="AB20" t="s">
+      <c r="AC20" t="s">
         <v>162</v>
       </c>
-      <c r="AC20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD20">
+      <c r="AD20" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE20">
         <v>26.52</v>
       </c>
-      <c r="AE20">
+      <c r="AF20">
         <v>11</v>
       </c>
-      <c r="AF20">
+      <c r="AG20">
         <v>8</v>
       </c>
-      <c r="AG20">
-        <v>2</v>
-      </c>
       <c r="AH20">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>156</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
         <v>4</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>12</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>155</v>
       </c>
-      <c r="F21" s="2">
+      <c r="G21" s="2">
         <v>45953</v>
       </c>
-      <c r="G21" s="10">
+      <c r="H21" s="10">
         <v>0.45833333333333298</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>0</v>
       </c>
-      <c r="I21">
-        <v>10</v>
-      </c>
       <c r="J21">
+        <v>10</v>
+      </c>
+      <c r="K21">
         <v>0.4909</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N21">
-        <v>10</v>
-      </c>
       <c r="O21">
+        <v>10</v>
+      </c>
+      <c r="P21">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S21">
+      <c r="T21">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z21">
+      <c r="AA21">
         <v>21</v>
       </c>
-      <c r="AB21" t="s">
-        <v>1</v>
-      </c>
       <c r="AC21" t="s">
         <v>1</v>
       </c>
-      <c r="AD21">
+      <c r="AD21" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE21">
         <v>25.39</v>
       </c>
-      <c r="AE21">
-        <v>9</v>
-      </c>
       <c r="AF21">
+        <v>9</v>
+      </c>
+      <c r="AG21">
         <v>7</v>
       </c>
-      <c r="AG21">
-        <v>2</v>
-      </c>
       <c r="AH21">
         <v>2</v>
       </c>
-      <c r="AN21" t="s">
+      <c r="AI21">
+        <v>2</v>
+      </c>
+      <c r="AO21" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>156</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C22">
-        <v>5</v>
-      </c>
-      <c r="D22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
         <v>6</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>155</v>
       </c>
-      <c r="F22" s="2">
+      <c r="G22" s="2">
         <v>45953</v>
       </c>
-      <c r="G22" s="10">
+      <c r="H22" s="10">
         <v>0.45833333333333298</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>0</v>
       </c>
-      <c r="I22">
-        <v>10</v>
-      </c>
       <c r="J22">
+        <v>10</v>
+      </c>
+      <c r="K22">
         <v>0.47770000000000001</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>8</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S22">
+      <c r="T22">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="Z22">
+      <c r="AA22">
         <v>22</v>
       </c>
-      <c r="AB22" t="s">
-        <v>1</v>
-      </c>
       <c r="AC22" t="s">
         <v>1</v>
       </c>
-      <c r="AD22">
+      <c r="AD22" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE22">
         <v>28.55</v>
       </c>
-      <c r="AE22">
+      <c r="AF22">
         <v>17</v>
       </c>
-      <c r="AF22">
+      <c r="AG22">
         <v>8</v>
       </c>
-      <c r="AG22">
-        <v>2</v>
-      </c>
       <c r="AH22">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>156</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
         <v>6</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>13</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>155</v>
       </c>
-      <c r="F23" s="2">
+      <c r="G23" s="2">
         <v>45953</v>
       </c>
-      <c r="G23" s="10">
+      <c r="H23" s="10">
         <v>0.45833333333333298</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>0</v>
       </c>
-      <c r="I23">
-        <v>10</v>
-      </c>
       <c r="J23">
+        <v>10</v>
+      </c>
+      <c r="K23">
         <v>0.47989999999999999</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N23">
-        <v>10</v>
-      </c>
       <c r="O23">
+        <v>10</v>
+      </c>
+      <c r="P23">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z23">
+      <c r="AA23">
         <v>23</v>
       </c>
-      <c r="AA23">
-        <v>9</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>1</v>
+      <c r="AB23">
+        <v>9</v>
       </c>
       <c r="AC23" t="s">
         <v>1</v>
       </c>
-      <c r="AD23">
+      <c r="AD23" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE23">
         <v>24.46</v>
       </c>
-      <c r="AE23">
-        <v>10</v>
-      </c>
       <c r="AF23">
+        <v>10</v>
+      </c>
+      <c r="AG23">
         <v>8</v>
       </c>
-      <c r="AG23">
-        <v>2</v>
-      </c>
       <c r="AH23">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>156</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
         <v>7</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>12</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>155</v>
       </c>
-      <c r="F24" s="2">
+      <c r="G24" s="2">
         <v>45953</v>
       </c>
-      <c r="G24" s="10">
+      <c r="H24" s="10">
         <v>0.45833333333333298</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>0</v>
       </c>
-      <c r="I24">
-        <v>10</v>
-      </c>
       <c r="J24">
+        <v>10</v>
+      </c>
+      <c r="K24">
         <v>0.46079999999999999</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N24">
-        <v>10</v>
-      </c>
       <c r="O24">
+        <v>10</v>
+      </c>
+      <c r="P24">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S24">
+      <c r="T24">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z24">
+      <c r="AA24">
         <v>24</v>
       </c>
-      <c r="AB24" t="s">
-        <v>1</v>
-      </c>
       <c r="AC24" t="s">
         <v>1</v>
       </c>
-      <c r="AD24">
+      <c r="AD24" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE24">
         <v>28.59</v>
       </c>
-      <c r="AE24">
+      <c r="AF24">
         <v>15</v>
       </c>
-      <c r="AF24">
+      <c r="AG24">
         <v>8</v>
       </c>
-      <c r="AG24">
-        <v>1</v>
-      </c>
       <c r="AH24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="AI24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>156</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
         <v>8</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>6</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>155</v>
       </c>
-      <c r="F25" s="2">
+      <c r="G25" s="2">
         <v>45953</v>
       </c>
-      <c r="G25" s="10">
+      <c r="H25" s="10">
         <v>0.45833333333333298</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>0</v>
       </c>
-      <c r="I25">
-        <v>10</v>
-      </c>
       <c r="J25">
+        <v>10</v>
+      </c>
+      <c r="K25">
         <v>0.46360000000000001</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>9.5</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <f t="shared" si="1"/>
         <v>0.95</v>
       </c>
-      <c r="R25">
+      <c r="S25">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S25">
+      <c r="T25">
         <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
-      <c r="Z25">
+      <c r="AA25">
         <v>25</v>
       </c>
-      <c r="AA25">
+      <c r="AB25">
         <v>30</v>
       </c>
-      <c r="AB25" t="s">
-        <v>1</v>
-      </c>
       <c r="AC25" t="s">
         <v>1</v>
       </c>
-      <c r="AD25">
+      <c r="AD25" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE25">
         <v>26.55</v>
       </c>
-      <c r="AE25">
+      <c r="AF25">
         <v>13</v>
       </c>
-      <c r="AF25">
+      <c r="AG25">
         <v>7</v>
       </c>
-      <c r="AG25">
-        <v>2</v>
-      </c>
       <c r="AH25">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>156</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C26">
-        <v>9</v>
-      </c>
-      <c r="D26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26">
+        <v>9</v>
+      </c>
+      <c r="E26" t="s">
         <v>13</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>155</v>
       </c>
-      <c r="F26" s="2">
+      <c r="G26" s="2">
         <v>45953</v>
       </c>
-      <c r="G26" s="10">
+      <c r="H26" s="10">
         <v>0.45833333333333298</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>0</v>
       </c>
-      <c r="I26">
-        <v>10</v>
-      </c>
       <c r="J26">
+        <v>10</v>
+      </c>
+      <c r="K26">
         <v>0.50549999999999995</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N26">
-        <v>10</v>
-      </c>
       <c r="O26">
+        <v>10</v>
+      </c>
+      <c r="P26">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S26">
+      <c r="T26">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z26">
+      <c r="AA26">
         <v>26</v>
       </c>
-      <c r="AB26" t="s">
-        <v>1</v>
-      </c>
       <c r="AC26" t="s">
         <v>1</v>
       </c>
-      <c r="AD26">
+      <c r="AD26" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE26">
         <v>23.62</v>
-      </c>
-      <c r="AE26">
-        <v>8</v>
       </c>
       <c r="AF26">
         <v>8</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AH26">
         <v>2</v>
       </c>
-      <c r="AN26" t="s">
+      <c r="AI26">
+        <v>2</v>
+      </c>
+      <c r="AO26" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>156</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>10</v>
-      </c>
-      <c r="D27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>10</v>
+      </c>
+      <c r="E27" t="s">
         <v>12</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>155</v>
       </c>
-      <c r="F27" s="2">
+      <c r="G27" s="2">
         <v>45953</v>
       </c>
-      <c r="G27" s="10">
+      <c r="H27" s="10">
         <v>0.45833333333333298</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>0</v>
       </c>
-      <c r="I27">
-        <v>10</v>
-      </c>
       <c r="J27">
+        <v>10</v>
+      </c>
+      <c r="K27">
         <v>0.51680000000000004</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N27">
-        <v>10</v>
-      </c>
       <c r="O27">
+        <v>10</v>
+      </c>
+      <c r="P27">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S27">
+      <c r="T27">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z27">
+      <c r="AA27">
         <v>28</v>
       </c>
-      <c r="AB27" t="s">
-        <v>1</v>
-      </c>
       <c r="AC27" t="s">
         <v>1</v>
       </c>
-      <c r="AD27">
+      <c r="AD27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE27">
         <v>29.36</v>
       </c>
-      <c r="AE27">
+      <c r="AF27">
         <v>17</v>
       </c>
-      <c r="AF27">
+      <c r="AG27">
         <v>7</v>
       </c>
-      <c r="AG27">
-        <v>2</v>
-      </c>
       <c r="AH27">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>156</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
         <v>11</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>6</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>155</v>
       </c>
-      <c r="F28" s="2">
+      <c r="G28" s="2">
         <v>45953</v>
       </c>
-      <c r="G28" s="10">
+      <c r="H28" s="10">
         <v>0.45833333333333298</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>0</v>
       </c>
-      <c r="I28">
-        <v>10</v>
-      </c>
       <c r="J28">
+        <v>10</v>
+      </c>
+      <c r="K28">
         <v>0.47489999999999999</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N28">
-        <v>10</v>
-      </c>
       <c r="O28">
+        <v>10</v>
+      </c>
+      <c r="P28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R28">
+      <c r="S28">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S28">
+      <c r="T28">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z28">
+      <c r="AA28">
         <v>29</v>
       </c>
-      <c r="AA28">
+      <c r="AB28">
         <v>11</v>
       </c>
-      <c r="AB28" t="s">
-        <v>1</v>
-      </c>
       <c r="AC28" t="s">
         <v>1</v>
       </c>
-      <c r="AD28">
+      <c r="AD28" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE28">
         <v>29.46</v>
       </c>
-      <c r="AE28">
+      <c r="AF28">
         <v>17</v>
       </c>
-      <c r="AF28">
+      <c r="AG28">
         <v>8</v>
       </c>
-      <c r="AG28">
-        <v>2</v>
-      </c>
       <c r="AH28">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>156</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
         <v>12</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>13</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>155</v>
       </c>
-      <c r="F29" s="2">
+      <c r="G29" s="2">
         <v>45953</v>
       </c>
-      <c r="G29" s="10">
+      <c r="H29" s="10">
         <v>0.45833333333333298</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>0</v>
       </c>
-      <c r="I29">
-        <v>10</v>
-      </c>
       <c r="J29">
+        <v>10</v>
+      </c>
+      <c r="K29">
         <v>0.50090000000000001</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N29">
-        <v>10</v>
-      </c>
       <c r="O29">
+        <v>10</v>
+      </c>
+      <c r="P29">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S29">
+      <c r="T29">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z29">
+      <c r="AA29">
         <v>32</v>
       </c>
-      <c r="AA29">
+      <c r="AB29">
         <v>13</v>
       </c>
-      <c r="AB29" t="s">
-        <v>1</v>
-      </c>
       <c r="AC29" t="s">
         <v>1</v>
       </c>
-      <c r="AD29">
+      <c r="AD29" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE29">
         <v>23.96</v>
       </c>
-      <c r="AE29">
+      <c r="AF29">
         <v>8</v>
       </c>
-      <c r="AF29">
+      <c r="AG29">
         <v>6</v>
       </c>
-      <c r="AG29">
-        <v>2</v>
-      </c>
       <c r="AH29">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>156</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
         <v>13</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>12</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>155</v>
       </c>
-      <c r="F30" s="2">
+      <c r="G30" s="2">
         <v>45953</v>
       </c>
-      <c r="G30" s="10">
+      <c r="H30" s="10">
         <v>0.45833333333333298</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>0</v>
       </c>
-      <c r="I30">
-        <v>10</v>
-      </c>
       <c r="J30">
+        <v>10</v>
+      </c>
+      <c r="K30">
         <v>0.52549999999999997</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N30">
-        <v>10</v>
-      </c>
       <c r="O30">
+        <v>10</v>
+      </c>
+      <c r="P30">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S30">
+      <c r="T30">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z30">
+      <c r="AA30">
         <v>33</v>
       </c>
-      <c r="AB30" t="s">
-        <v>1</v>
-      </c>
       <c r="AC30" t="s">
         <v>1</v>
       </c>
-      <c r="AD30">
+      <c r="AD30" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE30">
         <v>24.83</v>
       </c>
-      <c r="AE30">
-        <v>10</v>
-      </c>
       <c r="AF30">
+        <v>10</v>
+      </c>
+      <c r="AG30">
         <v>8</v>
       </c>
-      <c r="AG30">
-        <v>2</v>
-      </c>
       <c r="AH30">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>156</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
         <v>14</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>6</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>155</v>
       </c>
-      <c r="F31" s="2">
+      <c r="G31" s="2">
         <v>45953</v>
       </c>
-      <c r="G31" s="10">
+      <c r="H31" s="10">
         <v>0.45833333333333298</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>0</v>
       </c>
-      <c r="I31">
-        <v>10</v>
-      </c>
       <c r="J31">
+        <v>10</v>
+      </c>
+      <c r="K31">
         <v>0.49430000000000002</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N31">
-        <v>10</v>
-      </c>
       <c r="O31">
+        <v>10</v>
+      </c>
+      <c r="P31">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S31">
+      <c r="T31">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z31">
+      <c r="AA31">
         <v>35</v>
       </c>
-      <c r="AB31" t="s">
-        <v>1</v>
-      </c>
       <c r="AC31" t="s">
         <v>1</v>
       </c>
-      <c r="AD31">
+      <c r="AD31" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE31">
         <v>28.52</v>
       </c>
-      <c r="AE31">
+      <c r="AF31">
         <v>14</v>
       </c>
-      <c r="AF31">
-        <v>5</v>
-      </c>
       <c r="AG31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AH31">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>156</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32">
         <v>15</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>13</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>155</v>
       </c>
-      <c r="F32" s="2">
+      <c r="G32" s="2">
         <v>45953</v>
       </c>
-      <c r="G32" s="10">
+      <c r="H32" s="10">
         <v>0.45833333333333298</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>0</v>
       </c>
-      <c r="I32">
-        <v>10</v>
-      </c>
       <c r="J32">
+        <v>10</v>
+      </c>
+      <c r="K32">
         <v>0.52490000000000003</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N32">
-        <v>10</v>
-      </c>
       <c r="O32">
+        <v>10</v>
+      </c>
+      <c r="P32">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R32">
+      <c r="S32">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S32">
+      <c r="T32">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z32">
+      <c r="AA32">
         <v>37</v>
       </c>
-      <c r="AB32" t="s">
-        <v>1</v>
-      </c>
       <c r="AC32" t="s">
         <v>1</v>
       </c>
-      <c r="AD32">
+      <c r="AD32" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE32">
         <v>26.6</v>
       </c>
-      <c r="AE32">
+      <c r="AF32">
         <v>13</v>
       </c>
-      <c r="AF32">
+      <c r="AG32">
         <v>8</v>
       </c>
-      <c r="AG32">
-        <v>2</v>
-      </c>
       <c r="AH32">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>156</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
         <v>16</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>12</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>155</v>
       </c>
-      <c r="F33" s="2">
+      <c r="G33" s="2">
         <v>45953</v>
       </c>
-      <c r="G33" s="10">
+      <c r="H33" s="10">
         <v>0.45833333333333298</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>0</v>
       </c>
-      <c r="I33">
-        <v>10</v>
-      </c>
       <c r="J33">
+        <v>10</v>
+      </c>
+      <c r="K33">
         <v>0.52170000000000005</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N33">
-        <v>9</v>
-      </c>
       <c r="O33">
+        <v>9</v>
+      </c>
+      <c r="P33">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="S33">
+      <c r="T33">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="Z33">
+      <c r="AA33">
         <v>39</v>
       </c>
-      <c r="AB33" t="s">
-        <v>1</v>
-      </c>
       <c r="AC33" t="s">
         <v>1</v>
       </c>
-      <c r="AD33">
+      <c r="AD33" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE33">
         <v>24.99</v>
       </c>
-      <c r="AE33">
-        <v>10</v>
-      </c>
       <c r="AF33">
+        <v>10</v>
+      </c>
+      <c r="AG33">
         <v>7</v>
       </c>
-      <c r="AG33">
-        <v>2</v>
-      </c>
       <c r="AH33">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>156</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
         <v>6</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>155</v>
       </c>
-      <c r="F34" s="2">
+      <c r="G34" s="2">
         <v>45958</v>
       </c>
-      <c r="G34" s="10">
+      <c r="H34" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H34">
-        <v>3</v>
-      </c>
       <c r="I34">
-        <v>10</v>
-      </c>
-      <c r="M34">
-        <f t="shared" ref="M34:M65" si="7">I34+L34</f>
+        <v>3</v>
+      </c>
+      <c r="J34">
         <v>10</v>
       </c>
       <c r="N34">
+        <f t="shared" ref="N34:N65" si="7">J34+M34</f>
         <v>10</v>
       </c>
       <c r="O34">
-        <f t="shared" ref="O34:O65" si="8">N34/M34</f>
-        <v>1</v>
-      </c>
-      <c r="R34">
-        <f t="shared" ref="R34:R65" si="9">I34+L34+P34</f>
-        <v>10</v>
+        <v>10</v>
+      </c>
+      <c r="P34">
+        <f t="shared" ref="P34:P65" si="8">O34/N34</f>
+        <v>1</v>
       </c>
       <c r="S34">
+        <f t="shared" ref="S34:S65" si="9">J34+M34+Q34</f>
+        <v>10</v>
+      </c>
+      <c r="T34">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z34">
+      <c r="AA34">
         <v>40</v>
       </c>
-      <c r="AA34">
+      <c r="AB34">
         <v>30</v>
       </c>
-      <c r="AB34" t="s">
-        <v>1</v>
-      </c>
       <c r="AC34" t="s">
         <v>1</v>
       </c>
-      <c r="AD34">
+      <c r="AD34" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE34">
         <v>23.44</v>
       </c>
-      <c r="AE34">
-        <v>10</v>
-      </c>
       <c r="AF34">
+        <v>10</v>
+      </c>
+      <c r="AG34">
         <v>8</v>
       </c>
-      <c r="AG34">
-        <v>2</v>
-      </c>
       <c r="AH34">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>156</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C35">
-        <v>2</v>
-      </c>
-      <c r="D35" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35" t="s">
         <v>13</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>155</v>
       </c>
-      <c r="F35" s="2">
+      <c r="G35" s="2">
         <v>45958</v>
       </c>
-      <c r="G35" s="10">
+      <c r="H35" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H35">
-        <v>3</v>
-      </c>
       <c r="I35">
-        <v>10</v>
-      </c>
-      <c r="M35">
+        <v>3</v>
+      </c>
+      <c r="J35">
+        <v>10</v>
+      </c>
+      <c r="N35">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>3.5</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
-      <c r="R35">
+      <c r="S35">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S35">
+      <c r="T35">
         <f t="shared" si="6"/>
         <v>6.5</v>
       </c>
-      <c r="Z35">
+      <c r="AA35">
         <v>41</v>
       </c>
-      <c r="AB35" t="s">
-        <v>1</v>
-      </c>
       <c r="AC35" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD35" t="s">
         <v>16</v>
       </c>
-      <c r="AD35">
+      <c r="AE35">
         <v>39.75</v>
       </c>
-      <c r="AE35">
+      <c r="AF35">
         <v>42</v>
       </c>
-      <c r="AF35">
+      <c r="AG35">
         <v>8</v>
       </c>
-      <c r="AG35">
-        <v>2</v>
-      </c>
       <c r="AH35">
         <v>2</v>
       </c>
-    </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>156</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C36">
         <v>3</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36" t="s">
         <v>12</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>155</v>
       </c>
-      <c r="F36" s="2">
+      <c r="G36" s="2">
         <v>45958</v>
       </c>
-      <c r="G36" s="10">
+      <c r="H36" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H36">
-        <v>3</v>
-      </c>
       <c r="I36">
-        <v>10</v>
-      </c>
-      <c r="M36">
+        <v>3</v>
+      </c>
+      <c r="J36">
+        <v>10</v>
+      </c>
+      <c r="N36">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>4.5</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <f t="shared" si="8"/>
         <v>0.45</v>
       </c>
-      <c r="R36">
+      <c r="S36">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S36">
+      <c r="T36">
         <f t="shared" si="6"/>
         <v>5.5</v>
       </c>
-      <c r="Z36">
+      <c r="AA36">
         <v>42</v>
       </c>
-      <c r="AA36">
+      <c r="AB36">
         <v>97</v>
       </c>
-      <c r="AB36" t="s">
-        <v>1</v>
-      </c>
       <c r="AC36" t="s">
         <v>1</v>
       </c>
-      <c r="AD36">
+      <c r="AD36" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE36">
         <v>29.75</v>
       </c>
-      <c r="AE36">
+      <c r="AF36">
         <v>16</v>
       </c>
-      <c r="AF36">
+      <c r="AG36">
         <v>6</v>
       </c>
-      <c r="AG36">
-        <v>1</v>
-      </c>
       <c r="AH36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="AI36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>156</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37">
         <v>4</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>6</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>155</v>
       </c>
-      <c r="F37" s="2">
+      <c r="G37" s="2">
         <v>45958</v>
       </c>
-      <c r="G37" s="10">
+      <c r="H37" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H37">
-        <v>3</v>
-      </c>
       <c r="I37">
-        <v>10</v>
-      </c>
-      <c r="M37">
+        <v>3</v>
+      </c>
+      <c r="J37">
+        <v>10</v>
+      </c>
+      <c r="N37">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>7</v>
       </c>
-      <c r="O37">
+      <c r="P37">
         <f t="shared" si="8"/>
         <v>0.7</v>
       </c>
-      <c r="R37">
+      <c r="S37">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S37">
+      <c r="T37">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="Z37">
+      <c r="AA37">
         <v>43</v>
       </c>
-      <c r="AA37">
+      <c r="AB37">
         <v>77</v>
       </c>
-      <c r="AB37" t="s">
-        <v>1</v>
-      </c>
       <c r="AC37" t="s">
         <v>1</v>
       </c>
-      <c r="AD37">
+      <c r="AD37" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE37">
         <v>26.6</v>
       </c>
-      <c r="AE37">
+      <c r="AF37">
         <v>13</v>
       </c>
-      <c r="AF37">
+      <c r="AG37">
         <v>7</v>
       </c>
-      <c r="AG37">
-        <v>2</v>
-      </c>
       <c r="AH37">
+        <v>2</v>
+      </c>
+      <c r="AI37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>156</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C38">
-        <v>5</v>
-      </c>
-      <c r="D38" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38">
+        <v>5</v>
+      </c>
+      <c r="E38" t="s">
         <v>13</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>155</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45958</v>
       </c>
-      <c r="G38" s="10">
+      <c r="H38" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H38">
-        <v>3</v>
-      </c>
       <c r="I38">
-        <v>10</v>
-      </c>
-      <c r="M38">
+        <v>3</v>
+      </c>
+      <c r="J38">
+        <v>10</v>
+      </c>
+      <c r="N38">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N38">
-        <v>5</v>
-      </c>
       <c r="O38">
+        <v>5</v>
+      </c>
+      <c r="P38">
         <f t="shared" si="8"/>
         <v>0.5</v>
       </c>
-      <c r="R38">
+      <c r="S38">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S38">
+      <c r="T38">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="Z38">
+      <c r="AA38">
         <v>44</v>
       </c>
-      <c r="AB38" t="s">
-        <v>1</v>
-      </c>
       <c r="AC38" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD38" t="s">
         <v>16</v>
       </c>
-      <c r="AD38">
+      <c r="AE38">
         <v>35.270000000000003</v>
       </c>
-      <c r="AE38">
+      <c r="AF38">
         <v>30</v>
       </c>
-      <c r="AF38">
+      <c r="AG38">
         <v>8</v>
       </c>
-      <c r="AG38">
-        <v>2</v>
-      </c>
       <c r="AH38">
         <v>2</v>
       </c>
-    </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>156</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39">
         <v>6</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>12</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>155</v>
       </c>
-      <c r="F39" s="2">
+      <c r="G39" s="2">
         <v>45958</v>
       </c>
-      <c r="G39" s="10">
+      <c r="H39" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H39">
-        <v>3</v>
-      </c>
       <c r="I39">
-        <v>10</v>
-      </c>
-      <c r="M39">
+        <v>3</v>
+      </c>
+      <c r="J39">
+        <v>10</v>
+      </c>
+      <c r="N39">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>8</v>
       </c>
-      <c r="O39">
+      <c r="P39">
         <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
-      <c r="R39">
+      <c r="S39">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S39">
+      <c r="T39">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="Z39">
+      <c r="AA39">
         <v>45</v>
       </c>
-      <c r="AB39" t="s">
-        <v>1</v>
-      </c>
       <c r="AC39" t="s">
         <v>1</v>
       </c>
-      <c r="AD39">
+      <c r="AD39" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE39">
         <v>25</v>
       </c>
-      <c r="AE39">
-        <v>10</v>
-      </c>
       <c r="AF39">
+        <v>10</v>
+      </c>
+      <c r="AG39">
         <v>8</v>
       </c>
-      <c r="AG39">
-        <v>1</v>
-      </c>
       <c r="AH39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="AI39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>156</v>
       </c>
       <c r="B40">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C40">
+        <v>3</v>
+      </c>
+      <c r="D40">
         <v>7</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>6</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>155</v>
       </c>
-      <c r="F40" s="2">
+      <c r="G40" s="2">
         <v>45958</v>
       </c>
-      <c r="G40" s="10">
+      <c r="H40" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H40">
-        <v>3</v>
-      </c>
       <c r="I40">
-        <v>10</v>
-      </c>
-      <c r="M40">
+        <v>3</v>
+      </c>
+      <c r="J40">
+        <v>10</v>
+      </c>
+      <c r="N40">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>8</v>
       </c>
-      <c r="O40">
+      <c r="P40">
         <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
-      <c r="R40">
+      <c r="S40">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S40">
+      <c r="T40">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="Z40">
+      <c r="AA40">
         <v>46</v>
       </c>
-      <c r="AB40" t="s">
-        <v>1</v>
-      </c>
       <c r="AC40" t="s">
         <v>1</v>
       </c>
-      <c r="AD40">
+      <c r="AD40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE40">
         <v>28.41</v>
       </c>
-      <c r="AE40">
+      <c r="AF40">
         <v>17</v>
       </c>
-      <c r="AF40">
+      <c r="AG40">
         <v>8</v>
       </c>
-      <c r="AG40">
-        <v>2</v>
-      </c>
       <c r="AH40">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>156</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C41">
+        <v>3</v>
+      </c>
+      <c r="D41">
         <v>8</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>13</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>155</v>
       </c>
-      <c r="F41" s="2">
+      <c r="G41" s="2">
         <v>45958</v>
       </c>
-      <c r="G41" s="10">
+      <c r="H41" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H41">
-        <v>3</v>
-      </c>
       <c r="I41">
-        <v>10</v>
-      </c>
-      <c r="M41">
+        <v>3</v>
+      </c>
+      <c r="J41">
+        <v>10</v>
+      </c>
+      <c r="N41">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N41">
+      <c r="O41">
         <v>7</v>
       </c>
-      <c r="O41">
+      <c r="P41">
         <f t="shared" si="8"/>
         <v>0.7</v>
       </c>
-      <c r="R41">
+      <c r="S41">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S41">
+      <c r="T41">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="Z41">
+      <c r="AA41">
         <v>47</v>
       </c>
-      <c r="AB41" t="s">
-        <v>1</v>
-      </c>
       <c r="AC41" t="s">
         <v>1</v>
       </c>
-      <c r="AD41">
+      <c r="AD41" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE41">
         <v>25.04</v>
       </c>
-      <c r="AE41">
+      <c r="AF41">
         <v>11</v>
       </c>
-      <c r="AF41">
+      <c r="AG41">
         <v>7</v>
       </c>
-      <c r="AG41">
-        <v>2</v>
-      </c>
       <c r="AH41">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>156</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C42">
-        <v>9</v>
-      </c>
-      <c r="D42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42">
+        <v>9</v>
+      </c>
+      <c r="E42" t="s">
         <v>12</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>155</v>
       </c>
-      <c r="F42" s="2">
+      <c r="G42" s="2">
         <v>45958</v>
       </c>
-      <c r="G42" s="10">
+      <c r="H42" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H42">
-        <v>3</v>
-      </c>
       <c r="I42">
-        <v>10</v>
-      </c>
-      <c r="M42">
+        <v>3</v>
+      </c>
+      <c r="J42">
+        <v>10</v>
+      </c>
+      <c r="N42">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N42">
-        <v>9</v>
-      </c>
       <c r="O42">
+        <v>9</v>
+      </c>
+      <c r="P42">
         <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
-      <c r="R42">
+      <c r="S42">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S42">
+      <c r="T42">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="Z42">
+      <c r="AA42">
         <v>48</v>
       </c>
-      <c r="AA42">
+      <c r="AB42">
         <v>99</v>
       </c>
-      <c r="AB42" t="s">
-        <v>1</v>
-      </c>
       <c r="AC42" t="s">
         <v>1</v>
       </c>
-      <c r="AD42">
+      <c r="AD42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE42">
         <v>25.24</v>
       </c>
-      <c r="AE42">
-        <v>10</v>
-      </c>
       <c r="AF42">
+        <v>10</v>
+      </c>
+      <c r="AG42">
         <v>4</v>
       </c>
-      <c r="AG42">
+      <c r="AH42">
         <v>0</v>
       </c>
-      <c r="AH42">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>156</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C43">
-        <v>10</v>
-      </c>
-      <c r="D43" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43">
+        <v>10</v>
+      </c>
+      <c r="E43" t="s">
         <v>6</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>155</v>
       </c>
-      <c r="F43" s="2">
+      <c r="G43" s="2">
         <v>45958</v>
       </c>
-      <c r="G43" s="10">
+      <c r="H43" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H43">
-        <v>3</v>
-      </c>
       <c r="I43">
-        <v>10</v>
-      </c>
-      <c r="M43">
+        <v>3</v>
+      </c>
+      <c r="J43">
+        <v>10</v>
+      </c>
+      <c r="N43">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N43">
-        <v>9</v>
-      </c>
       <c r="O43">
+        <v>9</v>
+      </c>
+      <c r="P43">
         <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
-      <c r="R43">
+      <c r="S43">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S43">
+      <c r="T43">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="Z43">
+      <c r="AA43">
         <v>49</v>
       </c>
-      <c r="AB43" t="s">
-        <v>1</v>
-      </c>
       <c r="AC43" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD43" t="s">
         <v>0</v>
       </c>
-      <c r="AD43">
+      <c r="AE43">
         <v>21.09</v>
       </c>
-      <c r="AE43">
+      <c r="AF43">
         <v>8</v>
       </c>
-      <c r="AF43">
+      <c r="AG43">
         <v>7</v>
       </c>
-      <c r="AG43">
-        <v>2</v>
-      </c>
       <c r="AH43">
         <v>2</v>
       </c>
-    </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>156</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44">
         <v>11</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>13</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>155</v>
       </c>
-      <c r="F44" s="2">
+      <c r="G44" s="2">
         <v>45958</v>
       </c>
-      <c r="G44" s="10">
+      <c r="H44" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H44">
-        <v>3</v>
-      </c>
       <c r="I44">
-        <v>10</v>
-      </c>
-      <c r="M44">
+        <v>3</v>
+      </c>
+      <c r="J44">
+        <v>10</v>
+      </c>
+      <c r="N44">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N44">
-        <v>10</v>
-      </c>
       <c r="O44">
+        <v>10</v>
+      </c>
+      <c r="P44">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="R44">
+      <c r="S44">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S44">
+      <c r="T44">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z44">
+      <c r="AA44">
         <v>50</v>
       </c>
-      <c r="AB44" t="s">
-        <v>1</v>
-      </c>
       <c r="AC44" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD44" t="s">
         <v>16</v>
       </c>
-      <c r="AD44">
+      <c r="AE44">
         <v>32.94</v>
       </c>
-      <c r="AE44">
+      <c r="AF44">
         <v>24</v>
       </c>
-      <c r="AF44">
+      <c r="AG44">
         <v>7</v>
       </c>
-      <c r="AG44">
-        <v>2</v>
-      </c>
       <c r="AH44">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>156</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45">
         <v>12</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>12</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>155</v>
       </c>
-      <c r="F45" s="2">
+      <c r="G45" s="2">
         <v>45958</v>
       </c>
-      <c r="G45" s="10">
+      <c r="H45" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H45">
-        <v>3</v>
-      </c>
       <c r="I45">
-        <v>10</v>
-      </c>
-      <c r="M45">
+        <v>3</v>
+      </c>
+      <c r="J45">
+        <v>10</v>
+      </c>
+      <c r="N45">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N45">
-        <v>5</v>
-      </c>
       <c r="O45">
+        <v>5</v>
+      </c>
+      <c r="P45">
         <f t="shared" si="8"/>
         <v>0.5</v>
       </c>
-      <c r="R45">
+      <c r="S45">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S45">
+      <c r="T45">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="Z45">
+      <c r="AA45">
         <v>51</v>
       </c>
-      <c r="AB45" t="s">
-        <v>1</v>
-      </c>
       <c r="AC45" t="s">
         <v>1</v>
       </c>
-      <c r="AD45">
+      <c r="AD45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE45">
         <v>26.97</v>
       </c>
-      <c r="AE45">
+      <c r="AF45">
         <v>13</v>
       </c>
-      <c r="AF45">
+      <c r="AG45">
         <v>8</v>
       </c>
-      <c r="AG45">
-        <v>2</v>
-      </c>
       <c r="AH45">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>156</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="D46">
         <v>13</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>6</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>155</v>
       </c>
-      <c r="F46" s="2">
+      <c r="G46" s="2">
         <v>45958</v>
       </c>
-      <c r="G46" s="10">
+      <c r="H46" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H46">
-        <v>3</v>
-      </c>
       <c r="I46">
-        <v>10</v>
-      </c>
-      <c r="M46">
+        <v>3</v>
+      </c>
+      <c r="J46">
+        <v>10</v>
+      </c>
+      <c r="N46">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N46">
+      <c r="O46">
         <v>7</v>
       </c>
-      <c r="O46">
+      <c r="P46">
         <f t="shared" si="8"/>
         <v>0.7</v>
       </c>
-      <c r="R46">
+      <c r="S46">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S46">
+      <c r="T46">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="Z46">
+      <c r="AA46">
         <v>52</v>
       </c>
-      <c r="AA46">
+      <c r="AB46">
         <v>26</v>
       </c>
-      <c r="AB46" t="s">
-        <v>1</v>
-      </c>
       <c r="AC46" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="s">
         <v>16</v>
       </c>
-      <c r="AD46">
+      <c r="AE46">
         <v>30.1</v>
       </c>
-      <c r="AE46">
+      <c r="AF46">
         <v>19</v>
       </c>
-      <c r="AF46">
+      <c r="AG46">
         <v>8</v>
       </c>
-      <c r="AG46">
-        <v>2</v>
-      </c>
       <c r="AH46">
         <v>2</v>
       </c>
-    </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>156</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47">
         <v>14</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>13</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>155</v>
       </c>
-      <c r="F47" s="2">
+      <c r="G47" s="2">
         <v>45958</v>
       </c>
-      <c r="G47" s="10">
+      <c r="H47" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H47">
-        <v>3</v>
-      </c>
       <c r="I47">
-        <v>10</v>
-      </c>
-      <c r="M47">
+        <v>3</v>
+      </c>
+      <c r="J47">
+        <v>10</v>
+      </c>
+      <c r="N47">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N47">
-        <v>9</v>
-      </c>
       <c r="O47">
+        <v>9</v>
+      </c>
+      <c r="P47">
         <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
-      <c r="R47">
+      <c r="S47">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S47">
+      <c r="T47">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="Z47">
+      <c r="AA47">
         <v>53</v>
       </c>
-      <c r="AA47">
+      <c r="AB47">
         <v>102</v>
       </c>
-      <c r="AB47" t="s">
-        <v>1</v>
-      </c>
       <c r="AC47" t="s">
         <v>1</v>
       </c>
-      <c r="AD47">
+      <c r="AD47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE47">
         <v>26.62</v>
       </c>
-      <c r="AE47">
+      <c r="AF47">
         <v>13</v>
       </c>
-      <c r="AF47">
+      <c r="AG47">
         <v>7</v>
       </c>
-      <c r="AG47">
-        <v>2</v>
-      </c>
       <c r="AH47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+        <v>2</v>
+      </c>
+      <c r="AI47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>156</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="C48">
+        <v>3</v>
+      </c>
+      <c r="D48">
         <v>15</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>12</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>155</v>
       </c>
-      <c r="F48" s="2">
+      <c r="G48" s="2">
         <v>45958</v>
       </c>
-      <c r="G48" s="10">
+      <c r="H48" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H48">
-        <v>3</v>
-      </c>
       <c r="I48">
-        <v>10</v>
-      </c>
-      <c r="M48">
+        <v>3</v>
+      </c>
+      <c r="J48">
+        <v>10</v>
+      </c>
+      <c r="N48">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N48">
-        <v>5</v>
-      </c>
       <c r="O48">
+        <v>5</v>
+      </c>
+      <c r="P48">
         <f t="shared" si="8"/>
         <v>0.5</v>
       </c>
-      <c r="R48">
+      <c r="S48">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S48">
+      <c r="T48">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="Z48">
+      <c r="AA48">
         <v>54</v>
       </c>
-      <c r="AB48" t="s">
-        <v>1</v>
-      </c>
       <c r="AC48" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD48" t="s">
         <v>16</v>
       </c>
-      <c r="AD48">
+      <c r="AE48">
         <v>38.04</v>
       </c>
-      <c r="AE48">
+      <c r="AF48">
         <v>34</v>
       </c>
-      <c r="AF48">
+      <c r="AG48">
         <v>7</v>
       </c>
-      <c r="AG48">
-        <v>2</v>
-      </c>
       <c r="AH48">
         <v>2</v>
       </c>
-    </row>
-    <row r="49" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>156</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49">
         <v>16</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>6</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>155</v>
       </c>
-      <c r="F49" s="2">
+      <c r="G49" s="2">
         <v>45958</v>
       </c>
-      <c r="G49" s="10">
+      <c r="H49" s="10">
         <v>0.41666666666666669</v>
       </c>
-      <c r="H49">
-        <v>3</v>
-      </c>
       <c r="I49">
-        <v>10</v>
-      </c>
-      <c r="M49">
+        <v>3</v>
+      </c>
+      <c r="J49">
+        <v>10</v>
+      </c>
+      <c r="N49">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N49">
-        <v>10</v>
-      </c>
       <c r="O49">
+        <v>10</v>
+      </c>
+      <c r="P49">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="R49">
+      <c r="S49">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S49">
+      <c r="T49">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z49">
+      <c r="AA49">
         <v>55</v>
       </c>
-      <c r="AA49">
+      <c r="AB49">
         <v>87</v>
       </c>
-      <c r="AB49" t="s">
-        <v>1</v>
-      </c>
       <c r="AC49" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD49" t="s">
         <v>0</v>
       </c>
-      <c r="AD49">
+      <c r="AE49">
         <v>21.59</v>
       </c>
-      <c r="AE49">
+      <c r="AF49">
         <v>8</v>
       </c>
-      <c r="AF49">
-        <v>5</v>
-      </c>
       <c r="AG49">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AH49">
         <v>2</v>
       </c>
-      <c r="AN49" t="s">
+      <c r="AI49">
+        <v>2</v>
+      </c>
+      <c r="AO49" t="s">
         <v>159</v>
       </c>
-      <c r="AO49" t="s">
+      <c r="AP49" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="50" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>156</v>
       </c>
       <c r="B50">
+        <v>33</v>
+      </c>
+      <c r="C50">
         <v>4</v>
       </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50" t="s">
         <v>13</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>155</v>
       </c>
-      <c r="F50" s="2">
+      <c r="G50" s="2">
         <v>45959</v>
       </c>
-      <c r="G50" s="10">
+      <c r="H50" s="10">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>4</v>
       </c>
-      <c r="I50">
-        <v>10</v>
-      </c>
-      <c r="M50">
+      <c r="J50">
+        <v>10</v>
+      </c>
+      <c r="N50">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N50">
+      <c r="O50">
         <v>9.5</v>
       </c>
-      <c r="O50">
+      <c r="P50">
         <f t="shared" si="8"/>
         <v>0.95</v>
       </c>
-      <c r="R50">
+      <c r="S50">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S50">
+      <c r="T50">
         <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
-      <c r="Z50">
+      <c r="AA50">
         <v>56</v>
       </c>
-      <c r="AA50">
+      <c r="AB50">
         <v>99</v>
       </c>
-      <c r="AB50" t="s">
-        <v>1</v>
-      </c>
       <c r="AC50" t="s">
         <v>1</v>
       </c>
-      <c r="AD50">
+      <c r="AD50" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE50">
         <v>27.07</v>
       </c>
-      <c r="AE50">
+      <c r="AF50">
         <v>12</v>
       </c>
-      <c r="AF50">
+      <c r="AG50">
         <v>8</v>
       </c>
-      <c r="AG50">
-        <v>1</v>
-      </c>
       <c r="AH50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="AI50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>156</v>
       </c>
       <c r="B51">
+        <v>34</v>
+      </c>
+      <c r="C51">
         <v>4</v>
       </c>
-      <c r="C51">
-        <v>2</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="D51">
+        <v>2</v>
+      </c>
+      <c r="E51" t="s">
         <v>12</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>155</v>
       </c>
-      <c r="F51" s="2">
+      <c r="G51" s="2">
         <v>45959</v>
       </c>
-      <c r="G51" s="10">
+      <c r="H51" s="10">
         <v>0.47916666666666669</v>
       </c>
-      <c r="H51">
+      <c r="I51">
         <v>4</v>
       </c>
-      <c r="I51">
-        <v>10</v>
-      </c>
-      <c r="M51">
+      <c r="J51">
+        <v>10</v>
+      </c>
+      <c r="N51">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N51">
+      <c r="O51">
         <v>6.5</v>
       </c>
-      <c r="O51">
+      <c r="P51">
         <f t="shared" si="8"/>
         <v>0.65</v>
       </c>
-      <c r="R51">
+      <c r="S51">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S51">
+      <c r="T51">
         <f t="shared" si="6"/>
         <v>3.5</v>
       </c>
-      <c r="Z51">
+      <c r="AA51">
         <v>57</v>
       </c>
-      <c r="AA51">
+      <c r="AB51">
         <v>41</v>
       </c>
-      <c r="AB51" t="s">
-        <v>1</v>
-      </c>
       <c r="AC51" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="s">
         <v>16</v>
       </c>
-      <c r="AD51">
+      <c r="AE51">
         <v>38.49</v>
       </c>
-      <c r="AE51">
+      <c r="AF51">
         <v>40</v>
       </c>
-      <c r="AF51">
+      <c r="AG51">
         <v>8</v>
       </c>
-      <c r="AG51">
-        <v>2</v>
-      </c>
       <c r="AH51">
         <v>2</v>
       </c>
-    </row>
-    <row r="52" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>156</v>
       </c>
       <c r="B52">
+        <v>35</v>
+      </c>
+      <c r="C52">
         <v>4</v>
       </c>
-      <c r="C52">
-        <v>3</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52" t="s">
         <v>6</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>155</v>
       </c>
-      <c r="F52" s="2">
+      <c r="G52" s="2">
         <v>45959</v>
       </c>
-      <c r="G52" s="10">
+      <c r="H52" s="10">
         <v>0.47916666666666702</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>4</v>
       </c>
-      <c r="I52">
-        <v>10</v>
-      </c>
-      <c r="M52">
+      <c r="J52">
+        <v>10</v>
+      </c>
+      <c r="N52">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N52">
+      <c r="O52">
         <v>8.5</v>
       </c>
-      <c r="O52">
+      <c r="P52">
         <f t="shared" si="8"/>
         <v>0.85</v>
       </c>
-      <c r="R52">
+      <c r="S52">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S52">
+      <c r="T52">
         <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
-      <c r="Z52">
+      <c r="AA52">
         <v>58</v>
       </c>
-      <c r="AA52">
+      <c r="AB52">
         <v>70</v>
       </c>
-      <c r="AB52" t="s">
-        <v>1</v>
-      </c>
       <c r="AC52" t="s">
         <v>1</v>
       </c>
-      <c r="AD52">
+      <c r="AD52" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE52">
         <v>25.21</v>
       </c>
-      <c r="AE52">
-        <v>10</v>
-      </c>
       <c r="AF52">
+        <v>10</v>
+      </c>
+      <c r="AG52">
         <v>6</v>
       </c>
-      <c r="AG52">
-        <v>1</v>
-      </c>
       <c r="AH52">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>156</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="C53">
         <v>4</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53">
+        <v>4</v>
+      </c>
+      <c r="E53" t="s">
         <v>13</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>155</v>
       </c>
-      <c r="F53" s="2">
+      <c r="G53" s="2">
         <v>45959</v>
       </c>
-      <c r="G53" s="10">
+      <c r="H53" s="10">
         <v>0.47916666666666702</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>4</v>
       </c>
-      <c r="I53">
-        <v>10</v>
-      </c>
-      <c r="M53">
+      <c r="J53">
+        <v>10</v>
+      </c>
+      <c r="N53">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N53">
+      <c r="O53">
         <v>8.5</v>
       </c>
-      <c r="O53">
+      <c r="P53">
         <f t="shared" si="8"/>
         <v>0.85</v>
       </c>
-      <c r="R53">
+      <c r="S53">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S53">
+      <c r="T53">
         <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
-      <c r="Z53">
+      <c r="AA53">
         <v>59</v>
       </c>
-      <c r="AA53">
+      <c r="AB53">
         <v>80</v>
       </c>
-      <c r="AB53" t="s">
-        <v>1</v>
-      </c>
       <c r="AC53" t="s">
         <v>1</v>
       </c>
-      <c r="AD53">
+      <c r="AD53" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE53">
         <v>25.84</v>
       </c>
-      <c r="AE53">
+      <c r="AF53">
         <v>14</v>
       </c>
-      <c r="AF53">
+      <c r="AG53">
         <v>8</v>
       </c>
-      <c r="AG53">
-        <v>2</v>
-      </c>
       <c r="AH53">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>156</v>
       </c>
       <c r="B54">
+        <v>37</v>
+      </c>
+      <c r="C54">
         <v>4</v>
       </c>
-      <c r="C54">
-        <v>5</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="D54">
+        <v>5</v>
+      </c>
+      <c r="E54" t="s">
         <v>12</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>155</v>
       </c>
-      <c r="F54" s="2">
+      <c r="G54" s="2">
         <v>45959</v>
       </c>
-      <c r="G54" s="10">
+      <c r="H54" s="10">
         <v>0.47916666666666702</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>4</v>
       </c>
-      <c r="I54">
-        <v>10</v>
-      </c>
-      <c r="M54">
+      <c r="J54">
+        <v>10</v>
+      </c>
+      <c r="N54">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N54">
-        <v>9</v>
-      </c>
       <c r="O54">
+        <v>9</v>
+      </c>
+      <c r="P54">
         <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
-      <c r="R54">
+      <c r="S54">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S54">
+      <c r="T54">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="Z54">
+      <c r="AA54">
         <v>60</v>
       </c>
-      <c r="AB54" t="s">
-        <v>1</v>
-      </c>
       <c r="AC54" t="s">
         <v>1</v>
       </c>
-      <c r="AD54">
+      <c r="AD54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE54">
         <v>23.41</v>
       </c>
-      <c r="AE54">
-        <v>9</v>
-      </c>
       <c r="AF54">
+        <v>9</v>
+      </c>
+      <c r="AG54">
         <v>8</v>
       </c>
-      <c r="AG54">
-        <v>1</v>
-      </c>
       <c r="AH54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="AI54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>156</v>
       </c>
       <c r="B55">
+        <v>38</v>
+      </c>
+      <c r="C55">
         <v>4</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>6</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>6</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>155</v>
       </c>
-      <c r="F55" s="2">
+      <c r="G55" s="2">
         <v>45959</v>
       </c>
-      <c r="G55" s="10">
+      <c r="H55" s="10">
         <v>0.47916666666666702</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>4</v>
       </c>
-      <c r="I55">
-        <v>10</v>
-      </c>
-      <c r="M55">
+      <c r="J55">
+        <v>10</v>
+      </c>
+      <c r="N55">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N55">
-        <v>9</v>
-      </c>
       <c r="O55">
+        <v>9</v>
+      </c>
+      <c r="P55">
         <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
-      <c r="R55">
+      <c r="S55">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S55">
+      <c r="T55">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="Z55">
+      <c r="AA55">
         <v>61</v>
       </c>
-      <c r="AA55">
+      <c r="AB55">
         <v>81</v>
       </c>
-      <c r="AB55" t="s">
-        <v>1</v>
-      </c>
       <c r="AC55" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD55" t="s">
         <v>16</v>
       </c>
-      <c r="AD55">
+      <c r="AE55">
         <v>30.38</v>
       </c>
-      <c r="AE55">
+      <c r="AF55">
         <v>22</v>
       </c>
-      <c r="AF55">
+      <c r="AG55">
         <v>8</v>
       </c>
-      <c r="AG55">
-        <v>2</v>
-      </c>
       <c r="AH55">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>156</v>
       </c>
       <c r="B56">
+        <v>39</v>
+      </c>
+      <c r="C56">
         <v>4</v>
       </c>
-      <c r="C56">
+      <c r="D56">
         <v>7</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>13</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>155</v>
       </c>
-      <c r="F56" s="2">
+      <c r="G56" s="2">
         <v>45959</v>
       </c>
-      <c r="G56" s="10">
+      <c r="H56" s="10">
         <v>0.47916666666666702</v>
       </c>
-      <c r="H56">
+      <c r="I56">
         <v>4</v>
       </c>
-      <c r="I56">
-        <v>10</v>
-      </c>
-      <c r="M56">
+      <c r="J56">
+        <v>10</v>
+      </c>
+      <c r="N56">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N56">
-        <v>10</v>
-      </c>
       <c r="O56">
+        <v>10</v>
+      </c>
+      <c r="P56">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="R56">
+      <c r="S56">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S56">
+      <c r="T56">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z56">
+      <c r="AA56">
         <v>62</v>
       </c>
-      <c r="AA56">
+      <c r="AB56">
         <v>92</v>
       </c>
-      <c r="AB56" t="s">
-        <v>1</v>
-      </c>
       <c r="AC56" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD56" t="s">
         <v>0</v>
       </c>
-      <c r="AD56">
+      <c r="AE56">
         <v>20.48</v>
       </c>
-      <c r="AE56">
+      <c r="AF56">
         <v>6</v>
       </c>
-      <c r="AF56">
+      <c r="AG56">
         <v>8</v>
       </c>
-      <c r="AG56">
-        <v>2</v>
-      </c>
       <c r="AH56">
         <v>2</v>
       </c>
-    </row>
-    <row r="57" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>156</v>
       </c>
       <c r="B57">
+        <v>40</v>
+      </c>
+      <c r="C57">
         <v>4</v>
       </c>
-      <c r="C57">
+      <c r="D57">
         <v>8</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>12</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>155</v>
       </c>
-      <c r="F57" s="2">
+      <c r="G57" s="2">
         <v>45959</v>
       </c>
-      <c r="G57" s="10">
+      <c r="H57" s="10">
         <v>0.47916666666666702</v>
       </c>
-      <c r="H57">
+      <c r="I57">
         <v>4</v>
       </c>
-      <c r="I57">
-        <v>10</v>
-      </c>
-      <c r="M57">
+      <c r="J57">
+        <v>10</v>
+      </c>
+      <c r="N57">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N57">
+      <c r="O57">
         <v>8.5</v>
       </c>
-      <c r="O57">
+      <c r="P57">
         <f t="shared" si="8"/>
         <v>0.85</v>
       </c>
-      <c r="R57">
+      <c r="S57">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S57">
+      <c r="T57">
         <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
-      <c r="Z57">
+      <c r="AA57">
         <v>63</v>
       </c>
-      <c r="AB57" t="s">
-        <v>1</v>
-      </c>
       <c r="AC57" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD57" t="s">
         <v>16</v>
       </c>
-      <c r="AD57">
+      <c r="AE57">
         <v>40.880000000000003</v>
       </c>
-      <c r="AE57">
+      <c r="AF57">
         <v>41</v>
       </c>
-      <c r="AF57">
+      <c r="AG57">
         <v>8</v>
       </c>
-      <c r="AG57">
-        <v>1</v>
-      </c>
       <c r="AH57">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="AI57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>156</v>
       </c>
       <c r="B58">
+        <v>41</v>
+      </c>
+      <c r="C58">
         <v>4</v>
       </c>
-      <c r="C58">
-        <v>9</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="D58">
+        <v>9</v>
+      </c>
+      <c r="E58" t="s">
         <v>6</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>155</v>
       </c>
-      <c r="F58" s="2">
+      <c r="G58" s="2">
         <v>45959</v>
       </c>
-      <c r="G58" s="10">
+      <c r="H58" s="10">
         <v>0.47916666666666702</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <v>4</v>
       </c>
-      <c r="I58">
-        <v>10</v>
-      </c>
-      <c r="M58">
+      <c r="J58">
+        <v>10</v>
+      </c>
+      <c r="N58">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N58">
-        <v>10</v>
-      </c>
       <c r="O58">
+        <v>10</v>
+      </c>
+      <c r="P58">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="R58">
+      <c r="S58">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S58">
+      <c r="T58">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z58">
+      <c r="AA58">
         <v>64</v>
       </c>
-      <c r="AA58">
+      <c r="AB58">
         <v>90</v>
       </c>
-      <c r="AB58" t="s">
-        <v>1</v>
-      </c>
       <c r="AC58" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD58" t="s">
         <v>16</v>
       </c>
-      <c r="AD58">
+      <c r="AE58">
         <v>31.11</v>
       </c>
-      <c r="AE58">
+      <c r="AF58">
         <v>20</v>
       </c>
-      <c r="AF58">
+      <c r="AG58">
         <v>7</v>
       </c>
-      <c r="AG58">
-        <v>2</v>
-      </c>
       <c r="AH58">
         <v>2</v>
       </c>
-    </row>
-    <row r="59" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>156</v>
       </c>
       <c r="B59">
+        <v>42</v>
+      </c>
+      <c r="C59">
         <v>4</v>
       </c>
-      <c r="C59">
-        <v>10</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="D59">
+        <v>10</v>
+      </c>
+      <c r="E59" t="s">
         <v>13</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>155</v>
       </c>
-      <c r="F59" s="2">
+      <c r="G59" s="2">
         <v>45959</v>
       </c>
-      <c r="G59" s="10">
+      <c r="H59" s="10">
         <v>0.47916666666666702</v>
       </c>
-      <c r="H59">
+      <c r="I59">
         <v>4</v>
       </c>
-      <c r="I59">
-        <v>10</v>
-      </c>
-      <c r="M59">
+      <c r="J59">
+        <v>10</v>
+      </c>
+      <c r="N59">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N59">
-        <v>1</v>
-      </c>
       <c r="O59">
+        <v>1</v>
+      </c>
+      <c r="P59">
         <f t="shared" si="8"/>
         <v>0.1</v>
       </c>
-      <c r="R59">
+      <c r="S59">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S59">
+      <c r="T59">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="Z59">
+      <c r="AA59">
         <v>65</v>
       </c>
-      <c r="AB59" t="s">
-        <v>1</v>
-      </c>
       <c r="AC59" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD59" t="s">
         <v>16</v>
       </c>
-      <c r="AD59">
+      <c r="AE59">
         <v>35.61</v>
       </c>
-      <c r="AE59">
+      <c r="AF59">
         <v>27</v>
       </c>
-      <c r="AF59">
+      <c r="AG59">
         <v>8</v>
       </c>
-      <c r="AG59">
-        <v>2</v>
-      </c>
       <c r="AH59">
         <v>2</v>
       </c>
-      <c r="AO59" t="s">
+      <c r="AI59">
+        <v>2</v>
+      </c>
+      <c r="AP59" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>156</v>
       </c>
       <c r="B60">
+        <v>43</v>
+      </c>
+      <c r="C60">
         <v>4</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>11</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>12</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>155</v>
       </c>
-      <c r="F60" s="2">
+      <c r="G60" s="2">
         <v>45959</v>
       </c>
-      <c r="G60" s="10">
+      <c r="H60" s="10">
         <v>0.47916666666666702</v>
       </c>
-      <c r="H60">
+      <c r="I60">
         <v>4</v>
       </c>
-      <c r="I60">
-        <v>10</v>
-      </c>
-      <c r="M60">
+      <c r="J60">
+        <v>10</v>
+      </c>
+      <c r="N60">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N60">
+      <c r="O60">
         <v>9.5</v>
       </c>
-      <c r="O60">
+      <c r="P60">
         <f t="shared" si="8"/>
         <v>0.95</v>
       </c>
-      <c r="R60">
+      <c r="S60">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S60">
+      <c r="T60">
         <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
-      <c r="Z60">
+      <c r="AA60">
         <v>66</v>
       </c>
-      <c r="AB60" t="s">
-        <v>1</v>
-      </c>
       <c r="AC60" t="s">
         <v>1</v>
       </c>
-      <c r="AD60">
+      <c r="AD60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE60">
         <v>28.04</v>
       </c>
-      <c r="AE60">
+      <c r="AF60">
         <v>15</v>
       </c>
-      <c r="AF60">
+      <c r="AG60">
         <v>8</v>
       </c>
-      <c r="AG60">
-        <v>2</v>
-      </c>
       <c r="AH60">
         <v>2</v>
       </c>
-    </row>
-    <row r="61" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>156</v>
       </c>
       <c r="B61">
+        <v>44</v>
+      </c>
+      <c r="C61">
         <v>4</v>
       </c>
-      <c r="C61">
+      <c r="D61">
         <v>12</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>6</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>155</v>
       </c>
-      <c r="F61" s="2">
+      <c r="G61" s="2">
         <v>45959</v>
       </c>
-      <c r="G61" s="10">
+      <c r="H61" s="10">
         <v>0.47916666666666702</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <v>4</v>
       </c>
-      <c r="I61">
-        <v>10</v>
-      </c>
-      <c r="M61">
+      <c r="J61">
+        <v>10</v>
+      </c>
+      <c r="N61">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N61">
-        <v>9</v>
-      </c>
       <c r="O61">
+        <v>9</v>
+      </c>
+      <c r="P61">
         <f t="shared" si="8"/>
         <v>0.9</v>
       </c>
-      <c r="R61">
+      <c r="S61">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S61">
+      <c r="T61">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="Z61">
+      <c r="AA61">
         <v>67</v>
       </c>
-      <c r="AA61">
+      <c r="AB61">
         <v>83</v>
       </c>
-      <c r="AB61" t="s">
-        <v>1</v>
-      </c>
       <c r="AC61" t="s">
         <v>1</v>
       </c>
-      <c r="AD61">
+      <c r="AD61" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE61">
         <v>28.37</v>
       </c>
-      <c r="AE61">
+      <c r="AF61">
         <v>15</v>
       </c>
-      <c r="AF61">
+      <c r="AG61">
         <v>8</v>
       </c>
-      <c r="AG61">
-        <v>2</v>
-      </c>
       <c r="AH61">
         <v>2</v>
       </c>
-    </row>
-    <row r="62" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>156</v>
       </c>
       <c r="B62">
+        <v>45</v>
+      </c>
+      <c r="C62">
         <v>4</v>
       </c>
-      <c r="C62">
+      <c r="D62">
         <v>13</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>13</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>155</v>
       </c>
-      <c r="F62" s="2">
+      <c r="G62" s="2">
         <v>45959</v>
       </c>
-      <c r="G62" s="10">
+      <c r="H62" s="10">
         <v>0.47916666666666702</v>
       </c>
-      <c r="H62">
+      <c r="I62">
         <v>4</v>
       </c>
-      <c r="I62">
-        <v>10</v>
-      </c>
-      <c r="M62">
+      <c r="J62">
+        <v>10</v>
+      </c>
+      <c r="N62">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N62">
+      <c r="O62">
         <v>8</v>
       </c>
-      <c r="O62">
+      <c r="P62">
         <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
-      <c r="R62">
+      <c r="S62">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S62">
+      <c r="T62">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="Z62">
+      <c r="AA62">
         <v>68</v>
       </c>
-      <c r="AB62" t="s">
-        <v>1</v>
-      </c>
       <c r="AC62" t="s">
         <v>1</v>
       </c>
-      <c r="AD62">
+      <c r="AD62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE62">
         <v>25.25</v>
       </c>
-      <c r="AE62">
+      <c r="AF62">
         <v>11</v>
       </c>
-      <c r="AF62">
+      <c r="AG62">
         <v>8</v>
       </c>
-      <c r="AG62">
-        <v>2</v>
-      </c>
       <c r="AH62">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>156</v>
       </c>
       <c r="B63">
+        <v>46</v>
+      </c>
+      <c r="C63">
         <v>4</v>
       </c>
-      <c r="C63">
+      <c r="D63">
         <v>14</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>12</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>155</v>
       </c>
-      <c r="F63" s="2">
+      <c r="G63" s="2">
         <v>45959</v>
       </c>
-      <c r="G63" s="10">
+      <c r="H63" s="10">
         <v>0.47916666666666702</v>
       </c>
-      <c r="H63">
+      <c r="I63">
         <v>4</v>
       </c>
-      <c r="I63">
-        <v>10</v>
-      </c>
-      <c r="M63">
+      <c r="J63">
+        <v>10</v>
+      </c>
+      <c r="N63">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N63">
+      <c r="O63">
         <v>9.5</v>
       </c>
-      <c r="O63">
+      <c r="P63">
         <f t="shared" si="8"/>
         <v>0.95</v>
       </c>
-      <c r="R63">
+      <c r="S63">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S63">
+      <c r="T63">
         <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
-      <c r="Z63">
+      <c r="AA63">
         <v>69</v>
       </c>
-      <c r="AA63">
+      <c r="AB63">
         <v>76</v>
       </c>
-      <c r="AB63" t="s">
-        <v>1</v>
-      </c>
       <c r="AC63" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD63" t="s">
         <v>16</v>
       </c>
-      <c r="AD63">
+      <c r="AE63">
         <v>30.46</v>
       </c>
-      <c r="AE63">
+      <c r="AF63">
         <v>20</v>
       </c>
-      <c r="AF63">
+      <c r="AG63">
         <v>8</v>
       </c>
-      <c r="AG63">
-        <v>2</v>
-      </c>
       <c r="AH63">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="1:41" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:42" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>156</v>
       </c>
       <c r="B64">
+        <v>47</v>
+      </c>
+      <c r="C64">
         <v>4</v>
       </c>
-      <c r="C64">
+      <c r="D64">
         <v>15</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>6</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>155</v>
       </c>
-      <c r="F64" s="2">
+      <c r="G64" s="2">
         <v>45959</v>
       </c>
-      <c r="G64" s="10">
+      <c r="H64" s="10">
         <v>0.47916666666666702</v>
       </c>
-      <c r="H64">
+      <c r="I64">
         <v>4</v>
       </c>
-      <c r="I64">
-        <v>10</v>
-      </c>
-      <c r="M64">
+      <c r="J64">
+        <v>10</v>
+      </c>
+      <c r="N64">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N64">
-        <v>10</v>
-      </c>
       <c r="O64">
+        <v>10</v>
+      </c>
+      <c r="P64">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="R64">
+      <c r="S64">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S64">
+      <c r="T64">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z64">
+      <c r="AA64">
         <v>70</v>
       </c>
-      <c r="AA64">
+      <c r="AB64">
         <v>79</v>
       </c>
-      <c r="AB64" t="s">
-        <v>1</v>
-      </c>
       <c r="AC64" t="s">
         <v>1</v>
       </c>
-      <c r="AD64">
+      <c r="AD64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE64">
         <v>24.78</v>
       </c>
-      <c r="AE64">
-        <v>10</v>
-      </c>
       <c r="AF64">
+        <v>10</v>
+      </c>
+      <c r="AG64">
         <v>6</v>
       </c>
-      <c r="AG64">
-        <v>2</v>
-      </c>
       <c r="AH64">
         <v>2</v>
       </c>
-    </row>
-    <row r="65" spans="1:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="AI64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:35" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>156</v>
       </c>
       <c r="B65">
+        <v>48</v>
+      </c>
+      <c r="C65">
         <v>4</v>
       </c>
-      <c r="C65">
+      <c r="D65">
         <v>16</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>13</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>155</v>
       </c>
-      <c r="F65" s="2">
+      <c r="G65" s="2">
         <v>45959</v>
       </c>
-      <c r="G65" s="10">
+      <c r="H65" s="10">
         <v>0.47916666666666702</v>
       </c>
-      <c r="H65">
+      <c r="I65">
         <v>4</v>
       </c>
-      <c r="I65">
-        <v>10</v>
-      </c>
-      <c r="M65">
+      <c r="J65">
+        <v>10</v>
+      </c>
+      <c r="N65">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="N65">
+      <c r="O65">
         <v>8</v>
       </c>
-      <c r="O65">
+      <c r="P65">
         <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
-      <c r="R65">
+      <c r="S65">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="S65">
+      <c r="T65">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="Z65">
+      <c r="AA65">
         <v>71</v>
       </c>
-      <c r="AB65" t="s">
-        <v>1</v>
-      </c>
       <c r="AC65" t="s">
         <v>1</v>
       </c>
-      <c r="AD65">
+      <c r="AD65" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE65">
         <v>24.34</v>
       </c>
-      <c r="AE65">
-        <v>9</v>
-      </c>
       <c r="AF65">
+        <v>9</v>
+      </c>
+      <c r="AG65">
         <v>8</v>
       </c>
-      <c r="AG65">
-        <v>2</v>
-      </c>
       <c r="AH65">
+        <v>2</v>
+      </c>
+      <c r="AI65">
         <v>1</v>
       </c>
     </row>

--- a/data/raw/NCE_data.xlsx
+++ b/data/raw/NCE_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://waikatouniversitynz-my.sharepoint.com/personal/or81_students_waikato_ac_nz/Documents/Documents/PhD/01_thesis_chapters/05_fear_study/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="8_{1C509BC5-B9CD-4355-A94E-B3E32C99D6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1685010-C209-4645-BD02-64B5452F4E5B}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="8_{1C509BC5-B9CD-4355-A94E-B3E32C99D6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{003AD1E5-8066-4073-A0FE-EAFF5DE9D967}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="5" xr2:uid="{884ED942-72D7-478A-91F6-B92A4F060477}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{884ED942-72D7-478A-91F6-B92A4F060477}"/>
   </bookViews>
   <sheets>
     <sheet name="NCE_exp" sheetId="2" r:id="rId1"/>
@@ -47,10 +47,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={3461571A-8435-47F5-932C-87907A560006}</author>
-    <author>tc={725FDFAA-9574-4676-B0CD-96F47B5BAC4E}</author>
-    <author>tc={2F95F192-4B86-4AC9-8D2D-24C01B901B1E}</author>
     <author>tc={8FD33AC5-01BC-4A61-82BE-07CE2703C754}</author>
-    <author>tc={DA4195C2-418A-4F3F-9226-CF4AB1AFECEF}</author>
   </authors>
   <commentList>
     <comment ref="E1" authorId="0" shapeId="0" xr:uid="{3461571A-8435-47F5-932C-87907A560006}">
@@ -61,36 +58,12 @@
     Treatment is applied by adding to the 7 Liter in the tank an extra Liter of water coming from the catfish or eel holding tanks or a Liter of dechlorinaded tab water.</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{725FDFAA-9574-4676-B0CD-96F47B5BAC4E}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Pellets left after this time</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="2" shapeId="0" xr:uid="{2F95F192-4B86-4AC9-8D2D-24C01B901B1E}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Extra food given when less than 3 pellets left. Than 5 new given</t>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="3" shapeId="0" xr:uid="{8FD33AC5-01BC-4A61-82BE-07CE2703C754}">
+    <comment ref="M1" authorId="1" shapeId="0" xr:uid="{8FD33AC5-01BC-4A61-82BE-07CE2703C754}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Light might not have gone out for round 1 due to error with the lighting from now fixed and day is 7:00-20:00</t>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="4" shapeId="0" xr:uid="{DA4195C2-418A-4F3F-9226-CF4AB1AFECEF}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Extra food given when less than 3 pellets left. Than 5 new given</t>
       </text>
     </comment>
   </commentList>
@@ -152,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4026" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3911" uniqueCount="197">
   <si>
     <t>S</t>
   </si>
@@ -732,6 +705,18 @@
   <si>
     <t>probably error in length measurment</t>
   </si>
+  <si>
+    <t>size_mm</t>
+  </si>
+  <si>
+    <t>legs</t>
+  </si>
+  <si>
+    <t>claws</t>
+  </si>
+  <si>
+    <t>antenna</t>
+  </si>
 </sst>
 </file>
 
@@ -820,7 +805,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -836,7 +821,6 @@
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
@@ -1182,17 +1166,8 @@
   <threadedComment ref="E1" dT="2025-10-07T22:37:37.41" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{3461571A-8435-47F5-932C-87907A560006}">
     <text>Treatment is applied by adding to the 7 Liter in the tank an extra Liter of water coming from the catfish or eel holding tanks or a Liter of dechlorinaded tab water.</text>
   </threadedComment>
-  <threadedComment ref="L1" dT="2025-10-07T22:21:57.50" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{725FDFAA-9574-4676-B0CD-96F47B5BAC4E}">
-    <text>Pellets left after this time</text>
-  </threadedComment>
-  <threadedComment ref="M1" dT="2025-10-07T22:32:08.27" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{2F95F192-4B86-4AC9-8D2D-24C01B901B1E}">
-    <text>Extra food given when less than 3 pellets left. Than 5 new given</text>
-  </threadedComment>
-  <threadedComment ref="O1" dT="2025-10-07T22:28:09.61" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{8FD33AC5-01BC-4A61-82BE-07CE2703C754}">
+  <threadedComment ref="M1" dT="2025-10-07T22:28:09.61" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{8FD33AC5-01BC-4A61-82BE-07CE2703C754}">
     <text>Light might not have gone out for round 1 due to error with the lighting from now fixed and day is 7:00-20:00</text>
-  </threadedComment>
-  <threadedComment ref="Q1" dT="2025-10-07T22:32:08.27" personId="{4724CB31-5F20-483E-A3EB-ECD5F8F6A30B}" id="{DA4195C2-418A-4F3F-9226-CF4AB1AFECEF}">
-    <text>Extra food given when less than 3 pellets left. Than 5 new given</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -1284,7 +1259,7 @@
     <col min="61" max="61" width="7.20703125" bestFit="1" customWidth="1"/>
     <col min="62" max="62" width="8.5234375" bestFit="1" customWidth="1"/>
     <col min="63" max="63" width="10.41796875" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11.26171875" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="14.15625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
@@ -1502,7 +1477,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:71" s="16" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:71" s="15" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -1524,136 +1499,136 @@
       <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="M2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="P2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="R2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="S2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="T2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="U2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="V2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="W2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="X2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AN2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AQ2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AR2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AT2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AU2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AV2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AX2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY2" s="17" t="s">
+      <c r="I2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="R2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="S2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="T2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="U2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="V2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="W2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="X2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AV2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW2" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AX2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY2" s="16" t="s">
         <v>3</v>
       </c>
       <c r="BA2">
@@ -2996,7 +2971,7 @@
         <v>45924</v>
       </c>
     </row>
-    <row r="10" spans="1:71" s="16" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:71" s="15" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -3018,131 +2993,131 @@
       <c r="G10" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="16" t="s">
+      <c r="I10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="M10" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="N10" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="O10" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="P10" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q10" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="R10" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="S10" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="T10" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="U10" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="V10" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="W10" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="X10" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y10" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z10" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA10" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB10" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC10" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD10" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE10" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF10" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG10" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH10" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI10" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK10" s="17"/>
-      <c r="AL10" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM10" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AN10" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO10" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP10" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AQ10" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AR10" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS10" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AT10" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AU10" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AV10" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW10" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AX10" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY10" s="17" t="s">
+      <c r="K10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="P10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="S10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="T10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="U10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="V10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="W10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="X10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF10" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH10" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK10" s="16"/>
+      <c r="AL10" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN10" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP10" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR10" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT10" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AV10" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AX10" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY10" s="16" t="s">
         <v>3</v>
       </c>
       <c r="BA10">
@@ -4468,7 +4443,7 @@
       </c>
       <c r="BR17" s="2"/>
     </row>
-    <row r="18" spans="1:70" s="16" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:70" s="15" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -4490,76 +4465,76 @@
       <c r="G18" t="s">
         <v>6</v>
       </c>
-      <c r="H18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="K18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="M18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="O18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="S18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="U18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="W18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="X18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE18" s="16" t="s">
+      <c r="H18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="15" t="s">
         <v>3</v>
       </c>
       <c r="AF18" t="s">
@@ -4568,53 +4543,53 @@
       <c r="AG18" t="s">
         <v>3</v>
       </c>
-      <c r="AH18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK18" s="17"/>
-      <c r="AL18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AN18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AQ18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AR18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AT18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AU18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AV18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AX18" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY18" s="17" t="s">
+      <c r="AH18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK18" s="16"/>
+      <c r="AL18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AV18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AX18" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY18" s="16" t="s">
         <v>3</v>
       </c>
       <c r="BA18">
@@ -5926,7 +5901,7 @@
       </c>
       <c r="BR25" s="2"/>
     </row>
-    <row r="26" spans="1:70" s="16" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:70" s="15" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -5948,131 +5923,131 @@
       <c r="G26" t="s">
         <v>12</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="I26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="K26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="M26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="O26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="S26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="U26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="W26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="X26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK26" s="17"/>
-      <c r="AL26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AN26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AQ26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AR26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AS26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AT26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AU26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AV26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="AX26" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY26" s="17" t="s">
+      <c r="I26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="U26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="W26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK26" s="16"/>
+      <c r="AL26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AS26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AU26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AV26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="AX26" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY26" s="16" t="s">
         <v>3</v>
       </c>
       <c r="BA26">
@@ -14829,13 +14804,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{853DF2F7-7B07-467C-B845-65DDCE944602}">
-  <dimension ref="A1:AP65"/>
+  <dimension ref="A1:Y49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="7" max="7" width="9.83984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5234375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.9453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="18" max="18" width="9.15625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="4" t="s">
         <v>135</v>
       </c>
@@ -14870,5741 +14852,3396 @@
         <v>180</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>176</v>
+        <v>46</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>175</v>
+        <v>45</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>174</v>
+        <v>43</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>173</v>
+        <v>42</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG1" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH1" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="AJ1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="AL1" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="AM1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="AN1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AO1" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="AP1" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
         <v>156</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H2" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="J2">
+        <v>10</v>
+      </c>
+      <c r="K2">
+        <v>0.47839999999999999</v>
+      </c>
+      <c r="L2">
+        <f>J2</f>
+        <v>10</v>
+      </c>
+      <c r="M2">
+        <v>9.5</v>
+      </c>
+      <c r="N2">
+        <f>M2/L2</f>
+        <v>0.95</v>
+      </c>
+      <c r="O2">
+        <v>17</v>
+      </c>
+      <c r="P2">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>24.15</v>
+      </c>
+      <c r="T2">
+        <v>8</v>
+      </c>
+      <c r="U2">
+        <v>4</v>
+      </c>
+      <c r="V2">
+        <v>2</v>
+      </c>
+      <c r="W2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G3" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H3" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>0.4506</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L49" si="0">J3</f>
+        <v>10</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N17" si="1">M3/L3</f>
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3">
+        <v>17</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>162</v>
+      </c>
+      <c r="R3" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>25.35</v>
+      </c>
+      <c r="T3">
+        <v>12</v>
+      </c>
+      <c r="U3">
+        <v>7</v>
+      </c>
+      <c r="V3">
+        <v>2</v>
+      </c>
+      <c r="W3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G2" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H2" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I2" s="3">
-        <v>2</v>
-      </c>
-      <c r="J2" s="3">
-        <v>5</v>
-      </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3">
-        <v>2</v>
-      </c>
-      <c r="M2" s="3">
-        <v>5</v>
-      </c>
-      <c r="N2" s="3">
-        <f t="shared" ref="N2:N33" si="0">J2+M2</f>
-        <v>10</v>
-      </c>
-      <c r="O2" s="3">
+      <c r="F4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G4" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>10</v>
+      </c>
+      <c r="K4">
+        <v>0.47849999999999998</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M4">
+        <v>9</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="1"/>
+        <v>0.9</v>
+      </c>
+      <c r="O4">
+        <v>20</v>
+      </c>
+      <c r="P4">
+        <v>14</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>162</v>
+      </c>
+      <c r="R4" t="s">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>26.52</v>
+      </c>
+      <c r="T4">
+        <v>11</v>
+      </c>
+      <c r="U4">
+        <v>8</v>
+      </c>
+      <c r="V4">
+        <v>2</v>
+      </c>
+      <c r="W4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G5" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>0.4909</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M5">
+        <v>10</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>21</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>25.39</v>
+      </c>
+      <c r="T5">
+        <v>9</v>
+      </c>
+      <c r="U5">
         <v>7</v>
       </c>
-      <c r="P2" s="3">
-        <f t="shared" ref="P2:P33" si="1">O2/N2</f>
-        <v>0.7</v>
-      </c>
-      <c r="Q2" s="3">
+      <c r="V5">
+        <v>2</v>
+      </c>
+      <c r="W5">
+        <v>2</v>
+      </c>
+      <c r="X5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="R2" s="3">
-        <v>2</v>
-      </c>
-      <c r="S2" s="3">
-        <f t="shared" ref="S2:S33" si="2">J2+M2+Q2</f>
-        <v>10</v>
-      </c>
-      <c r="T2" s="3">
-        <f t="shared" ref="T2:T17" si="3">S2-R2</f>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>0.47770000000000001</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M6">
         <v>8</v>
       </c>
-      <c r="U2" s="10">
-        <f>S2*pellet_weigth!$B$3</f>
-        <v>0.54136666666666644</v>
-      </c>
-      <c r="V2" s="3">
-        <v>5.3125999999999998</v>
-      </c>
-      <c r="W2" s="3">
-        <v>5.3324999999999996</v>
-      </c>
-      <c r="X2" s="3">
-        <f t="shared" ref="X2:X17" si="4">W2-V2</f>
-        <v>1.9899999999999807E-2</v>
-      </c>
-      <c r="Y2" s="10">
-        <f t="shared" ref="Y2:Y17" si="5">U2-X2</f>
-        <v>0.52146666666666663</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA2" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="3">
-        <v>27</v>
-      </c>
-      <c r="AC2" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="3">
-        <v>28.66</v>
-      </c>
-      <c r="AF2" s="3">
-        <v>16</v>
-      </c>
-      <c r="AG2" s="3">
-        <v>8</v>
-      </c>
-      <c r="AH2" s="3">
-        <v>2</v>
-      </c>
-      <c r="AI2" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ2" s="3"/>
-      <c r="AK2" s="3"/>
-      <c r="AL2" s="3"/>
-      <c r="AM2" s="3"/>
-      <c r="AN2" s="3"/>
-      <c r="AO2" s="3"/>
-      <c r="AP2" s="3"/>
-    </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G3" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H3" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I3" s="3">
-        <v>2</v>
-      </c>
-      <c r="J3" s="3">
-        <v>5</v>
-      </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3">
-        <v>5</v>
-      </c>
-      <c r="M3" s="3">
-        <v>0</v>
-      </c>
-      <c r="N3" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O3" s="3">
-        <v>5</v>
-      </c>
-      <c r="P3" s="3">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>0</v>
-      </c>
-      <c r="R3" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="S3" s="3">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="T3" s="3">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="U3" s="10">
-        <f>S3*pellet_weigth!$B$3</f>
-        <v>0.27068333333333322</v>
-      </c>
-      <c r="V3" s="3">
-        <v>5.3052999999999999</v>
-      </c>
-      <c r="W3" s="3">
-        <v>5.3487999999999998</v>
-      </c>
-      <c r="X3" s="3">
-        <f t="shared" si="4"/>
-        <v>4.3499999999999872E-2</v>
-      </c>
-      <c r="Y3" s="10">
-        <f t="shared" si="5"/>
-        <v>0.22718333333333335</v>
-      </c>
-      <c r="Z3" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA3" s="3">
-        <v>2</v>
-      </c>
-      <c r="AB3" s="3">
-        <v>30</v>
-      </c>
-      <c r="AC3" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="3">
-        <v>27.29</v>
-      </c>
-      <c r="AF3" s="3">
-        <v>12</v>
-      </c>
-      <c r="AG3" s="3">
-        <v>8</v>
-      </c>
-      <c r="AH3" s="3">
-        <v>2</v>
-      </c>
-      <c r="AI3" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="3"/>
-      <c r="AL3" s="3"/>
-      <c r="AM3" s="3"/>
-      <c r="AN3" s="3"/>
-      <c r="AO3" s="3"/>
-      <c r="AP3" s="3"/>
-    </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
-        <v>3</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G4" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H4" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I4" s="3">
-        <v>2</v>
-      </c>
-      <c r="J4" s="3">
-        <v>5</v>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3">
-        <v>5</v>
-      </c>
-      <c r="N4" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O4" s="3">
-        <v>1</v>
-      </c>
-      <c r="P4" s="3">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>5</v>
-      </c>
-      <c r="R4" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="S4" s="3">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="T4" s="3">
-        <f t="shared" si="3"/>
-        <v>10.5</v>
-      </c>
-      <c r="U4" s="10">
-        <f>S4*pellet_weigth!$B$3</f>
-        <v>0.81204999999999972</v>
-      </c>
-      <c r="V4" s="3">
-        <v>5.3022</v>
-      </c>
-      <c r="W4" s="3">
-        <v>5.4924999999999997</v>
-      </c>
-      <c r="X4" s="3">
-        <f t="shared" si="4"/>
-        <v>0.19029999999999969</v>
-      </c>
-      <c r="Y4" s="10">
-        <f t="shared" si="5"/>
-        <v>0.62175000000000002</v>
-      </c>
-      <c r="Z4" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB4" s="3">
-        <v>18</v>
-      </c>
-      <c r="AC4" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="3">
-        <v>28.54</v>
-      </c>
-      <c r="AF4" s="3">
-        <v>16</v>
-      </c>
-      <c r="AG4" s="3">
-        <v>8</v>
-      </c>
-      <c r="AH4" s="3">
-        <v>2</v>
-      </c>
-      <c r="AI4" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ4" s="3"/>
-      <c r="AK4" s="3"/>
-      <c r="AL4" s="3"/>
-      <c r="AM4" s="3"/>
-      <c r="AN4" s="3"/>
-      <c r="AO4" s="3"/>
-      <c r="AP4" s="3"/>
-    </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3">
-        <v>4</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G5" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H5" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I5" s="3">
-        <v>2</v>
-      </c>
-      <c r="J5" s="3">
-        <v>5</v>
-      </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3">
-        <v>4</v>
-      </c>
-      <c r="M5" s="3">
-        <v>0</v>
-      </c>
-      <c r="N5" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O5" s="3">
-        <v>4</v>
-      </c>
-      <c r="P5" s="3">
+      <c r="N6">
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="O6">
+        <v>22</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" t="s">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>28.55</v>
+      </c>
+      <c r="T6">
+        <v>17</v>
+      </c>
+      <c r="U6">
+        <v>8</v>
+      </c>
+      <c r="V6">
+        <v>2</v>
+      </c>
+      <c r="W6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="R5" s="3">
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
+        <v>0.47989999999999999</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M7">
+        <v>10</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>23</v>
+      </c>
+      <c r="P7">
+        <v>9</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7" t="s">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>24.46</v>
+      </c>
+      <c r="T7">
+        <v>10</v>
+      </c>
+      <c r="U7">
+        <v>8</v>
+      </c>
+      <c r="V7">
+        <v>2</v>
+      </c>
+      <c r="W7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H8" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="I8">
         <v>0</v>
       </c>
-      <c r="S5" s="3">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="T5" s="3">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="U5" s="10">
-        <f>S5*pellet_weigth!$B$3</f>
-        <v>0.27068333333333322</v>
-      </c>
-      <c r="V5" s="3">
-        <v>5.3243999999999998</v>
-      </c>
-      <c r="W5" s="3">
-        <v>5.3719000000000001</v>
-      </c>
-      <c r="X5" s="3">
-        <f t="shared" si="4"/>
-        <v>4.750000000000032E-2</v>
-      </c>
-      <c r="Y5" s="10">
-        <f t="shared" si="5"/>
-        <v>0.2231833333333329</v>
-      </c>
-      <c r="Z5" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA5" s="3">
-        <v>4</v>
-      </c>
-      <c r="AB5" s="3">
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>0.46079999999999999</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M8">
+        <v>10</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>24</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8" t="s">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>28.59</v>
+      </c>
+      <c r="T8">
+        <v>15</v>
+      </c>
+      <c r="U8">
+        <v>8</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>155</v>
+      </c>
+      <c r="G9" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+      <c r="K9">
+        <v>0.46360000000000001</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M9">
+        <v>9.5</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="1"/>
+        <v>0.95</v>
+      </c>
+      <c r="O9">
+        <v>25</v>
+      </c>
+      <c r="P9">
+        <v>30</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" t="s">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>26.55</v>
+      </c>
+      <c r="T9">
+        <v>13</v>
+      </c>
+      <c r="U9">
         <v>7</v>
       </c>
-      <c r="AC5" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD5" s="3" t="s">
+      <c r="V9">
+        <v>2</v>
+      </c>
+      <c r="W9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>155</v>
+      </c>
+      <c r="G10" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>10</v>
+      </c>
+      <c r="K10">
+        <v>0.50549999999999995</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M10">
+        <v>10</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>26</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" t="s">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>23.62</v>
+      </c>
+      <c r="T10">
+        <v>8</v>
+      </c>
+      <c r="U10">
+        <v>8</v>
+      </c>
+      <c r="V10">
+        <v>2</v>
+      </c>
+      <c r="W10">
+        <v>2</v>
+      </c>
+      <c r="X10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>155</v>
+      </c>
+      <c r="G11" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
+      <c r="K11">
+        <v>0.51680000000000004</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>28</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>1</v>
+      </c>
+      <c r="R11" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>29.36</v>
+      </c>
+      <c r="T11">
+        <v>17</v>
+      </c>
+      <c r="U11">
+        <v>7</v>
+      </c>
+      <c r="V11">
+        <v>2</v>
+      </c>
+      <c r="W11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>155</v>
+      </c>
+      <c r="G12" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>10</v>
+      </c>
+      <c r="K12">
+        <v>0.47489999999999999</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M12">
+        <v>10</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>29</v>
+      </c>
+      <c r="P12">
+        <v>11</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>1</v>
+      </c>
+      <c r="R12" t="s">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>29.46</v>
+      </c>
+      <c r="T12">
+        <v>17</v>
+      </c>
+      <c r="U12">
+        <v>8</v>
+      </c>
+      <c r="V12">
+        <v>2</v>
+      </c>
+      <c r="W12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>155</v>
+      </c>
+      <c r="G13" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>10</v>
+      </c>
+      <c r="K13">
+        <v>0.50090000000000001</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M13">
+        <v>10</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>32</v>
+      </c>
+      <c r="P13">
+        <v>13</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>1</v>
+      </c>
+      <c r="R13" t="s">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>23.96</v>
+      </c>
+      <c r="T13">
+        <v>8</v>
+      </c>
+      <c r="U13">
+        <v>6</v>
+      </c>
+      <c r="V13">
+        <v>2</v>
+      </c>
+      <c r="W13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>155</v>
+      </c>
+      <c r="G14" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>10</v>
+      </c>
+      <c r="K14">
+        <v>0.52549999999999997</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M14">
+        <v>10</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>33</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>1</v>
+      </c>
+      <c r="R14" t="s">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>24.83</v>
+      </c>
+      <c r="T14">
+        <v>10</v>
+      </c>
+      <c r="U14">
+        <v>8</v>
+      </c>
+      <c r="V14">
+        <v>2</v>
+      </c>
+      <c r="W14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>156</v>
+      </c>
+      <c r="B15">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>155</v>
+      </c>
+      <c r="G15" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>10</v>
+      </c>
+      <c r="K15">
+        <v>0.49430000000000002</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M15">
+        <v>10</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>35</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>1</v>
+      </c>
+      <c r="R15" t="s">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>28.52</v>
+      </c>
+      <c r="T15">
+        <v>14</v>
+      </c>
+      <c r="U15">
+        <v>5</v>
+      </c>
+      <c r="V15">
+        <v>2</v>
+      </c>
+      <c r="W15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>155</v>
+      </c>
+      <c r="G16" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H16" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>10</v>
+      </c>
+      <c r="K16">
+        <v>0.52490000000000003</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M16">
+        <v>10</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>37</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>1</v>
+      </c>
+      <c r="R16" t="s">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>26.6</v>
+      </c>
+      <c r="T16">
+        <v>13</v>
+      </c>
+      <c r="U16">
+        <v>8</v>
+      </c>
+      <c r="V16">
+        <v>2</v>
+      </c>
+      <c r="W16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B17">
         <v>16</v>
       </c>
-      <c r="AE5" s="3">
-        <v>30.81</v>
-      </c>
-      <c r="AF5" s="3">
-        <v>20</v>
-      </c>
-      <c r="AG5" s="3">
-        <v>8</v>
-      </c>
-      <c r="AH5" s="3">
-        <v>2</v>
-      </c>
-      <c r="AI5" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ5" s="3"/>
-      <c r="AK5" s="3"/>
-      <c r="AL5" s="3"/>
-      <c r="AM5" s="3"/>
-      <c r="AN5" s="3"/>
-      <c r="AO5" s="3"/>
-      <c r="AP5" s="3"/>
-    </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>16</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>155</v>
+      </c>
+      <c r="G17" s="2">
+        <v>45953</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="I17">
         <v>0</v>
       </c>
-      <c r="C6" s="3">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3">
-        <v>5</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G6" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H6" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I6" s="3">
-        <v>2</v>
-      </c>
-      <c r="J6" s="3">
-        <v>5</v>
-      </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3">
-        <v>5</v>
-      </c>
-      <c r="M6" s="3">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3">
+      <c r="J17">
+        <v>10</v>
+      </c>
+      <c r="K17">
+        <v>0.52170000000000005</v>
+      </c>
+      <c r="L17">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O6" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="P6" s="3">
+        <v>10</v>
+      </c>
+      <c r="M17">
+        <v>9</v>
+      </c>
+      <c r="N17">
         <f t="shared" si="1"/>
         <v>0.9</v>
       </c>
-      <c r="Q6" s="3">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="S6" s="3">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="T6" s="3">
-        <f t="shared" si="3"/>
-        <v>4.5</v>
-      </c>
-      <c r="U6" s="10">
-        <f>S6*pellet_weigth!$B$3</f>
-        <v>0.27068333333333322</v>
-      </c>
-      <c r="V6" s="3">
-        <v>5.3045999999999998</v>
-      </c>
-      <c r="W6" s="3">
-        <v>5.3333000000000004</v>
-      </c>
-      <c r="X6" s="3">
-        <f t="shared" si="4"/>
-        <v>2.8700000000000614E-2</v>
-      </c>
-      <c r="Y6" s="10">
-        <f t="shared" si="5"/>
-        <v>0.24198333333333261</v>
-      </c>
-      <c r="Z6" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AB6" s="3"/>
-      <c r="AC6" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="3">
-        <v>20.21</v>
-      </c>
-      <c r="AF6" s="3">
-        <v>5</v>
-      </c>
-      <c r="AG6" s="3">
-        <v>8</v>
-      </c>
-      <c r="AH6" s="3">
-        <v>2</v>
-      </c>
-      <c r="AI6" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ6" s="3"/>
-      <c r="AK6" s="3"/>
-      <c r="AL6" s="3"/>
-      <c r="AM6" s="3"/>
-      <c r="AN6" s="3"/>
-      <c r="AO6" s="3"/>
-      <c r="AP6" s="3"/>
-    </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3">
-        <v>6</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G7" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H7" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I7" s="3">
-        <v>2</v>
-      </c>
-      <c r="J7" s="3">
-        <v>5</v>
-      </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3">
-        <v>1</v>
-      </c>
-      <c r="M7" s="3">
-        <v>5</v>
-      </c>
-      <c r="N7" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O7" s="3">
-        <v>5</v>
-      </c>
-      <c r="P7" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>0</v>
-      </c>
-      <c r="R7" s="3">
-        <v>5</v>
-      </c>
-      <c r="S7" s="3">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="T7" s="3">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="U7" s="10">
-        <f>S7*pellet_weigth!$B$3</f>
-        <v>0.54136666666666644</v>
-      </c>
-      <c r="V7" s="3">
-        <v>5.3489000000000004</v>
-      </c>
-      <c r="W7" s="3">
-        <v>5.4973000000000001</v>
-      </c>
-      <c r="X7" s="3">
-        <f t="shared" si="4"/>
-        <v>0.14839999999999964</v>
-      </c>
-      <c r="Y7" s="10">
-        <f t="shared" si="5"/>
-        <v>0.3929666666666668</v>
-      </c>
-      <c r="Z7" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA7" s="3">
-        <v>6</v>
-      </c>
-      <c r="AB7" s="3"/>
-      <c r="AC7" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="3">
-        <v>23.21</v>
-      </c>
-      <c r="AF7" s="3">
-        <v>8</v>
-      </c>
-      <c r="AG7" s="3">
-        <v>6</v>
-      </c>
-      <c r="AH7" s="3">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ7" s="3"/>
-      <c r="AK7" s="3"/>
-      <c r="AL7" s="3"/>
-      <c r="AM7" s="3"/>
-      <c r="AN7" s="3"/>
-      <c r="AO7" s="3"/>
-      <c r="AP7" s="3"/>
-    </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="O17">
+        <v>39</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>1</v>
+      </c>
+      <c r="R17" t="s">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>24.99</v>
+      </c>
+      <c r="T17">
+        <v>10</v>
+      </c>
+      <c r="U17">
         <v>7</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G8" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H8" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2</v>
-      </c>
-      <c r="J8" s="3">
-        <v>5</v>
-      </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>5</v>
-      </c>
-      <c r="N8" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O8" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="P8" s="3">
-        <f t="shared" si="1"/>
-        <v>0.25</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>5</v>
-      </c>
-      <c r="R8" s="3">
-        <v>5</v>
-      </c>
-      <c r="S8" s="3">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="T8" s="3">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="U8" s="10">
-        <f>S8*pellet_weigth!$B$3</f>
-        <v>0.81204999999999972</v>
-      </c>
-      <c r="V8" s="3">
-        <v>5.3219000000000003</v>
-      </c>
-      <c r="W8" s="3">
-        <v>5.5107999999999997</v>
-      </c>
-      <c r="X8" s="3">
-        <f t="shared" si="4"/>
-        <v>0.1888999999999994</v>
-      </c>
-      <c r="Y8" s="10">
-        <f t="shared" si="5"/>
-        <v>0.62315000000000031</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>7</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>35</v>
-      </c>
-      <c r="AC8" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>25.55</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>11</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>7</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>2</v>
-      </c>
-      <c r="AI8" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ8" s="3"/>
-      <c r="AK8" s="3"/>
-      <c r="AL8" s="3"/>
-      <c r="AM8" s="3"/>
-      <c r="AN8" s="3"/>
-      <c r="AO8" s="3"/>
-      <c r="AP8" s="3"/>
-    </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B9" s="3">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3">
-        <v>8</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G9" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H9" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2</v>
-      </c>
-      <c r="J9" s="3">
-        <v>5</v>
-      </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3">
-        <v>2</v>
-      </c>
-      <c r="M9" s="3">
-        <v>5</v>
-      </c>
-      <c r="N9" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O9" s="3">
-        <v>7</v>
-      </c>
-      <c r="P9" s="3">
-        <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>0</v>
-      </c>
-      <c r="R9" s="3">
-        <v>6</v>
-      </c>
-      <c r="S9" s="3">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="T9" s="3">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="U9" s="10">
-        <f>S9*pellet_weigth!$B$3</f>
-        <v>0.54136666666666644</v>
-      </c>
-      <c r="V9" s="3">
-        <v>5.3417000000000003</v>
-      </c>
-      <c r="W9" s="3">
-        <v>5.4987000000000004</v>
-      </c>
-      <c r="X9" s="3">
-        <f t="shared" si="4"/>
-        <v>0.15700000000000003</v>
-      </c>
-      <c r="Y9" s="10">
-        <f t="shared" si="5"/>
-        <v>0.38436666666666641</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>8</v>
-      </c>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>21.62</v>
-      </c>
-      <c r="AF9" s="3">
-        <v>7</v>
-      </c>
-      <c r="AG9" s="3">
-        <v>8</v>
-      </c>
-      <c r="AH9" s="3">
-        <v>2</v>
-      </c>
-      <c r="AI9" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ9" s="3"/>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="3"/>
-      <c r="AM9" s="3"/>
-      <c r="AN9" s="3"/>
-      <c r="AO9" s="3"/>
-      <c r="AP9" s="3"/>
-    </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B10" s="3">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3">
-        <v>9</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G10" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H10" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2</v>
-      </c>
-      <c r="J10" s="3">
-        <v>5</v>
-      </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
-        <v>0</v>
-      </c>
-      <c r="S10" s="3">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="T10" s="3">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="U10" s="10">
-        <f>S10*pellet_weigth!$B$3</f>
-        <v>0.54136666666666644</v>
-      </c>
-      <c r="V10" s="3">
-        <v>5.3342000000000001</v>
-      </c>
-      <c r="W10" s="3">
-        <v>5.3574000000000002</v>
-      </c>
-      <c r="X10" s="3">
-        <f t="shared" si="4"/>
-        <v>2.3200000000000109E-2</v>
-      </c>
-      <c r="Y10" s="10">
-        <f t="shared" si="5"/>
-        <v>0.51816666666666633</v>
-      </c>
-      <c r="Z10" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>9</v>
-      </c>
-      <c r="AB10" s="3"/>
-      <c r="AC10" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD10" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>29.91</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>16</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>8</v>
-      </c>
-      <c r="AH10" s="3">
-        <v>2</v>
-      </c>
-      <c r="AI10" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ10" s="3"/>
-      <c r="AK10" s="3"/>
-      <c r="AL10" s="3"/>
-      <c r="AM10" s="3"/>
-      <c r="AN10" s="3"/>
-      <c r="AO10" s="3"/>
-      <c r="AP10" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B11" s="3">
-        <v>0</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3">
-        <v>10</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G11" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H11" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I11" s="3">
-        <v>2</v>
-      </c>
-      <c r="J11" s="3">
-        <v>5</v>
-      </c>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3">
-        <v>2</v>
-      </c>
-      <c r="M11" s="3">
-        <v>5</v>
-      </c>
-      <c r="N11" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O11" s="3">
-        <v>5</v>
-      </c>
-      <c r="P11" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>0</v>
-      </c>
-      <c r="R11" s="3">
-        <v>2</v>
-      </c>
-      <c r="S11" s="3">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="T11" s="3">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="U11" s="10">
-        <f>S11*pellet_weigth!$B$3</f>
-        <v>0.54136666666666644</v>
-      </c>
-      <c r="V11" s="3">
-        <v>5.2823000000000002</v>
-      </c>
-      <c r="W11" s="3">
-        <v>5.3703000000000003</v>
-      </c>
-      <c r="X11" s="3">
-        <f t="shared" si="4"/>
-        <v>8.8000000000000078E-2</v>
-      </c>
-      <c r="Y11" s="10">
-        <f t="shared" si="5"/>
-        <v>0.45336666666666636</v>
-      </c>
-      <c r="Z11" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA11" s="3">
-        <v>10</v>
-      </c>
-      <c r="AB11" s="3">
-        <v>10</v>
-      </c>
-      <c r="AC11" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE11" s="3">
-        <v>26.41</v>
-      </c>
-      <c r="AF11" s="3">
-        <v>12</v>
-      </c>
-      <c r="AG11" s="3">
-        <v>6</v>
-      </c>
-      <c r="AH11" s="3">
-        <v>2</v>
-      </c>
-      <c r="AI11" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ11" s="3"/>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="3"/>
-      <c r="AM11" s="3"/>
-      <c r="AN11" s="3"/>
-      <c r="AO11" s="3"/>
-      <c r="AP11" s="3"/>
-    </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B12" s="3">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3">
-        <v>11</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G12" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H12" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I12" s="3">
-        <v>2</v>
-      </c>
-      <c r="J12" s="3">
-        <v>5</v>
-      </c>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3">
-        <v>5</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O12" s="3">
-        <v>5</v>
-      </c>
-      <c r="P12" s="3">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>0</v>
-      </c>
-      <c r="R12" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="S12" s="3">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="T12" s="3">
-        <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="U12" s="10">
-        <f>S12*pellet_weigth!$B$3</f>
-        <v>0.27068333333333322</v>
-      </c>
-      <c r="V12" s="3">
-        <v>5.3769</v>
-      </c>
-      <c r="W12" s="3">
-        <v>5.4090999999999996</v>
-      </c>
-      <c r="X12" s="3">
-        <f t="shared" si="4"/>
-        <v>3.2199999999999562E-2</v>
-      </c>
-      <c r="Y12" s="10">
-        <f t="shared" si="5"/>
-        <v>0.23848333333333366</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>11</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD12" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE12" s="3">
-        <v>25.6</v>
-      </c>
-      <c r="AF12" s="3">
-        <v>11</v>
-      </c>
-      <c r="AG12" s="3">
-        <v>8</v>
-      </c>
-      <c r="AH12" s="3">
-        <v>2</v>
-      </c>
-      <c r="AI12" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ12" s="3"/>
-      <c r="AK12" s="3"/>
-      <c r="AL12" s="3"/>
-      <c r="AM12" s="3"/>
-      <c r="AN12" s="3"/>
-      <c r="AO12" s="3"/>
-      <c r="AP12" s="3"/>
-    </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B13" s="3">
-        <v>0</v>
-      </c>
-      <c r="C13" s="3">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3">
-        <v>12</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G13" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H13" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I13" s="3">
-        <v>2</v>
-      </c>
-      <c r="J13" s="3">
-        <v>5</v>
-      </c>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3">
-        <v>2</v>
-      </c>
-      <c r="M13" s="3">
-        <v>5</v>
-      </c>
-      <c r="N13" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O13" s="3">
-        <v>7</v>
-      </c>
-      <c r="P13" s="3">
-        <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>0</v>
-      </c>
-      <c r="R13" s="3">
-        <v>1</v>
-      </c>
-      <c r="S13" s="3">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="T13" s="3">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="U13" s="10">
-        <f>S13*pellet_weigth!$B$3</f>
-        <v>0.54136666666666644</v>
-      </c>
-      <c r="V13" s="3">
-        <v>5.2651000000000003</v>
-      </c>
-      <c r="W13" s="3">
-        <v>5.3334999999999999</v>
-      </c>
-      <c r="X13" s="3">
-        <f t="shared" si="4"/>
-        <v>6.8399999999999572E-2</v>
-      </c>
-      <c r="Y13" s="10">
-        <f t="shared" si="5"/>
-        <v>0.47296666666666687</v>
-      </c>
-      <c r="Z13" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA13" s="3">
-        <v>12</v>
-      </c>
-      <c r="AB13" s="3">
-        <v>20</v>
-      </c>
-      <c r="AC13" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE13" s="3">
-        <v>24.06</v>
-      </c>
-      <c r="AF13" s="3">
-        <v>10</v>
-      </c>
-      <c r="AG13" s="3">
-        <v>8</v>
-      </c>
-      <c r="AH13" s="3">
-        <v>2</v>
-      </c>
-      <c r="AI13" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ13" s="3"/>
-      <c r="AK13" s="3"/>
-      <c r="AL13" s="3"/>
-      <c r="AM13" s="3"/>
-      <c r="AN13" s="3"/>
-      <c r="AO13" s="3"/>
-      <c r="AP13" s="3"/>
-    </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B14" s="3">
-        <v>0</v>
-      </c>
-      <c r="C14" s="3">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3">
-        <v>13</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G14" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H14" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I14" s="3">
-        <v>2</v>
-      </c>
-      <c r="J14" s="3">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O14" s="3">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="S14" s="3">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
-        <f t="shared" si="3"/>
-        <v>4.5</v>
-      </c>
-      <c r="U14" s="10">
-        <f>S14*pellet_weigth!$B$3</f>
-        <v>0.27068333333333322</v>
-      </c>
-      <c r="V14" s="3">
-        <v>5.3407999999999998</v>
-      </c>
-      <c r="W14" s="3">
-        <v>5.3845999999999998</v>
-      </c>
-      <c r="X14" s="3">
-        <f t="shared" si="4"/>
-        <v>4.3800000000000061E-2</v>
-      </c>
-      <c r="Y14" s="10">
-        <f t="shared" si="5"/>
-        <v>0.22688333333333316</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>13</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>8</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>29.75</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>17</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>8</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>2</v>
-      </c>
-      <c r="AI14" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ14" s="3"/>
-      <c r="AK14" s="3"/>
-      <c r="AL14" s="3"/>
-      <c r="AM14" s="3"/>
-      <c r="AN14" s="3"/>
-      <c r="AO14" s="3"/>
-      <c r="AP14" s="3"/>
-    </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B15" s="3">
-        <v>0</v>
-      </c>
-      <c r="C15" s="3">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3">
-        <v>14</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G15" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H15" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I15" s="3">
-        <v>2</v>
-      </c>
-      <c r="J15" s="3">
-        <v>5</v>
-      </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3">
-        <v>5</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O15" s="3">
-        <v>5</v>
-      </c>
-      <c r="P15" s="3">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="S15" s="3">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="T15" s="3">
-        <f t="shared" si="3"/>
-        <v>4.5</v>
-      </c>
-      <c r="U15" s="10">
-        <f>S15*pellet_weigth!$B$3</f>
-        <v>0.27068333333333322</v>
-      </c>
-      <c r="V15" s="3">
-        <v>5.335</v>
-      </c>
-      <c r="W15" s="3">
-        <v>5.3742999999999999</v>
-      </c>
-      <c r="X15" s="3">
-        <f t="shared" si="4"/>
-        <v>3.9299999999999891E-2</v>
-      </c>
-      <c r="Y15" s="10">
-        <f t="shared" si="5"/>
-        <v>0.23138333333333333</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>14</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>38</v>
-      </c>
-      <c r="AC15" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD15" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>5</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>5</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>21.24</v>
-      </c>
-      <c r="AK15" s="3">
-        <v>5</v>
-      </c>
-      <c r="AL15" s="3">
-        <v>5</v>
-      </c>
-      <c r="AM15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="12">
-        <v>45939</v>
-      </c>
-      <c r="AP15" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B16" s="3">
-        <v>0</v>
-      </c>
-      <c r="C16" s="3">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3">
-        <v>15</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G16" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H16" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I16" s="3">
-        <v>2</v>
-      </c>
-      <c r="J16" s="3">
-        <v>5</v>
-      </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3">
-        <v>2</v>
-      </c>
-      <c r="M16" s="3">
-        <v>5</v>
-      </c>
-      <c r="N16" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O16" s="3">
-        <v>7</v>
-      </c>
-      <c r="P16" s="3">
-        <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>0</v>
-      </c>
-      <c r="R16" s="3">
-        <v>1</v>
-      </c>
-      <c r="S16" s="3">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="T16" s="3">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="U16" s="10">
-        <f>S16*pellet_weigth!$B$3</f>
-        <v>0.54136666666666644</v>
-      </c>
-      <c r="V16" s="3">
-        <v>5.3906000000000001</v>
-      </c>
-      <c r="W16" s="3">
-        <v>5.5160999999999998</v>
-      </c>
-      <c r="X16" s="3">
-        <f t="shared" si="4"/>
-        <v>0.12549999999999972</v>
-      </c>
-      <c r="Y16" s="10">
-        <f t="shared" si="5"/>
-        <v>0.41586666666666672</v>
-      </c>
-      <c r="Z16" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA16" s="3">
-        <v>15</v>
-      </c>
-      <c r="AB16" s="3"/>
-      <c r="AC16" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD16" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="3">
-        <v>20.73</v>
-      </c>
-      <c r="AF16" s="3">
-        <v>5</v>
-      </c>
-      <c r="AG16" s="3">
-        <v>8</v>
-      </c>
-      <c r="AH16" s="3">
-        <v>2</v>
-      </c>
-      <c r="AI16" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ16" s="3"/>
-      <c r="AK16" s="3"/>
-      <c r="AL16" s="3"/>
-      <c r="AM16" s="3"/>
-      <c r="AN16" s="3"/>
-      <c r="AO16" s="3"/>
-      <c r="AP16" s="3"/>
-    </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B17" s="3">
-        <v>0</v>
-      </c>
-      <c r="C17" s="3">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3">
-        <v>16</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G17" s="15">
-        <v>45937</v>
-      </c>
-      <c r="H17" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2</v>
-      </c>
-      <c r="J17" s="3">
-        <v>5</v>
-      </c>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3">
-        <v>1</v>
-      </c>
-      <c r="M17" s="3">
-        <v>5</v>
-      </c>
-      <c r="N17" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O17" s="3">
-        <v>6</v>
-      </c>
-      <c r="P17" s="3">
-        <f t="shared" si="1"/>
-        <v>0.6</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="T17" s="3">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="U17" s="10">
-        <f>S17*pellet_weigth!$B$3</f>
-        <v>0.54136666666666644</v>
-      </c>
-      <c r="V17" s="3">
-        <v>5.3566000000000003</v>
-      </c>
-      <c r="W17" s="3">
-        <v>5.4272999999999998</v>
-      </c>
-      <c r="X17" s="3">
-        <f t="shared" si="4"/>
-        <v>7.0699999999999541E-2</v>
-      </c>
-      <c r="Y17" s="10">
-        <f t="shared" si="5"/>
-        <v>0.4706666666666669</v>
-      </c>
-      <c r="Z17" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>16</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>4</v>
-      </c>
-      <c r="AC17" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>26.88</v>
-      </c>
-      <c r="AF17" s="3">
-        <v>14</v>
-      </c>
-      <c r="AG17" s="3">
-        <v>8</v>
-      </c>
-      <c r="AH17" s="3">
-        <v>2</v>
-      </c>
-      <c r="AI17" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ17" s="9"/>
-      <c r="AK17" s="3"/>
-      <c r="AL17" s="3"/>
-      <c r="AM17" s="3"/>
-      <c r="AN17" s="3"/>
-      <c r="AO17" s="3"/>
-      <c r="AP17" s="3"/>
-    </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="V17">
+        <v>2</v>
+      </c>
+      <c r="W17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>156</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
         <v>155</v>
       </c>
       <c r="G18" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H18" s="8">
-        <v>0.45833333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18">
         <v>10</v>
       </c>
-      <c r="K18">
-        <v>0.47839999999999999</v>
+      <c r="L18">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M18">
+        <v>10</v>
       </c>
       <c r="N18">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" ref="N18:N49" si="2">M18/L18</f>
+        <v>1</v>
       </c>
       <c r="O18">
-        <v>9.5</v>
+        <v>40</v>
       </c>
       <c r="P18">
-        <f t="shared" si="1"/>
-        <v>0.95</v>
+        <v>30</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>1</v>
+      </c>
+      <c r="R18" t="s">
+        <v>1</v>
       </c>
       <c r="S18">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <v>23.44</v>
       </c>
       <c r="T18">
-        <f t="shared" ref="T18:T65" si="6">S18-O18</f>
-        <v>0.5</v>
-      </c>
-      <c r="AA18">
-        <v>17</v>
-      </c>
-      <c r="AB18">
-        <v>23</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE18">
-        <v>24.15</v>
-      </c>
-      <c r="AF18">
+        <v>10</v>
+      </c>
+      <c r="U18">
         <v>8</v>
       </c>
-      <c r="AG18">
-        <v>4</v>
-      </c>
-      <c r="AH18">
-        <v>2</v>
-      </c>
-      <c r="AI18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="V18">
+        <v>2</v>
+      </c>
+      <c r="W18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>156</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19">
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F19" t="s">
         <v>155</v>
       </c>
       <c r="G19" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H19" s="8">
-        <v>0.45833333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J19">
         <v>10</v>
       </c>
-      <c r="K19">
-        <v>0.4506</v>
+      <c r="L19">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M19">
+        <v>3.5</v>
       </c>
       <c r="N19">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.35</v>
       </c>
       <c r="O19">
-        <v>10</v>
-      </c>
-      <c r="P19">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>41</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>1</v>
+      </c>
+      <c r="R19" t="s">
+        <v>16</v>
       </c>
       <c r="S19">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <v>39.75</v>
       </c>
       <c r="T19">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA19">
-        <v>19</v>
-      </c>
-      <c r="AB19">
-        <v>17</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE19">
-        <v>25.35</v>
-      </c>
-      <c r="AF19">
-        <v>12</v>
-      </c>
-      <c r="AG19">
-        <v>7</v>
-      </c>
-      <c r="AH19">
-        <v>2</v>
-      </c>
-      <c r="AI19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+        <v>42</v>
+      </c>
+      <c r="U19">
+        <v>8</v>
+      </c>
+      <c r="V19">
+        <v>2</v>
+      </c>
+      <c r="W19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>156</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20">
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20" t="s">
         <v>155</v>
       </c>
       <c r="G20" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H20" s="8">
-        <v>0.45833333333333298</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20">
         <v>10</v>
       </c>
-      <c r="K20">
-        <v>0.47849999999999998</v>
+      <c r="L20">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M20">
+        <v>4.5</v>
       </c>
       <c r="N20">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.45</v>
       </c>
       <c r="O20">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="P20">
-        <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>97</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>1</v>
+      </c>
+      <c r="R20" t="s">
+        <v>1</v>
       </c>
       <c r="S20">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <v>29.75</v>
       </c>
       <c r="T20">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="AA20">
-        <v>20</v>
-      </c>
-      <c r="AB20">
-        <v>14</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE20">
-        <v>26.52</v>
-      </c>
-      <c r="AF20">
-        <v>11</v>
-      </c>
-      <c r="AG20">
-        <v>8</v>
-      </c>
-      <c r="AH20">
-        <v>2</v>
-      </c>
-      <c r="AI20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+        <v>16</v>
+      </c>
+      <c r="U20">
+        <v>6</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>156</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
         <v>155</v>
       </c>
       <c r="G21" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H21" s="8">
-        <v>0.45833333333333298</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I21">
+        <v>3</v>
+      </c>
+      <c r="J21">
+        <v>10</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M21">
+        <v>7</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="2"/>
+        <v>0.7</v>
+      </c>
+      <c r="O21">
+        <v>43</v>
+      </c>
+      <c r="P21">
+        <v>77</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>1</v>
+      </c>
+      <c r="R21" t="s">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>26.6</v>
+      </c>
+      <c r="T21">
+        <v>13</v>
+      </c>
+      <c r="U21">
+        <v>7</v>
+      </c>
+      <c r="V21">
+        <v>2</v>
+      </c>
+      <c r="W21">
         <v>0</v>
       </c>
-      <c r="J21">
-        <v>10</v>
-      </c>
-      <c r="K21">
-        <v>0.4909</v>
-      </c>
-      <c r="N21">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O21">
-        <v>10</v>
-      </c>
-      <c r="P21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="S21">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="T21">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>21</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE21">
-        <v>25.39</v>
-      </c>
-      <c r="AF21">
-        <v>9</v>
-      </c>
-      <c r="AG21">
-        <v>7</v>
-      </c>
-      <c r="AH21">
-        <v>2</v>
-      </c>
-      <c r="AI21">
-        <v>2</v>
-      </c>
-      <c r="AO21" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>156</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22">
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F22" t="s">
         <v>155</v>
       </c>
       <c r="G22" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H22" s="8">
-        <v>0.45833333333333298</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22">
         <v>10</v>
       </c>
-      <c r="K22">
-        <v>0.47770000000000001</v>
+      <c r="L22">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M22">
+        <v>5</v>
       </c>
       <c r="N22">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="O22">
+        <v>44</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>1</v>
+      </c>
+      <c r="R22" t="s">
+        <v>16</v>
+      </c>
+      <c r="S22">
+        <v>35.270000000000003</v>
+      </c>
+      <c r="T22">
+        <v>30</v>
+      </c>
+      <c r="U22">
         <v>8</v>
       </c>
-      <c r="P22">
-        <f t="shared" si="1"/>
-        <v>0.8</v>
-      </c>
-      <c r="S22">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="T22">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AA22">
-        <v>22</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE22">
-        <v>28.55</v>
-      </c>
-      <c r="AF22">
-        <v>17</v>
-      </c>
-      <c r="AG22">
-        <v>8</v>
-      </c>
-      <c r="AH22">
-        <v>2</v>
-      </c>
-      <c r="AI22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="V22">
+        <v>2</v>
+      </c>
+      <c r="W22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>156</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23">
         <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F23" t="s">
         <v>155</v>
       </c>
       <c r="G23" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H23" s="8">
-        <v>0.45833333333333298</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23">
         <v>10</v>
       </c>
-      <c r="K23">
-        <v>0.47989999999999999</v>
+      <c r="L23">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M23">
+        <v>8</v>
       </c>
       <c r="N23">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.8</v>
       </c>
       <c r="O23">
-        <v>10</v>
-      </c>
-      <c r="P23">
-        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>1</v>
+      </c>
+      <c r="R23" t="s">
         <v>1</v>
       </c>
       <c r="S23">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>23</v>
-      </c>
-      <c r="AB23">
-        <v>9</v>
-      </c>
-      <c r="AC23" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE23">
-        <v>24.46</v>
-      </c>
-      <c r="AF23">
-        <v>10</v>
-      </c>
-      <c r="AG23">
+        <v>10</v>
+      </c>
+      <c r="U23">
         <v>8</v>
       </c>
-      <c r="AH23">
-        <v>2</v>
-      </c>
-      <c r="AI23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>156</v>
       </c>
       <c r="B24">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24">
         <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
         <v>155</v>
       </c>
       <c r="G24" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H24" s="8">
-        <v>0.45833333333333298</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24">
         <v>10</v>
       </c>
-      <c r="K24">
-        <v>0.46079999999999999</v>
+      <c r="L24">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M24">
+        <v>8</v>
       </c>
       <c r="N24">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.8</v>
       </c>
       <c r="O24">
-        <v>10</v>
-      </c>
-      <c r="P24">
-        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>1</v>
+      </c>
+      <c r="R24" t="s">
         <v>1</v>
       </c>
       <c r="S24">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <v>28.41</v>
       </c>
       <c r="T24">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA24">
-        <v>24</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE24">
-        <v>28.59</v>
-      </c>
-      <c r="AF24">
-        <v>15</v>
-      </c>
-      <c r="AG24">
+        <v>17</v>
+      </c>
+      <c r="U24">
         <v>8</v>
       </c>
-      <c r="AH24">
-        <v>1</v>
-      </c>
-      <c r="AI24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="V24">
+        <v>2</v>
+      </c>
+      <c r="W24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>156</v>
       </c>
       <c r="B25">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25">
         <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F25" t="s">
         <v>155</v>
       </c>
       <c r="G25" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H25" s="8">
-        <v>0.45833333333333298</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25">
         <v>10</v>
       </c>
-      <c r="K25">
-        <v>0.46360000000000001</v>
+      <c r="L25">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M25">
+        <v>7</v>
       </c>
       <c r="N25">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="O25">
-        <v>9.5</v>
-      </c>
-      <c r="P25">
-        <f t="shared" si="1"/>
-        <v>0.95</v>
+        <v>47</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R25" t="s">
+        <v>1</v>
       </c>
       <c r="S25">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <v>25.04</v>
       </c>
       <c r="T25">
-        <f t="shared" si="6"/>
-        <v>0.5</v>
-      </c>
-      <c r="AA25">
-        <v>25</v>
-      </c>
-      <c r="AB25">
-        <v>30</v>
-      </c>
-      <c r="AC25" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE25">
-        <v>26.55</v>
-      </c>
-      <c r="AF25">
-        <v>13</v>
-      </c>
-      <c r="AG25">
+        <v>11</v>
+      </c>
+      <c r="U25">
         <v>7</v>
       </c>
-      <c r="AH25">
-        <v>2</v>
-      </c>
-      <c r="AI25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="V25">
+        <v>2</v>
+      </c>
+      <c r="W25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>156</v>
       </c>
       <c r="B26">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26">
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F26" t="s">
         <v>155</v>
       </c>
       <c r="G26" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H26" s="8">
-        <v>0.45833333333333298</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I26">
+        <v>3</v>
+      </c>
+      <c r="J26">
+        <v>10</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M26">
+        <v>9</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="2"/>
+        <v>0.9</v>
+      </c>
+      <c r="O26">
+        <v>48</v>
+      </c>
+      <c r="P26">
+        <v>99</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>1</v>
+      </c>
+      <c r="R26" t="s">
+        <v>1</v>
+      </c>
+      <c r="S26">
+        <v>25.24</v>
+      </c>
+      <c r="T26">
+        <v>10</v>
+      </c>
+      <c r="U26">
+        <v>4</v>
+      </c>
+      <c r="V26">
         <v>0</v>
       </c>
-      <c r="J26">
-        <v>10</v>
-      </c>
-      <c r="K26">
-        <v>0.50549999999999995</v>
-      </c>
-      <c r="N26">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O26">
-        <v>10</v>
-      </c>
-      <c r="P26">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="S26">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="T26">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>26</v>
-      </c>
-      <c r="AC26" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE26">
-        <v>23.62</v>
-      </c>
-      <c r="AF26">
-        <v>8</v>
-      </c>
-      <c r="AG26">
-        <v>8</v>
-      </c>
-      <c r="AH26">
-        <v>2</v>
-      </c>
-      <c r="AI26">
-        <v>2</v>
-      </c>
-      <c r="AO26" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="W26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>156</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27">
         <v>10</v>
       </c>
       <c r="E27" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
         <v>155</v>
       </c>
       <c r="G27" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H27" s="8">
-        <v>0.45833333333333298</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27">
+        <v>10</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M27">
+        <v>9</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="2"/>
+        <v>0.9</v>
+      </c>
+      <c r="O27">
+        <v>49</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>1</v>
+      </c>
+      <c r="R27" t="s">
         <v>0</v>
       </c>
-      <c r="J27">
-        <v>10</v>
-      </c>
-      <c r="K27">
-        <v>0.51680000000000004</v>
-      </c>
-      <c r="N27">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O27">
-        <v>10</v>
-      </c>
-      <c r="P27">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="S27">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <v>21.09</v>
       </c>
       <c r="T27">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>28</v>
-      </c>
-      <c r="AC27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE27">
-        <v>29.36</v>
-      </c>
-      <c r="AF27">
-        <v>17</v>
-      </c>
-      <c r="AG27">
+        <v>8</v>
+      </c>
+      <c r="U27">
         <v>7</v>
       </c>
-      <c r="AH27">
-        <v>2</v>
-      </c>
-      <c r="AI27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="V27">
+        <v>2</v>
+      </c>
+      <c r="W27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>156</v>
       </c>
       <c r="B28">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28">
         <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F28" t="s">
         <v>155</v>
       </c>
       <c r="G28" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H28" s="8">
-        <v>0.45833333333333298</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28">
         <v>10</v>
       </c>
-      <c r="K28">
-        <v>0.47489999999999999</v>
+      <c r="L28">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M28">
+        <v>10</v>
       </c>
       <c r="N28">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="O28">
-        <v>10</v>
-      </c>
-      <c r="P28">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>1</v>
+      </c>
+      <c r="R28" t="s">
+        <v>16</v>
       </c>
       <c r="S28">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <v>32.94</v>
       </c>
       <c r="T28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>29</v>
-      </c>
-      <c r="AB28">
-        <v>11</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE28">
-        <v>29.46</v>
-      </c>
-      <c r="AF28">
-        <v>17</v>
-      </c>
-      <c r="AG28">
-        <v>8</v>
-      </c>
-      <c r="AH28">
-        <v>2</v>
-      </c>
-      <c r="AI28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+        <v>24</v>
+      </c>
+      <c r="U28">
+        <v>7</v>
+      </c>
+      <c r="V28">
+        <v>2</v>
+      </c>
+      <c r="W28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>156</v>
       </c>
       <c r="B29">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29">
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" t="s">
         <v>155</v>
       </c>
       <c r="G29" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H29" s="8">
-        <v>0.45833333333333298</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29">
         <v>10</v>
       </c>
-      <c r="K29">
-        <v>0.50090000000000001</v>
+      <c r="L29">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M29">
+        <v>5</v>
       </c>
       <c r="N29">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="O29">
-        <v>10</v>
-      </c>
-      <c r="P29">
-        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>1</v>
+      </c>
+      <c r="R29" t="s">
         <v>1</v>
       </c>
       <c r="S29">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <v>26.97</v>
       </c>
       <c r="T29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>32</v>
-      </c>
-      <c r="AB29">
         <v>13</v>
       </c>
-      <c r="AC29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE29">
-        <v>23.96</v>
-      </c>
-      <c r="AF29">
+      <c r="U29">
         <v>8</v>
       </c>
-      <c r="AG29">
-        <v>6</v>
-      </c>
-      <c r="AH29">
-        <v>2</v>
-      </c>
-      <c r="AI29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="V29">
+        <v>2</v>
+      </c>
+      <c r="W29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>156</v>
       </c>
       <c r="B30">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30">
         <v>13</v>
       </c>
       <c r="E30" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
         <v>155</v>
       </c>
       <c r="G30" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H30" s="8">
-        <v>0.45833333333333298</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J30">
         <v>10</v>
       </c>
-      <c r="K30">
-        <v>0.52549999999999997</v>
+      <c r="L30">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M30">
+        <v>7</v>
       </c>
       <c r="N30">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="O30">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="P30">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>1</v>
+      </c>
+      <c r="R30" t="s">
+        <v>16</v>
       </c>
       <c r="S30">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <v>30.1</v>
       </c>
       <c r="T30">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>33</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE30">
-        <v>24.83</v>
-      </c>
-      <c r="AF30">
-        <v>10</v>
-      </c>
-      <c r="AG30">
+        <v>19</v>
+      </c>
+      <c r="U30">
         <v>8</v>
       </c>
-      <c r="AH30">
-        <v>2</v>
-      </c>
-      <c r="AI30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+      <c r="V30">
+        <v>2</v>
+      </c>
+      <c r="W30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>156</v>
       </c>
       <c r="B31">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31">
         <v>14</v>
       </c>
       <c r="E31" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F31" t="s">
         <v>155</v>
       </c>
       <c r="G31" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H31" s="8">
-        <v>0.45833333333333298</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J31">
         <v>10</v>
       </c>
-      <c r="K31">
-        <v>0.49430000000000002</v>
+      <c r="L31">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M31">
+        <v>9</v>
       </c>
       <c r="N31">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.9</v>
       </c>
       <c r="O31">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="P31">
-        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>1</v>
+      </c>
+      <c r="R31" t="s">
         <v>1</v>
       </c>
       <c r="S31">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <v>26.62</v>
       </c>
       <c r="T31">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>35</v>
-      </c>
-      <c r="AC31" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD31" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE31">
-        <v>28.52</v>
-      </c>
-      <c r="AF31">
-        <v>14</v>
-      </c>
-      <c r="AG31">
-        <v>5</v>
-      </c>
-      <c r="AH31">
-        <v>2</v>
-      </c>
-      <c r="AI31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+        <v>13</v>
+      </c>
+      <c r="U31">
+        <v>7</v>
+      </c>
+      <c r="V31">
+        <v>2</v>
+      </c>
+      <c r="W31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>156</v>
       </c>
       <c r="B32">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32">
         <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F32" t="s">
         <v>155</v>
       </c>
       <c r="G32" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H32" s="8">
-        <v>0.45833333333333298</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32">
         <v>10</v>
       </c>
-      <c r="K32">
-        <v>0.52490000000000003</v>
+      <c r="L32">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M32">
+        <v>5</v>
       </c>
       <c r="N32">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="O32">
-        <v>10</v>
-      </c>
-      <c r="P32">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>1</v>
+      </c>
+      <c r="R32" t="s">
+        <v>16</v>
       </c>
       <c r="S32">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <v>38.04</v>
       </c>
       <c r="T32">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>37</v>
-      </c>
-      <c r="AC32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD32" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE32">
-        <v>26.6</v>
-      </c>
-      <c r="AF32">
-        <v>13</v>
-      </c>
-      <c r="AG32">
-        <v>8</v>
-      </c>
-      <c r="AH32">
-        <v>2</v>
-      </c>
-      <c r="AI32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+        <v>34</v>
+      </c>
+      <c r="U32">
+        <v>7</v>
+      </c>
+      <c r="V32">
+        <v>2</v>
+      </c>
+      <c r="W32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>156</v>
       </c>
       <c r="B33">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33">
         <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F33" t="s">
         <v>155</v>
       </c>
       <c r="G33" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
       <c r="H33" s="8">
-        <v>0.45833333333333298</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I33">
+        <v>3</v>
+      </c>
+      <c r="J33">
+        <v>10</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M33">
+        <v>10</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O33">
+        <v>55</v>
+      </c>
+      <c r="P33">
+        <v>87</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>1</v>
+      </c>
+      <c r="R33" t="s">
         <v>0</v>
       </c>
-      <c r="J33">
-        <v>10</v>
-      </c>
-      <c r="K33">
-        <v>0.52170000000000005</v>
-      </c>
-      <c r="N33">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="O33">
-        <v>9</v>
-      </c>
-      <c r="P33">
-        <f t="shared" si="1"/>
-        <v>0.9</v>
-      </c>
       <c r="S33">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <v>21.59</v>
       </c>
       <c r="T33">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="AA33">
-        <v>39</v>
-      </c>
-      <c r="AC33" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD33" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE33">
-        <v>24.99</v>
-      </c>
-      <c r="AF33">
-        <v>10</v>
-      </c>
-      <c r="AG33">
-        <v>7</v>
-      </c>
-      <c r="AH33">
-        <v>2</v>
-      </c>
-      <c r="AI33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+        <v>8</v>
+      </c>
+      <c r="U33">
+        <v>5</v>
+      </c>
+      <c r="V33">
+        <v>2</v>
+      </c>
+      <c r="W33">
+        <v>2</v>
+      </c>
+      <c r="X33" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>156</v>
       </c>
       <c r="B34">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F34" t="s">
         <v>155</v>
       </c>
       <c r="G34" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H34" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J34">
         <v>10</v>
       </c>
+      <c r="L34">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M34">
+        <v>9.5</v>
+      </c>
       <c r="N34">
-        <f t="shared" ref="N34:N65" si="7">J34+M34</f>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.95</v>
       </c>
       <c r="O34">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="P34">
-        <f t="shared" ref="P34:P65" si="8">O34/N34</f>
+        <v>99</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>1</v>
+      </c>
+      <c r="R34" t="s">
         <v>1</v>
       </c>
       <c r="S34">
-        <f t="shared" ref="S34:S65" si="9">J34+M34+Q34</f>
-        <v>10</v>
+        <v>27.07</v>
       </c>
       <c r="T34">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA34">
-        <v>40</v>
-      </c>
-      <c r="AB34">
-        <v>30</v>
-      </c>
-      <c r="AC34" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE34">
-        <v>23.44</v>
-      </c>
-      <c r="AF34">
-        <v>10</v>
-      </c>
-      <c r="AG34">
+        <v>12</v>
+      </c>
+      <c r="U34">
         <v>8</v>
       </c>
-      <c r="AH34">
-        <v>2</v>
-      </c>
-      <c r="AI34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+      <c r="V34">
+        <v>1</v>
+      </c>
+      <c r="W34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>156</v>
       </c>
       <c r="B35">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35">
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F35" t="s">
         <v>155</v>
       </c>
       <c r="G35" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H35" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J35">
         <v>10</v>
       </c>
+      <c r="L35">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M35">
+        <v>6.5</v>
+      </c>
       <c r="N35">
-        <f t="shared" si="7"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>57</v>
       </c>
       <c r="P35">
-        <f t="shared" si="8"/>
-        <v>0.35</v>
+        <v>41</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>1</v>
+      </c>
+      <c r="R35" t="s">
+        <v>16</v>
       </c>
       <c r="S35">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <v>38.49</v>
       </c>
       <c r="T35">
-        <f t="shared" si="6"/>
-        <v>6.5</v>
-      </c>
-      <c r="AA35">
-        <v>41</v>
-      </c>
-      <c r="AC35" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD35" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE35">
-        <v>39.75</v>
-      </c>
-      <c r="AF35">
-        <v>42</v>
-      </c>
-      <c r="AG35">
+        <v>40</v>
+      </c>
+      <c r="U35">
         <v>8</v>
       </c>
-      <c r="AH35">
-        <v>2</v>
-      </c>
-      <c r="AI35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+      <c r="V35">
+        <v>2</v>
+      </c>
+      <c r="W35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>156</v>
       </c>
       <c r="B36">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F36" t="s">
         <v>155</v>
       </c>
       <c r="G36" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H36" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J36">
         <v>10</v>
       </c>
+      <c r="L36">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M36">
+        <v>8.5</v>
+      </c>
       <c r="N36">
-        <f t="shared" si="7"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.85</v>
       </c>
       <c r="O36">
-        <v>4.5</v>
+        <v>58</v>
       </c>
       <c r="P36">
-        <f t="shared" si="8"/>
-        <v>0.45</v>
+        <v>70</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>1</v>
+      </c>
+      <c r="R36" t="s">
+        <v>1</v>
       </c>
       <c r="S36">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <v>25.21</v>
       </c>
       <c r="T36">
-        <f t="shared" si="6"/>
-        <v>5.5</v>
-      </c>
-      <c r="AA36">
-        <v>42</v>
-      </c>
-      <c r="AB36">
-        <v>97</v>
-      </c>
-      <c r="AC36" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD36" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE36">
-        <v>29.75</v>
-      </c>
-      <c r="AF36">
-        <v>16</v>
-      </c>
-      <c r="AG36">
+        <v>10</v>
+      </c>
+      <c r="U36">
         <v>6</v>
       </c>
-      <c r="AH36">
-        <v>1</v>
-      </c>
-      <c r="AI36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+      <c r="V36">
+        <v>1</v>
+      </c>
+      <c r="W36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>156</v>
       </c>
       <c r="B37">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37">
         <v>4</v>
       </c>
       <c r="E37" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F37" t="s">
         <v>155</v>
       </c>
       <c r="G37" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H37" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37">
         <v>10</v>
       </c>
+      <c r="L37">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M37">
+        <v>8.5</v>
+      </c>
       <c r="N37">
-        <f t="shared" si="7"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.85</v>
       </c>
       <c r="O37">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="P37">
-        <f t="shared" si="8"/>
-        <v>0.7</v>
+        <v>80</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>1</v>
+      </c>
+      <c r="R37" t="s">
+        <v>1</v>
       </c>
       <c r="S37">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <v>25.84</v>
       </c>
       <c r="T37">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AA37">
-        <v>43</v>
-      </c>
-      <c r="AB37">
-        <v>77</v>
-      </c>
-      <c r="AC37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD37" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE37">
-        <v>26.6</v>
-      </c>
-      <c r="AF37">
-        <v>13</v>
-      </c>
-      <c r="AG37">
-        <v>7</v>
-      </c>
-      <c r="AH37">
-        <v>2</v>
-      </c>
-      <c r="AI37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+        <v>14</v>
+      </c>
+      <c r="U37">
+        <v>8</v>
+      </c>
+      <c r="V37">
+        <v>2</v>
+      </c>
+      <c r="W37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>156</v>
       </c>
       <c r="B38">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38">
         <v>5</v>
       </c>
       <c r="E38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F38" t="s">
         <v>155</v>
       </c>
       <c r="G38" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H38" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J38">
         <v>10</v>
       </c>
+      <c r="L38">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M38">
+        <v>9</v>
+      </c>
       <c r="N38">
-        <f t="shared" si="7"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.9</v>
       </c>
       <c r="O38">
-        <v>5</v>
-      </c>
-      <c r="P38">
-        <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>60</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>1</v>
+      </c>
+      <c r="R38" t="s">
+        <v>1</v>
       </c>
       <c r="S38">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <v>23.41</v>
       </c>
       <c r="T38">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="AA38">
-        <v>44</v>
-      </c>
-      <c r="AC38" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD38" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE38">
-        <v>35.270000000000003</v>
-      </c>
-      <c r="AF38">
-        <v>30</v>
-      </c>
-      <c r="AG38">
+        <v>9</v>
+      </c>
+      <c r="U38">
         <v>8</v>
       </c>
-      <c r="AH38">
-        <v>2</v>
-      </c>
-      <c r="AI38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+      <c r="V38">
+        <v>1</v>
+      </c>
+      <c r="W38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>156</v>
       </c>
       <c r="B39">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39">
         <v>6</v>
       </c>
       <c r="E39" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F39" t="s">
         <v>155</v>
       </c>
       <c r="G39" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H39" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="I39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J39">
         <v>10</v>
       </c>
+      <c r="L39">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M39">
+        <v>9</v>
+      </c>
       <c r="N39">
-        <f t="shared" si="7"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.9</v>
       </c>
       <c r="O39">
+        <v>61</v>
+      </c>
+      <c r="P39">
+        <v>81</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>1</v>
+      </c>
+      <c r="R39" t="s">
+        <v>16</v>
+      </c>
+      <c r="S39">
+        <v>30.38</v>
+      </c>
+      <c r="T39">
+        <v>22</v>
+      </c>
+      <c r="U39">
         <v>8</v>
       </c>
-      <c r="P39">
-        <f t="shared" si="8"/>
-        <v>0.8</v>
-      </c>
-      <c r="S39">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T39">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AA39">
-        <v>45</v>
-      </c>
-      <c r="AC39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD39" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE39">
-        <v>25</v>
-      </c>
-      <c r="AF39">
-        <v>10</v>
-      </c>
-      <c r="AG39">
-        <v>8</v>
-      </c>
-      <c r="AH39">
-        <v>1</v>
-      </c>
-      <c r="AI39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+      <c r="V39">
+        <v>2</v>
+      </c>
+      <c r="W39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>156</v>
       </c>
       <c r="B40">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40">
         <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F40" t="s">
         <v>155</v>
       </c>
       <c r="G40" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H40" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J40">
         <v>10</v>
       </c>
+      <c r="L40">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M40">
+        <v>10</v>
+      </c>
       <c r="N40">
-        <f t="shared" si="7"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="O40">
+        <v>62</v>
+      </c>
+      <c r="P40">
+        <v>92</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>1</v>
+      </c>
+      <c r="R40" t="s">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>20.48</v>
+      </c>
+      <c r="T40">
+        <v>6</v>
+      </c>
+      <c r="U40">
         <v>8</v>
       </c>
-      <c r="P40">
-        <f t="shared" si="8"/>
-        <v>0.8</v>
-      </c>
-      <c r="S40">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T40">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AA40">
-        <v>46</v>
-      </c>
-      <c r="AC40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD40" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE40">
-        <v>28.41</v>
-      </c>
-      <c r="AF40">
-        <v>17</v>
-      </c>
-      <c r="AG40">
-        <v>8</v>
-      </c>
-      <c r="AH40">
-        <v>2</v>
-      </c>
-      <c r="AI40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+      <c r="V40">
+        <v>2</v>
+      </c>
+      <c r="W40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>156</v>
       </c>
       <c r="B41">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41">
         <v>8</v>
       </c>
       <c r="E41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F41" t="s">
         <v>155</v>
       </c>
       <c r="G41" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H41" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="I41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J41">
         <v>10</v>
       </c>
+      <c r="L41">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M41">
+        <v>8.5</v>
+      </c>
       <c r="N41">
-        <f t="shared" si="7"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.85</v>
       </c>
       <c r="O41">
-        <v>7</v>
-      </c>
-      <c r="P41">
-        <f t="shared" si="8"/>
-        <v>0.7</v>
+        <v>63</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>1</v>
+      </c>
+      <c r="R41" t="s">
+        <v>16</v>
       </c>
       <c r="S41">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <v>40.880000000000003</v>
       </c>
       <c r="T41">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AA41">
-        <v>47</v>
-      </c>
-      <c r="AC41" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD41" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE41">
-        <v>25.04</v>
-      </c>
-      <c r="AF41">
-        <v>11</v>
-      </c>
-      <c r="AG41">
-        <v>7</v>
-      </c>
-      <c r="AH41">
-        <v>2</v>
-      </c>
-      <c r="AI41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+        <v>41</v>
+      </c>
+      <c r="U41">
+        <v>8</v>
+      </c>
+      <c r="V41">
+        <v>1</v>
+      </c>
+      <c r="W41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>156</v>
       </c>
       <c r="B42">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42">
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F42" t="s">
         <v>155</v>
       </c>
       <c r="G42" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H42" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="I42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J42">
         <v>10</v>
       </c>
+      <c r="L42">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M42">
+        <v>10</v>
+      </c>
       <c r="N42">
-        <f t="shared" si="7"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="O42">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="P42">
-        <f t="shared" si="8"/>
-        <v>0.9</v>
+        <v>90</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>1</v>
+      </c>
+      <c r="R42" t="s">
+        <v>16</v>
       </c>
       <c r="S42">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <v>31.11</v>
       </c>
       <c r="T42">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="AA42">
-        <v>48</v>
-      </c>
-      <c r="AB42">
-        <v>99</v>
-      </c>
-      <c r="AC42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE42">
-        <v>25.24</v>
-      </c>
-      <c r="AF42">
-        <v>10</v>
-      </c>
-      <c r="AG42">
-        <v>4</v>
-      </c>
-      <c r="AH42">
-        <v>0</v>
-      </c>
-      <c r="AI42">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+        <v>20</v>
+      </c>
+      <c r="U42">
+        <v>7</v>
+      </c>
+      <c r="V42">
+        <v>2</v>
+      </c>
+      <c r="W42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>156</v>
       </c>
       <c r="B43">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43">
         <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F43" t="s">
         <v>155</v>
       </c>
       <c r="G43" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H43" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="I43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J43">
         <v>10</v>
       </c>
+      <c r="L43">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
       <c r="N43">
-        <f t="shared" si="7"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.1</v>
       </c>
       <c r="O43">
-        <v>9</v>
-      </c>
-      <c r="P43">
-        <f t="shared" si="8"/>
-        <v>0.9</v>
+        <v>65</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>1</v>
+      </c>
+      <c r="R43" t="s">
+        <v>16</v>
       </c>
       <c r="S43">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <v>35.61</v>
       </c>
       <c r="T43">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="AA43">
-        <v>49</v>
-      </c>
-      <c r="AC43" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD43" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE43">
-        <v>21.09</v>
-      </c>
-      <c r="AF43">
+        <v>27</v>
+      </c>
+      <c r="U43">
         <v>8</v>
       </c>
-      <c r="AG43">
-        <v>7</v>
-      </c>
-      <c r="AH43">
-        <v>2</v>
-      </c>
-      <c r="AI43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+      <c r="V43">
+        <v>2</v>
+      </c>
+      <c r="W43">
+        <v>2</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>156</v>
       </c>
       <c r="B44">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44">
         <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F44" t="s">
         <v>155</v>
       </c>
       <c r="G44" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H44" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="I44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J44">
         <v>10</v>
       </c>
+      <c r="L44">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M44">
+        <v>9.5</v>
+      </c>
       <c r="N44">
-        <f t="shared" si="7"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.95</v>
       </c>
       <c r="O44">
-        <v>10</v>
-      </c>
-      <c r="P44">
-        <f t="shared" si="8"/>
+        <v>66</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>1</v>
+      </c>
+      <c r="R44" t="s">
         <v>1</v>
       </c>
       <c r="S44">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <v>28.04</v>
       </c>
       <c r="T44">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA44">
-        <v>50</v>
-      </c>
-      <c r="AC44" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD44" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE44">
-        <v>32.94</v>
-      </c>
-      <c r="AF44">
-        <v>24</v>
-      </c>
-      <c r="AG44">
-        <v>7</v>
-      </c>
-      <c r="AH44">
-        <v>2</v>
-      </c>
-      <c r="AI44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+        <v>15</v>
+      </c>
+      <c r="U44">
+        <v>8</v>
+      </c>
+      <c r="V44">
+        <v>2</v>
+      </c>
+      <c r="W44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>156</v>
       </c>
       <c r="B45">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45">
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F45" t="s">
         <v>155</v>
       </c>
       <c r="G45" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H45" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="I45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J45">
         <v>10</v>
       </c>
+      <c r="L45">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M45">
+        <v>9</v>
+      </c>
       <c r="N45">
-        <f t="shared" si="7"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.9</v>
       </c>
       <c r="O45">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="P45">
-        <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>83</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R45" t="s">
+        <v>1</v>
       </c>
       <c r="S45">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <v>28.37</v>
       </c>
       <c r="T45">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="AA45">
-        <v>51</v>
-      </c>
-      <c r="AC45" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD45" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE45">
-        <v>26.97</v>
-      </c>
-      <c r="AF45">
-        <v>13</v>
-      </c>
-      <c r="AG45">
+        <v>15</v>
+      </c>
+      <c r="U45">
         <v>8</v>
       </c>
-      <c r="AH45">
-        <v>2</v>
-      </c>
-      <c r="AI45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+      <c r="V45">
+        <v>2</v>
+      </c>
+      <c r="W45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>156</v>
       </c>
       <c r="B46">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D46">
         <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F46" t="s">
         <v>155</v>
       </c>
       <c r="G46" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H46" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="I46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J46">
         <v>10</v>
       </c>
+      <c r="L46">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M46">
+        <v>8</v>
+      </c>
       <c r="N46">
-        <f t="shared" si="7"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.8</v>
       </c>
       <c r="O46">
-        <v>7</v>
-      </c>
-      <c r="P46">
-        <f t="shared" si="8"/>
-        <v>0.7</v>
+        <v>68</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>1</v>
+      </c>
+      <c r="R46" t="s">
+        <v>1</v>
       </c>
       <c r="S46">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <v>25.25</v>
       </c>
       <c r="T46">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="AA46">
-        <v>52</v>
-      </c>
-      <c r="AB46">
-        <v>26</v>
-      </c>
-      <c r="AC46" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD46" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE46">
-        <v>30.1</v>
-      </c>
-      <c r="AF46">
-        <v>19</v>
-      </c>
-      <c r="AG46">
+        <v>11</v>
+      </c>
+      <c r="U46">
         <v>8</v>
       </c>
-      <c r="AH46">
-        <v>2</v>
-      </c>
-      <c r="AI46">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+      <c r="V46">
+        <v>2</v>
+      </c>
+      <c r="W46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>156</v>
       </c>
       <c r="B47">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47">
         <v>14</v>
       </c>
       <c r="E47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F47" t="s">
         <v>155</v>
       </c>
       <c r="G47" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H47" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J47">
         <v>10</v>
       </c>
+      <c r="L47">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M47">
+        <v>9.5</v>
+      </c>
       <c r="N47">
-        <f t="shared" si="7"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.95</v>
       </c>
       <c r="O47">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="P47">
-        <f t="shared" si="8"/>
-        <v>0.9</v>
+        <v>76</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>1</v>
+      </c>
+      <c r="R47" t="s">
+        <v>16</v>
       </c>
       <c r="S47">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <v>30.46</v>
       </c>
       <c r="T47">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="AA47">
-        <v>53</v>
-      </c>
-      <c r="AB47">
-        <v>102</v>
-      </c>
-      <c r="AC47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE47">
-        <v>26.62</v>
-      </c>
-      <c r="AF47">
-        <v>13</v>
-      </c>
-      <c r="AG47">
-        <v>7</v>
-      </c>
-      <c r="AH47">
-        <v>2</v>
-      </c>
-      <c r="AI47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.55000000000000004">
+        <v>20</v>
+      </c>
+      <c r="U47">
+        <v>8</v>
+      </c>
+      <c r="V47">
+        <v>2</v>
+      </c>
+      <c r="W47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>156</v>
       </c>
       <c r="B48">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48">
         <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F48" t="s">
         <v>155</v>
       </c>
       <c r="G48" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H48" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J48">
         <v>10</v>
       </c>
+      <c r="L48">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M48">
+        <v>10</v>
+      </c>
       <c r="N48">
-        <f t="shared" si="7"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
       <c r="O48">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="P48">
-        <f t="shared" si="8"/>
-        <v>0.5</v>
+        <v>79</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>1</v>
+      </c>
+      <c r="R48" t="s">
+        <v>1</v>
       </c>
       <c r="S48">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <v>24.78</v>
       </c>
       <c r="T48">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="AA48">
-        <v>54</v>
-      </c>
-      <c r="AC48" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD48" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE48">
-        <v>38.04</v>
-      </c>
-      <c r="AF48">
-        <v>34</v>
-      </c>
-      <c r="AG48">
-        <v>7</v>
-      </c>
-      <c r="AH48">
-        <v>2</v>
-      </c>
-      <c r="AI48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.55000000000000004">
+        <v>10</v>
+      </c>
+      <c r="U48">
+        <v>6</v>
+      </c>
+      <c r="V48">
+        <v>2</v>
+      </c>
+      <c r="W48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>156</v>
       </c>
       <c r="B49">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D49">
         <v>16</v>
       </c>
       <c r="E49" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F49" t="s">
         <v>155</v>
       </c>
       <c r="G49" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="H49" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.47916666666666702</v>
       </c>
       <c r="I49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J49">
         <v>10</v>
       </c>
+      <c r="L49">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="M49">
+        <v>8</v>
+      </c>
       <c r="N49">
-        <f t="shared" si="7"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0.8</v>
       </c>
       <c r="O49">
-        <v>10</v>
-      </c>
-      <c r="P49">
-        <f t="shared" si="8"/>
+        <v>71</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>1</v>
+      </c>
+      <c r="R49" t="s">
         <v>1</v>
       </c>
       <c r="S49">
-        <f t="shared" si="9"/>
-        <v>10</v>
+        <v>24.34</v>
       </c>
       <c r="T49">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA49">
-        <v>55</v>
-      </c>
-      <c r="AB49">
-        <v>87</v>
-      </c>
-      <c r="AC49" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD49" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE49">
-        <v>21.59</v>
-      </c>
-      <c r="AF49">
+        <v>9</v>
+      </c>
+      <c r="U49">
         <v>8</v>
       </c>
-      <c r="AG49">
-        <v>5</v>
-      </c>
-      <c r="AH49">
-        <v>2</v>
-      </c>
-      <c r="AI49">
-        <v>2</v>
-      </c>
-      <c r="AO49" t="s">
-        <v>159</v>
-      </c>
-      <c r="AP49" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="50" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" t="s">
-        <v>156</v>
-      </c>
-      <c r="B50">
-        <v>33</v>
-      </c>
-      <c r="C50">
-        <v>4</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" t="s">
-        <v>155</v>
-      </c>
-      <c r="G50" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H50" s="8">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="I50">
-        <v>4</v>
-      </c>
-      <c r="J50">
-        <v>10</v>
-      </c>
-      <c r="N50">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O50">
-        <v>9.5</v>
-      </c>
-      <c r="P50">
-        <f t="shared" si="8"/>
-        <v>0.95</v>
-      </c>
-      <c r="S50">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T50">
-        <f t="shared" si="6"/>
-        <v>0.5</v>
-      </c>
-      <c r="AA50">
-        <v>56</v>
-      </c>
-      <c r="AB50">
-        <v>99</v>
-      </c>
-      <c r="AC50" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD50" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE50">
-        <v>27.07</v>
-      </c>
-      <c r="AF50">
-        <v>12</v>
-      </c>
-      <c r="AG50">
-        <v>8</v>
-      </c>
-      <c r="AH50">
-        <v>1</v>
-      </c>
-      <c r="AI50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" t="s">
-        <v>156</v>
-      </c>
-      <c r="B51">
-        <v>34</v>
-      </c>
-      <c r="C51">
-        <v>4</v>
-      </c>
-      <c r="D51">
-        <v>2</v>
-      </c>
-      <c r="E51" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" t="s">
-        <v>155</v>
-      </c>
-      <c r="G51" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H51" s="8">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="I51">
-        <v>4</v>
-      </c>
-      <c r="J51">
-        <v>10</v>
-      </c>
-      <c r="N51">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O51">
-        <v>6.5</v>
-      </c>
-      <c r="P51">
-        <f t="shared" si="8"/>
-        <v>0.65</v>
-      </c>
-      <c r="S51">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T51">
-        <f t="shared" si="6"/>
-        <v>3.5</v>
-      </c>
-      <c r="AA51">
-        <v>57</v>
-      </c>
-      <c r="AB51">
-        <v>41</v>
-      </c>
-      <c r="AC51" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD51" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE51">
-        <v>38.49</v>
-      </c>
-      <c r="AF51">
-        <v>40</v>
-      </c>
-      <c r="AG51">
-        <v>8</v>
-      </c>
-      <c r="AH51">
-        <v>2</v>
-      </c>
-      <c r="AI51">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" t="s">
-        <v>156</v>
-      </c>
-      <c r="B52">
-        <v>35</v>
-      </c>
-      <c r="C52">
-        <v>4</v>
-      </c>
-      <c r="D52">
-        <v>3</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>155</v>
-      </c>
-      <c r="G52" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H52" s="8">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="I52">
-        <v>4</v>
-      </c>
-      <c r="J52">
-        <v>10</v>
-      </c>
-      <c r="N52">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O52">
-        <v>8.5</v>
-      </c>
-      <c r="P52">
-        <f t="shared" si="8"/>
-        <v>0.85</v>
-      </c>
-      <c r="S52">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T52">
-        <f t="shared" si="6"/>
-        <v>1.5</v>
-      </c>
-      <c r="AA52">
-        <v>58</v>
-      </c>
-      <c r="AB52">
-        <v>70</v>
-      </c>
-      <c r="AC52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD52" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE52">
-        <v>25.21</v>
-      </c>
-      <c r="AF52">
-        <v>10</v>
-      </c>
-      <c r="AG52">
-        <v>6</v>
-      </c>
-      <c r="AH52">
-        <v>1</v>
-      </c>
-      <c r="AI52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" t="s">
-        <v>156</v>
-      </c>
-      <c r="B53">
-        <v>36</v>
-      </c>
-      <c r="C53">
-        <v>4</v>
-      </c>
-      <c r="D53">
-        <v>4</v>
-      </c>
-      <c r="E53" t="s">
-        <v>13</v>
-      </c>
-      <c r="F53" t="s">
-        <v>155</v>
-      </c>
-      <c r="G53" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H53" s="8">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="I53">
-        <v>4</v>
-      </c>
-      <c r="J53">
-        <v>10</v>
-      </c>
-      <c r="N53">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O53">
-        <v>8.5</v>
-      </c>
-      <c r="P53">
-        <f t="shared" si="8"/>
-        <v>0.85</v>
-      </c>
-      <c r="S53">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T53">
-        <f t="shared" si="6"/>
-        <v>1.5</v>
-      </c>
-      <c r="AA53">
-        <v>59</v>
-      </c>
-      <c r="AB53">
-        <v>80</v>
-      </c>
-      <c r="AC53" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD53" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE53">
-        <v>25.84</v>
-      </c>
-      <c r="AF53">
-        <v>14</v>
-      </c>
-      <c r="AG53">
-        <v>8</v>
-      </c>
-      <c r="AH53">
-        <v>2</v>
-      </c>
-      <c r="AI53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" t="s">
-        <v>156</v>
-      </c>
-      <c r="B54">
-        <v>37</v>
-      </c>
-      <c r="C54">
-        <v>4</v>
-      </c>
-      <c r="D54">
-        <v>5</v>
-      </c>
-      <c r="E54" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" t="s">
-        <v>155</v>
-      </c>
-      <c r="G54" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H54" s="8">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="I54">
-        <v>4</v>
-      </c>
-      <c r="J54">
-        <v>10</v>
-      </c>
-      <c r="N54">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O54">
-        <v>9</v>
-      </c>
-      <c r="P54">
-        <f t="shared" si="8"/>
-        <v>0.9</v>
-      </c>
-      <c r="S54">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T54">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="AA54">
-        <v>60</v>
-      </c>
-      <c r="AC54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD54" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE54">
-        <v>23.41</v>
-      </c>
-      <c r="AF54">
-        <v>9</v>
-      </c>
-      <c r="AG54">
-        <v>8</v>
-      </c>
-      <c r="AH54">
-        <v>1</v>
-      </c>
-      <c r="AI54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" t="s">
-        <v>156</v>
-      </c>
-      <c r="B55">
-        <v>38</v>
-      </c>
-      <c r="C55">
-        <v>4</v>
-      </c>
-      <c r="D55">
-        <v>6</v>
-      </c>
-      <c r="E55" t="s">
-        <v>6</v>
-      </c>
-      <c r="F55" t="s">
-        <v>155</v>
-      </c>
-      <c r="G55" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H55" s="8">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="I55">
-        <v>4</v>
-      </c>
-      <c r="J55">
-        <v>10</v>
-      </c>
-      <c r="N55">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O55">
-        <v>9</v>
-      </c>
-      <c r="P55">
-        <f t="shared" si="8"/>
-        <v>0.9</v>
-      </c>
-      <c r="S55">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T55">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="AA55">
-        <v>61</v>
-      </c>
-      <c r="AB55">
-        <v>81</v>
-      </c>
-      <c r="AC55" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD55" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE55">
-        <v>30.38</v>
-      </c>
-      <c r="AF55">
-        <v>22</v>
-      </c>
-      <c r="AG55">
-        <v>8</v>
-      </c>
-      <c r="AH55">
-        <v>2</v>
-      </c>
-      <c r="AI55">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" t="s">
-        <v>156</v>
-      </c>
-      <c r="B56">
-        <v>39</v>
-      </c>
-      <c r="C56">
-        <v>4</v>
-      </c>
-      <c r="D56">
-        <v>7</v>
-      </c>
-      <c r="E56" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" t="s">
-        <v>155</v>
-      </c>
-      <c r="G56" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H56" s="8">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="I56">
-        <v>4</v>
-      </c>
-      <c r="J56">
-        <v>10</v>
-      </c>
-      <c r="N56">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O56">
-        <v>10</v>
-      </c>
-      <c r="P56">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="S56">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T56">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA56">
-        <v>62</v>
-      </c>
-      <c r="AB56">
-        <v>92</v>
-      </c>
-      <c r="AC56" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD56" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE56">
-        <v>20.48</v>
-      </c>
-      <c r="AF56">
-        <v>6</v>
-      </c>
-      <c r="AG56">
-        <v>8</v>
-      </c>
-      <c r="AH56">
-        <v>2</v>
-      </c>
-      <c r="AI56">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" t="s">
-        <v>156</v>
-      </c>
-      <c r="B57">
-        <v>40</v>
-      </c>
-      <c r="C57">
-        <v>4</v>
-      </c>
-      <c r="D57">
-        <v>8</v>
-      </c>
-      <c r="E57" t="s">
-        <v>12</v>
-      </c>
-      <c r="F57" t="s">
-        <v>155</v>
-      </c>
-      <c r="G57" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H57" s="8">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="I57">
-        <v>4</v>
-      </c>
-      <c r="J57">
-        <v>10</v>
-      </c>
-      <c r="N57">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O57">
-        <v>8.5</v>
-      </c>
-      <c r="P57">
-        <f t="shared" si="8"/>
-        <v>0.85</v>
-      </c>
-      <c r="S57">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T57">
-        <f t="shared" si="6"/>
-        <v>1.5</v>
-      </c>
-      <c r="AA57">
-        <v>63</v>
-      </c>
-      <c r="AC57" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD57" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE57">
-        <v>40.880000000000003</v>
-      </c>
-      <c r="AF57">
-        <v>41</v>
-      </c>
-      <c r="AG57">
-        <v>8</v>
-      </c>
-      <c r="AH57">
-        <v>1</v>
-      </c>
-      <c r="AI57">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" t="s">
-        <v>156</v>
-      </c>
-      <c r="B58">
-        <v>41</v>
-      </c>
-      <c r="C58">
-        <v>4</v>
-      </c>
-      <c r="D58">
-        <v>9</v>
-      </c>
-      <c r="E58" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" t="s">
-        <v>155</v>
-      </c>
-      <c r="G58" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H58" s="8">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="I58">
-        <v>4</v>
-      </c>
-      <c r="J58">
-        <v>10</v>
-      </c>
-      <c r="N58">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O58">
-        <v>10</v>
-      </c>
-      <c r="P58">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="S58">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T58">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA58">
-        <v>64</v>
-      </c>
-      <c r="AB58">
-        <v>90</v>
-      </c>
-      <c r="AC58" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD58" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE58">
-        <v>31.11</v>
-      </c>
-      <c r="AF58">
-        <v>20</v>
-      </c>
-      <c r="AG58">
-        <v>7</v>
-      </c>
-      <c r="AH58">
-        <v>2</v>
-      </c>
-      <c r="AI58">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" t="s">
-        <v>156</v>
-      </c>
-      <c r="B59">
-        <v>42</v>
-      </c>
-      <c r="C59">
-        <v>4</v>
-      </c>
-      <c r="D59">
-        <v>10</v>
-      </c>
-      <c r="E59" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" t="s">
-        <v>155</v>
-      </c>
-      <c r="G59" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H59" s="8">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="I59">
-        <v>4</v>
-      </c>
-      <c r="J59">
-        <v>10</v>
-      </c>
-      <c r="N59">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O59">
-        <v>1</v>
-      </c>
-      <c r="P59">
-        <f t="shared" si="8"/>
-        <v>0.1</v>
-      </c>
-      <c r="S59">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T59">
-        <f t="shared" si="6"/>
-        <v>9</v>
-      </c>
-      <c r="AA59">
-        <v>65</v>
-      </c>
-      <c r="AC59" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD59" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE59">
-        <v>35.61</v>
-      </c>
-      <c r="AF59">
-        <v>27</v>
-      </c>
-      <c r="AG59">
-        <v>8</v>
-      </c>
-      <c r="AH59">
-        <v>2</v>
-      </c>
-      <c r="AI59">
-        <v>2</v>
-      </c>
-      <c r="AP59" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" t="s">
-        <v>156</v>
-      </c>
-      <c r="B60">
-        <v>43</v>
-      </c>
-      <c r="C60">
-        <v>4</v>
-      </c>
-      <c r="D60">
-        <v>11</v>
-      </c>
-      <c r="E60" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" t="s">
-        <v>155</v>
-      </c>
-      <c r="G60" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H60" s="8">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="I60">
-        <v>4</v>
-      </c>
-      <c r="J60">
-        <v>10</v>
-      </c>
-      <c r="N60">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O60">
-        <v>9.5</v>
-      </c>
-      <c r="P60">
-        <f t="shared" si="8"/>
-        <v>0.95</v>
-      </c>
-      <c r="S60">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T60">
-        <f t="shared" si="6"/>
-        <v>0.5</v>
-      </c>
-      <c r="AA60">
-        <v>66</v>
-      </c>
-      <c r="AC60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE60">
-        <v>28.04</v>
-      </c>
-      <c r="AF60">
-        <v>15</v>
-      </c>
-      <c r="AG60">
-        <v>8</v>
-      </c>
-      <c r="AH60">
-        <v>2</v>
-      </c>
-      <c r="AI60">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" t="s">
-        <v>156</v>
-      </c>
-      <c r="B61">
-        <v>44</v>
-      </c>
-      <c r="C61">
-        <v>4</v>
-      </c>
-      <c r="D61">
-        <v>12</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>155</v>
-      </c>
-      <c r="G61" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H61" s="8">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="I61">
-        <v>4</v>
-      </c>
-      <c r="J61">
-        <v>10</v>
-      </c>
-      <c r="N61">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O61">
-        <v>9</v>
-      </c>
-      <c r="P61">
-        <f t="shared" si="8"/>
-        <v>0.9</v>
-      </c>
-      <c r="S61">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T61">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="AA61">
-        <v>67</v>
-      </c>
-      <c r="AB61">
-        <v>83</v>
-      </c>
-      <c r="AC61" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD61" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE61">
-        <v>28.37</v>
-      </c>
-      <c r="AF61">
-        <v>15</v>
-      </c>
-      <c r="AG61">
-        <v>8</v>
-      </c>
-      <c r="AH61">
-        <v>2</v>
-      </c>
-      <c r="AI61">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" t="s">
-        <v>156</v>
-      </c>
-      <c r="B62">
-        <v>45</v>
-      </c>
-      <c r="C62">
-        <v>4</v>
-      </c>
-      <c r="D62">
-        <v>13</v>
-      </c>
-      <c r="E62" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" t="s">
-        <v>155</v>
-      </c>
-      <c r="G62" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H62" s="8">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="I62">
-        <v>4</v>
-      </c>
-      <c r="J62">
-        <v>10</v>
-      </c>
-      <c r="N62">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O62">
-        <v>8</v>
-      </c>
-      <c r="P62">
-        <f t="shared" si="8"/>
-        <v>0.8</v>
-      </c>
-      <c r="S62">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T62">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AA62">
-        <v>68</v>
-      </c>
-      <c r="AC62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE62">
-        <v>25.25</v>
-      </c>
-      <c r="AF62">
-        <v>11</v>
-      </c>
-      <c r="AG62">
-        <v>8</v>
-      </c>
-      <c r="AH62">
-        <v>2</v>
-      </c>
-      <c r="AI62">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" t="s">
-        <v>156</v>
-      </c>
-      <c r="B63">
-        <v>46</v>
-      </c>
-      <c r="C63">
-        <v>4</v>
-      </c>
-      <c r="D63">
-        <v>14</v>
-      </c>
-      <c r="E63" t="s">
-        <v>12</v>
-      </c>
-      <c r="F63" t="s">
-        <v>155</v>
-      </c>
-      <c r="G63" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H63" s="8">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="I63">
-        <v>4</v>
-      </c>
-      <c r="J63">
-        <v>10</v>
-      </c>
-      <c r="N63">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O63">
-        <v>9.5</v>
-      </c>
-      <c r="P63">
-        <f t="shared" si="8"/>
-        <v>0.95</v>
-      </c>
-      <c r="S63">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T63">
-        <f t="shared" si="6"/>
-        <v>0.5</v>
-      </c>
-      <c r="AA63">
-        <v>69</v>
-      </c>
-      <c r="AB63">
-        <v>76</v>
-      </c>
-      <c r="AC63" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD63" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE63">
-        <v>30.46</v>
-      </c>
-      <c r="AF63">
-        <v>20</v>
-      </c>
-      <c r="AG63">
-        <v>8</v>
-      </c>
-      <c r="AH63">
-        <v>2</v>
-      </c>
-      <c r="AI63">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" t="s">
-        <v>156</v>
-      </c>
-      <c r="B64">
-        <v>47</v>
-      </c>
-      <c r="C64">
-        <v>4</v>
-      </c>
-      <c r="D64">
-        <v>15</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" t="s">
-        <v>155</v>
-      </c>
-      <c r="G64" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H64" s="8">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="I64">
-        <v>4</v>
-      </c>
-      <c r="J64">
-        <v>10</v>
-      </c>
-      <c r="N64">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O64">
-        <v>10</v>
-      </c>
-      <c r="P64">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="S64">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T64">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA64">
-        <v>70</v>
-      </c>
-      <c r="AB64">
-        <v>79</v>
-      </c>
-      <c r="AC64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE64">
-        <v>24.78</v>
-      </c>
-      <c r="AF64">
-        <v>10</v>
-      </c>
-      <c r="AG64">
-        <v>6</v>
-      </c>
-      <c r="AH64">
-        <v>2</v>
-      </c>
-      <c r="AI64">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:35" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" t="s">
-        <v>156</v>
-      </c>
-      <c r="B65">
-        <v>48</v>
-      </c>
-      <c r="C65">
-        <v>4</v>
-      </c>
-      <c r="D65">
-        <v>16</v>
-      </c>
-      <c r="E65" t="s">
-        <v>13</v>
-      </c>
-      <c r="F65" t="s">
-        <v>155</v>
-      </c>
-      <c r="G65" s="2">
-        <v>45959</v>
-      </c>
-      <c r="H65" s="8">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="I65">
-        <v>4</v>
-      </c>
-      <c r="J65">
-        <v>10</v>
-      </c>
-      <c r="N65">
-        <f t="shared" si="7"/>
-        <v>10</v>
-      </c>
-      <c r="O65">
-        <v>8</v>
-      </c>
-      <c r="P65">
-        <f t="shared" si="8"/>
-        <v>0.8</v>
-      </c>
-      <c r="S65">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="T65">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="AA65">
-        <v>71</v>
-      </c>
-      <c r="AC65" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD65" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE65">
-        <v>24.34</v>
-      </c>
-      <c r="AF65">
-        <v>9</v>
-      </c>
-      <c r="AG65">
-        <v>8</v>
-      </c>
-      <c r="AH65">
-        <v>2</v>
-      </c>
-      <c r="AI65">
+      <c r="V49">
+        <v>2</v>
+      </c>
+      <c r="W49">
         <v>1</v>
       </c>
     </row>

--- a/data/raw/NCE_data.xlsx
+++ b/data/raw/NCE_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://waikatouniversitynz-my.sharepoint.com/personal/or81_students_waikato_ac_nz/Documents/Documents/PhD/01_thesis_chapters/05_fear_study/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="140" documentId="8_{1C509BC5-B9CD-4355-A94E-B3E32C99D6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{003AD1E5-8066-4073-A0FE-EAFF5DE9D967}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="8_{1C509BC5-B9CD-4355-A94E-B3E32C99D6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A37559C7-E1B4-4771-8AD6-26F106EB4C95}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{884ED942-72D7-478A-91F6-B92A4F060477}"/>
+    <workbookView minimized="1" xWindow="58395" yWindow="3450" windowWidth="7500" windowHeight="6000" xr2:uid="{884ED942-72D7-478A-91F6-B92A4F060477}"/>
   </bookViews>
   <sheets>
     <sheet name="NCE_exp" sheetId="2" r:id="rId1"/>
@@ -805,7 +805,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -823,6 +823,7 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4774,34 +4775,35 @@
       <c r="AY19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="BA19">
+      <c r="BA19" s="17">
         <v>58</v>
       </c>
-      <c r="BB19">
+      <c r="BB19" s="17">
         <v>58</v>
       </c>
-      <c r="BD19">
-        <v>2</v>
-      </c>
-      <c r="BE19" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF19" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG19">
+      <c r="BC19" s="17"/>
+      <c r="BD19" s="17">
+        <v>2</v>
+      </c>
+      <c r="BE19" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF19" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="BG19" s="17">
         <v>26.88</v>
       </c>
-      <c r="BH19">
+      <c r="BH19" s="17">
         <v>13</v>
       </c>
-      <c r="BI19">
+      <c r="BI19" s="17">
         <v>8</v>
       </c>
-      <c r="BJ19">
+      <c r="BJ19" s="17">
         <v>0</v>
       </c>
-      <c r="BK19">
+      <c r="BK19" s="17">
         <v>2</v>
       </c>
       <c r="BR19" s="2"/>
@@ -11506,7 +11508,7 @@
         <v>9</v>
       </c>
       <c r="BA56">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="BB56">
         <v>75</v>
@@ -12773,37 +12775,37 @@
       <c r="AY63" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="BA63">
+      <c r="BA63" s="17">
         <v>102</v>
       </c>
-      <c r="BB63">
+      <c r="BB63" s="17">
         <v>102</v>
       </c>
-      <c r="BC63">
+      <c r="BC63" s="17">
         <v>58</v>
       </c>
-      <c r="BD63">
+      <c r="BD63" s="17">
         <v>14</v>
       </c>
-      <c r="BE63" t="s">
-        <v>1</v>
-      </c>
-      <c r="BF63" t="s">
-        <v>1</v>
-      </c>
-      <c r="BG63">
+      <c r="BE63" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF63" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="BG63" s="17">
         <v>26.87</v>
       </c>
-      <c r="BH63">
+      <c r="BH63" s="17">
         <v>11</v>
       </c>
-      <c r="BI63">
+      <c r="BI63" s="17">
         <v>7</v>
       </c>
-      <c r="BJ63">
-        <v>2</v>
-      </c>
-      <c r="BK63">
+      <c r="BJ63" s="17">
+        <v>2</v>
+      </c>
+      <c r="BK63" s="17">
         <v>2</v>
       </c>
       <c r="BR63" s="2"/>
